--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>34.20000000000027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.05005e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.492</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2294850460880035</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9117348194682676</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.382022521022515</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.96481337859651</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.51316755848042</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.34705985591967</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 6.571x + -14531.524</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.205509400413091e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2652.816355383428</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8164290424822086</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>72.45000000000027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.05161e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.054</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3846586601078535</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.2503263427891</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.384893305564139</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.141879435883444</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.06379504898048</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.173x + -15104.066</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.926554895992382e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2535.796768424105</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8167890851169918</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>86.98000000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.05226e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.274</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2397672969372497</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.009010407698981</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.002422501929528</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.112992077985594</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.80798960018973</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.946x + -14320.865</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.212245093627643e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2490.787529487453</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8169176540291773</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97.51999999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.05291e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.414</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3501464651645957</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9717721362737951</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.069455352377541</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.996827109048287</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.7535500828057</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.900x + -14041.210</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.344720131362429e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2459.567312157532</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8170249113027882</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.05335e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.535</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3686085134892848</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.89116369914952</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.926453288571458</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.93998286664764</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.77058638393777</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.914x + -13919.007</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.664310027760281e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2432.208839873017</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000011593e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8171670241063483</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110.6200000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.05377e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.631</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1487730363654174</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8383467530932587</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.626298478154131</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.106449255987164</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>81.32543878358123</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.554x + -13022.089</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.900498580002884e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2407.354759170283</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8173498152651262</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>119.4199999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.05451e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2299338700590891</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7143512204342742</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.070379490846969</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.080394153878762</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.29900621639202</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.534x + -12856.937</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.052043104068951e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2384.044821637456</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000201779e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8175382246741291</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>128.26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.05481e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.83199999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2545023264494192</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.177978654821514</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.731666160886648</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.350571170729051</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81.35220862018741</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.575x + -12830.076</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.649142491406476e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2362.751824886014</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000009025e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8177361393076815</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>128.3099999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.05533e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.90900000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1920988709124505</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7597588092186146</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.05545177468824</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.638453666211698</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.95650726652701</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 6.283x + -12121.902</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.908130286251949e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2343.211486301636</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000067882e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8179322349113838</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.0555e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.98099999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4984085124369117</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.607854202421477</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.825480393688617</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.556753500969978</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.82040280242383</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 6.188x + -11836.707</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.05937704701869e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2324.677621349778</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.818146980576532</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>143.8800000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.05571e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.057</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7324841365319408</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.405327996482811</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.328669498677294</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.232004389831275</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>81.28144585114816</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 6.521x + -12418.732</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.571729883172873e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2306.326090182869</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000152832e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8183527964476967</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>142.9399999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.05597e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.125</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.04733327142602921</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.920580467823689</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.844943631070001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.672277950581289</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80.66582593562056</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 6.084x + -11455.128</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.790366233193906e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2288.712336173526</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000099389e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8185770352402901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>144.72</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.05623e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.193</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2782604091437579</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4801439799008048</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.52453563469924</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.418167897778835</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>80.70512503046389</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 6.110x + -11419.886</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.849710405073938e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2271.346971401868</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8188130232065193</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>158.98</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.0563e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.26900000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2696173664028442</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.085184214499734</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.159718663370333</v>
+      </c>
+      <c r="I15" t="n">
+        <v>161.5361781834394</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13.23225507074418</v>
+      </c>
+      <c r="K15" t="n">
+        <v>81.01223314878425</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 6.322x + -11759.363</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.662643561047096e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2254.441781294051</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8190634983198728</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>160.21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.05636e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.32899999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5187671132853936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.347753456221208</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.810854263797419</v>
+      </c>
+      <c r="I16" t="n">
+        <v>95.02163482108934</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12.80203987389221</v>
+      </c>
+      <c r="K16" t="n">
+        <v>80.66484607984803</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 6.083x + -11207.444</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.025842568782027e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2237.358463198035</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000327e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8193162547204189</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>167.8800000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.05674e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2997701145575761</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9605998038662696</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.018198539370903</v>
+      </c>
+      <c r="I17" t="n">
+        <v>117.7590066559949</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.01550196845362</v>
+      </c>
+      <c r="K17" t="n">
+        <v>80.5500727252478</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.008x + -10969.497</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.506004375871525e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2218.544026680097</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8195739759225688</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>160.3800000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.05681e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.46899999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1870019213098451</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9469573745814291</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.649445068294622</v>
+      </c>
+      <c r="I18" t="n">
+        <v>130.2858933423074</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.9785488939127</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80.31281421458912</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 5.858x + -10588.320</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.106273292875994e-07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2199.208638576296</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000030748e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8198329197472933</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>166.0400000000002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.05718e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1217157933677126</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.06403055153623</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.554126858888137</v>
+      </c>
+      <c r="I19" t="n">
+        <v>156.0368456143822</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11.69193191600545</v>
+      </c>
+      <c r="K19" t="n">
+        <v>80.02813702653556</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.688x + -10171.747</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.419850187548451e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2179.368621787795</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8201046979891833</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>165.3100000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.05747e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.636</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.03794074822452956</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5625863827636554</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.304550078785692</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.54069689900615</v>
+      </c>
+      <c r="K20" t="n">
+        <v>79.44889331479698</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 5.369x + -9480.571</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.047130096172059e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2160.272712394857</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.00000000000263e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8203777163172912</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>185.77</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.05768e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8069869720462988</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9343169398906577</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.561089956336871</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.4017455706923</v>
+      </c>
+      <c r="K21" t="n">
+        <v>79.91750698976013</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 5.624x + -9881.313</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.687192281668998e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2140.873516812504</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000120302e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8206657821089919</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>189.0699999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.05792e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.782</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6534863945577725</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9784512371289356</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.79013894862836</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14.93830358927775</v>
+      </c>
+      <c r="K22" t="n">
+        <v>79.26125899409929</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 5.273x + -9141.055</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.264954517345809e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2120.860802679746</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.820957461140848</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-353.1399999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.80773e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.444</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1445789469345338</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7604756728346141</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.853294080221938</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.669289995406845</v>
+      </c>
+      <c r="J2" t="n">
+        <v>89.76950346118916</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.09430783337544</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 30.055x + -78760.157</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.786831553088973e-07</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3011.390085308609</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000232958e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8161385629375092</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-76.56999999999971</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.83661e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.511</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3818162323081923</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.147766437032013</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.425940734313148</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10.26766489092141</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.09575976678013</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.670x + -21089.865</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.233518091867686e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2717.953516990817</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001024e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8169989630959666</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>55.86999999999989</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.789380000000001e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.307</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2553528543394512</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.148965500645029</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.178143219805741</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.621626337690618</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.88686765536133</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 7.015x + -15220.715</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.434306613700836e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2640.42276538133</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000028616e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8171656507180421</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>128.9199999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.76139e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.712</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4826688389467782</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.474534677935025</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.551418930969855</v>
+      </c>
+      <c r="I5" t="n">
+        <v>94.2665018684901</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.41846900261313</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.12892926366001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 7.233x + -15445.573</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.711065944226108e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2592.826133116453</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000041606e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8172691439735189</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>155.4600000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.74876e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.973</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.009891440307489442</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6965849257542726</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.756289284891249</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.200001266309295</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.41976774629789</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.628x + -13852.937</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.807054464653887e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2551.09613769508</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000016451e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8173830739668587</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>186.6400000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.74243e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3278303911701608</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9353620008008451</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.971391505277188</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.061888657648388</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>81.17035524019785</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.438x + -13236.676</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.612455610070082e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2512.0231756733</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000107133e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8175095380799655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>199.97</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.741360000000001e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.364</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05366468757043546</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7020164046096002</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.152978730997928</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.82604458027804</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.75572285552995</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.144x + -12411.653</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.679975798242193e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2475.294392573575</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000904e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8176623878828427</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>217.49</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.74237e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.518</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3516471436276056</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6421215460414904</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.976196603117052</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.761157167783962</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.57165800571153</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.022x + -11990.813</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.294722738196046e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2440.997626481409</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000016248e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8178330000012838</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>222.6900000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.74664e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.64400000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.061919367068565</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.175823067208262</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.517860839839246</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.400999184891</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.89208914264633</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.609x + -10973.140</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.160217842635149e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2409.05635538728</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000025692e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8180311021553025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>240.27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.751959999999999e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.765</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1398900408625366</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9920217197286048</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.595946545525786</v>
+      </c>
+      <c r="I11" t="n">
+        <v>218.4362878340127</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.90198656556534</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.04006496451282</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.695x + -11021.412</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.799878448228988e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2379.12308594633</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8182581466551765</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-7.980000000000018</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.72135e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.926</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1656.568567225756</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.028857051805552</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.016396611544593</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.71801986465499</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7.742967931525837</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-85.82040409444005</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = -13.684x + 33683.172</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.001697785037651e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2674.284493773773</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8165380297806613</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>151.9499999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.65722e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.03700000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2529629039766714</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.355951619639265</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.944795797822973</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.729611011067499</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.46238613246548</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 6.661x + -13909.111</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.527194843870823e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2543.438231911937</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.816893901879613</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>208.4600000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.64161e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.36199999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2382581298525882</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.258968562129347</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.306272676671824</v>
+      </c>
+      <c r="I4" t="n">
+        <v>113.2765236757852</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.10855099166881</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.73056589589275</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.880x + -14127.828</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.73755727272483e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2498.320323195103</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.816966791088103</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>223.5399999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.63627e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.54000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1760504078327485</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5045293470557471</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.391650945373703</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.573435797253967</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>80.77018552246251</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.154x + -12395.112</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.417716927405043e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2468.881075696555</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000226e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.817003527336025</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>240.8899999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.63395e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.223086058834283</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.273925209285006</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.820325334899557</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.958181476390237</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80.73905095853198</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.133x + -12233.196</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.771905265476392e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2444.66050228381</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000004754e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8170836664869446</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>246.8699999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.63448e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0741945992124429</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6978039638298839</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.960425074315506</v>
+      </c>
+      <c r="I7" t="n">
+        <v>156.9225691472907</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11.97479660027733</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.42384485326912</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.927x + -11690.927</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.054545805753066e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2422.261225547426</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000018646e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8172060814185189</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>256.3499999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.63549e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.85299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.001248707332933483</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7666237820916938</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.312164149141327</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25.25669326091678</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.24359187525593</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 5.816x + -11359.064</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.967864930265573e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2401.760521299128</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001124e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8173700029627323</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>271.4799999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.64281e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.91800000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3805797275400432</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.103456164048328</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.500830451179291</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.15069688435534</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.22458941476644</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 5.804x + -11257.414</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.151262931802478e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2382.859112404922</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8175663715730012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>269.51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.64436e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3606018139721277</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.932489075902218</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.416635528966547</v>
+      </c>
+      <c r="I10" t="n">
+        <v>92.1903162381076</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.10461781313708</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.97780457130467</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.658x + -10869.387</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.276352370959234e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2364.158321890183</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8177835016258257</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>277.5599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.648890000000001e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5511483594942026</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.948567449698868</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.168022407329723</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14.88958405013333</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79.71579786482299</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.511x + -10490.285</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.213274958644838e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2346.350680881624</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000037979e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8180193315197199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>280.8099999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.65104e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.111</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3340320331106048</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.721110757677336</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.77561061095463</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13.14867659308288</v>
+      </c>
+      <c r="K12" t="n">
+        <v>79.30153815519702</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 5.293x + -9976.290</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.285735264623511e-07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2328.743438180887</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000062752e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.81826740690988</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.65556e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.176</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3471056561107775</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.13709222758171</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.653177338914261</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.38858150051373</v>
+      </c>
+      <c r="K13" t="n">
+        <v>79.22364525887699</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 5.254x + -9821.919</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.501943032585831e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2311.154004215749</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8185265014020772</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>294.9799999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.65881e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.235</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2706076348460714</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.670943180479548</v>
+      </c>
+      <c r="H14" t="n">
+        <v>227.3232916582942</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.506617038875208</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15.61731569043798</v>
+      </c>
+      <c r="K14" t="n">
+        <v>78.61445943814785</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 4.966x + -9178.377</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.082177876915714e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2294.221169055784</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000020636e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.818778926608831</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>285.04</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.65832e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.30200000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6445833554132325</v>
+      </c>
+      <c r="H15" t="n">
+        <v>82.05334716232932</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.813064629317002</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17.6199836138575</v>
+      </c>
+      <c r="K15" t="n">
+        <v>78.30266259639752</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 4.830x + -8839.225</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.708787579501874e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2276.695625055484</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000275e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8190324203767602</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.66049e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.374</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4883549082127023</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.095797266738241</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.891766816469899</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14.94533875307528</v>
+      </c>
+      <c r="K16" t="n">
+        <v>77.5568465763868</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 4.532x + -8187.162</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.867870865145007e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2259.213562200337</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.00000000000057e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8193055149624258</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>311.3599999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.663550000000001e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.44199999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7034386978764323</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.348296817527572</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.868179526312546</v>
+      </c>
+      <c r="J17" t="n">
+        <v>15.32296882602677</v>
+      </c>
+      <c r="K17" t="n">
+        <v>76.80255617255989</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 4.264x + -7598.949</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.6082566251541e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2240.449683571833</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8195705992598853</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>316.1500000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.66478e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.518</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3641921920536133</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.188582495060085</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.504481906177751</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14.74180737221922</v>
+      </c>
+      <c r="K18" t="n">
+        <v>76.08746304544461</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 4.037x + -7095.700</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.582652997610923e-07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2221.403972757881</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000073e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.819850926027284</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>324.0700000000002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.66655e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.58799999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.780083888284994</v>
+      </c>
+      <c r="G19" t="n">
+        <v>265.9202271174925</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.285032003146982</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.418456234320121</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.97462815327426</v>
+      </c>
+      <c r="K19" t="n">
+        <v>74.42830302001586</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 3.588x + -6174.368</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.218837313543849e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2201.693149781671</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8201283384230544</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.67068e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.654</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.08991647443220739</v>
+      </c>
+      <c r="G20" t="n">
+        <v>129.7756561245102</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.325242113593637</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.857065206495601</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>75.7245552548771</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 3.930x + -6777.427</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.369674985823065e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2182.224619966437</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8204074573804105</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>328.8099999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.67213e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.714</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8293180911928117</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.856753153755542</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.671136805359361</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.79659607309218</v>
+      </c>
+      <c r="K21" t="n">
+        <v>71.47192935793714</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 2.984x + -4924.698</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.751548373145456e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2162.633245764146</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000292301e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8207055371406068</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.67732e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.795</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1133243076337183</v>
+      </c>
+      <c r="G22" t="n">
+        <v>138.6391193276019</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.728790196691539</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.280980592147037</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.80737643806228</v>
+      </c>
+      <c r="K22" t="n">
+        <v>74.51123344201001</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 3.609x + -6064.797</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.608922912703149e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2142.888228635001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8209818814846213</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-468.4699999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.88663e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.185</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2057593420806764</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.105907683838851</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.36970407044839</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.641220531884353</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49.39408555463013</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.96324123033871</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 28.119x + -71616.065</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.117751497835266e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2936.677572140641</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000012968e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8164851991062217</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-118.96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.8513e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.44799999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1203477286669403</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.898654026974901</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.635442683566334</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.719989318811659</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.13931916918921</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 20.012x + -45061.820</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.958086466774596e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2692.242874545106</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000014577e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8172474918555485</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41.80999999999995</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.78979e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.315</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02481220319470143</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6964719331509209</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.671513471678277</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.473927917717882</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.88833678925752</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 7.016x + -15106.113</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.247089447767962e-07</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2618.150634152249</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000153e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8174387567703176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.75794e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2879055827993872</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.506813794196044</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.773380966419395</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.314709404821689</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.39979066064795</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.612x + -13932.589</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.635158269243158e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2572.52477865014</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8175968994201085</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>152.8499999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.743639999999999e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.005</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1683943636202961</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.781194210531596</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.80280347844018</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.475649650161801</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.43435707413214</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.639x + -13786.633</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.416893742440481e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2533.289867695818</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000174e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8177714730722562</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>185.6900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.736049999999999e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.205</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.417429452196065</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.425321431417159</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.030845255892864</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.55664655669159</v>
+      </c>
+      <c r="K7" t="n">
+        <v>81.6869081072623</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.844x + -14050.344</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.678018887649372e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2495.576749485846</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000001539e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8179664656866953</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>189.9199999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.73717e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1286106502330682</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7330588641550995</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.361303792710249</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.748321941369903</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.52929401056504</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 5.995x + -12026.518</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.064094262318908e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2459.577970474297</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8181836745645537</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>205.45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.740380000000001e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.53</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04474668343653658</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.109429628303797</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.617469705417038</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.205082936199291</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.56663963579884</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.019x + -11913.143</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.39092983260449e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2424.696558775766</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000007224e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8184047662893781</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.74456e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.06423757596991378</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7650552631925904</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.509966839088409</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.834348293579376</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.45632785736454</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.948x + -11610.493</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.211950006983975e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2392.166845779026</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000000021e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8186232526962256</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>236.4200000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.74979e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.785</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5501458033630298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.509719737848023</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.000623241495188</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21.14189972878443</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14.38673845139171</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.50804722548756</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.981x + -11537.817</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.579255153750097e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2361.411093080482</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.818853211455457</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-129.3400000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.90408e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07862985149743296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6713827541761467</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.845018331475061</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.435321416442945</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.09007767888573</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 19.673x + -44562.783</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.402656826550151e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2685.379793263403</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000025999e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8174613803224149</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>116.5699999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.80772e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5110277694281686</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9770484696433644</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.319816735474548</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.397622809040036</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.84538930699718</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 6.979x + -14698.110</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.230863358269388e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2556.398313011775</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000461458e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8177850475871441</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>166.8400000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.79225e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.06399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7152535867745332</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.091341211769979</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.27294244963675</v>
+      </c>
+      <c r="I4" t="n">
+        <v>109.831049622968</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.22961902674731</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.69939753094116</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.854x + -14157.445</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.793223466398135e-07</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2512.416219146788</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8178456379488879</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>182.5399999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.79507e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.23099999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2019764229100033</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9836200509265005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.081804188927177</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.879212420928498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.33003173151414</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.558x + -13346.764</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.160967592451774e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2482.432594083486</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000055893e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8178922151452737</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>196.7799999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.80403e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.349</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2610037691569966</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6546857917244217</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.179115876654897</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.684186082680875</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.23911844931203</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.489x + -13058.470</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.488412954610819e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2456.274889146551</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8179899605417242</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>198.5599999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.81352e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.44</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1527783114673207</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8530274045713003</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.598212038295621</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.990977435564807</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.60546996201529</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.044x + -11989.416</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.680785128129256e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2431.055510540169</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000118768e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8181237090838903</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>214.6199999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.821129999999999e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.53400000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05929077803703878</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.238433217245756</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.560716357865072</v>
+      </c>
+      <c r="I8" t="n">
+        <v>142.9954905608733</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.09846820616437</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.02813574746196</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.334x + -12487.465</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.275129944872111e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2407.007506266758</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.0000000000002e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8182995252561174</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.82893e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.621</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5671932623847262</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8438618306635417</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.998470242387886</v>
+      </c>
+      <c r="I9" t="n">
+        <v>63.14283551123326</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.3343036825985</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.65532393194952</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.077x + -11839.364</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.338815598007196e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2383.483686951633</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.818506955335304</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>231.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.83558e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.718</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2629833315448777</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.418673959908506</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.145778115761439</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40.7591205789175</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.50598228471504</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.60168176755981</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 6.042x + -11661.338</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.146485842324968e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2361.323694518063</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8187235001853064</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.84276e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.794</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1551171840530976</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.050480866123949</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.290924625546688</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.44773017891563</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79.95085488340752</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.643x + -10739.335</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.095200877837401e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2339.502033475297</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8189363941046487</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>247.24</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.8483e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.861</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8945027922325282</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.366291899499271</v>
+      </c>
+      <c r="H12" t="n">
+        <v>175.4470384430855</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.11893742600376</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.35831355793997</v>
+      </c>
+      <c r="K12" t="n">
+        <v>79.96308992866611</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 5.650x + -10669.779</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.424735591807638e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2318.517083546198</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000043376e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8191824354446653</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>243.28</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.853999999999999e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.95699999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1127619683915746</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7495989397176721</v>
+      </c>
+      <c r="H13" t="n">
+        <v>92.74001119599137</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.295206003041953</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.53239605355517</v>
+      </c>
+      <c r="K13" t="n">
+        <v>79.46950916523271</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 5.380x + -10029.733</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.804969955157933e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2297.534806654126</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8194237523939037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>256.0899999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.85804e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8559532461375106</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.328389985989696</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.333184107710662</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14.66175364629218</v>
+      </c>
+      <c r="K14" t="n">
+        <v>79.31465910136225</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 5.300x + -9788.442</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.747167029613001e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2277.033258264069</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000099e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8196299009321035</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>261.1800000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.861950000000001e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.107</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2356607234229905</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.213634806891813</v>
+      </c>
+      <c r="H15" t="n">
+        <v>137.9658200224859</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.99416386679548</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.57072050935274</v>
+      </c>
+      <c r="K15" t="n">
+        <v>78.85400274089908</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 5.075x + -9265.581</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.505443976199296e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2256.68389540495</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000001436e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8199098661430432</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>253.6800000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.86953e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.157</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1185021279577231</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9864508394808011</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.304114361557826</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.3647802535071</v>
+      </c>
+      <c r="K16" t="n">
+        <v>78.36099238823104</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 4.855x + -8755.208</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.171452398963669e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2237.076718461622</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000634e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8201691887276035</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>257.3700000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.872379999999999e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.23699999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.05380113572511737</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.090143531918051</v>
+      </c>
+      <c r="H17" t="n">
+        <v>63.35111615984849</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.626598489664141</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17.43238285260841</v>
+      </c>
+      <c r="K17" t="n">
+        <v>78.17445881809338</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 4.776x + -8527.548</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.623683741287399e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2217.190969365798</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8204288800316157</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>267.5200000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.87643e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.07207044813801851</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.232324247895761</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.523189088942083</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.914344935431254</v>
+      </c>
+      <c r="K18" t="n">
+        <v>77.64146237975108</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 4.564x + -8047.945</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.027216755665779e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2197.636825311049</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8206916463326047</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>279.8899999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.8799e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6213181397165357</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.247902344606112</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.80461654878724</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.49138730460957</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76.52796988685211</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 4.174x + -7235.633</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.143263996301135e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2178.145451127642</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000001557e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8209766645390726</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>282.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.88563e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.453</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.188211527472301</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.019736079446583</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.326592394364633</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.10354341677175</v>
+      </c>
+      <c r="K20" t="n">
+        <v>75.90669352731483</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 3.983x + -6817.737</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.118932855856586e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2158.628595517052</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.00000000000026e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8212503947327692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>283.6300000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.8869e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6035058288152853</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8463011961467574</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.844202944668714</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.05602717923162</v>
+      </c>
+      <c r="K21" t="n">
+        <v>75.45103271350774</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 3.853x + -6511.877</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.233822405465896e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2139.201116971368</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8215162161485162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>274</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.88957e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.575</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8605719348080185</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.362185293685391</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.26643862178885</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75.66571386144132</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 3.913x + -6573.575</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.555134227633539e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2119.861688745518</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8218041925291998</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-614.54</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.02799e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.922</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3346450058000554</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.890959066615111</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.277958507874815</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.042836670231522</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.03495252401388</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.51033630518397</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 22.999x + -53974.720</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.251675918735745e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2722.482513789381</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000017296e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8176698051296899</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-96.30000000000018</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.01085e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.69499999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1610724394091827</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8934902534604947</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.973319903309193</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.59014275151022</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.74904427002542</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.605x + -37551.050</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.754931479180862e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2559.186523764559</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000242e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8181856435898024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>53.30999999999995</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.00401e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.489</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.388816161843519</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9792127061044772</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.860796190842195</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.954153685741215</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.9062215115754</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 7.032x + -14514.852</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.105581795386281e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2502.965694501199</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000528e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8183769204677546</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105.6900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.00171e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.84</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1415250389016196</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.246585801163391</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.645144929512142</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.36699026060447</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.49194910206108</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.685x + -13542.283</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.840245649741695e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2463.981582635214</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8185163722777227</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>137.9000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.00093e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.071</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1598942784002132</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5099825813020249</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.42525797530225</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.904213287956088</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80.99987116188733</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.314x + -12568.921</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.387716667712425e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2429.137587880458</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8186844962466338</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>165.1400000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0013e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.282</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1630186829299076</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5731723277345485</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.428068579194771</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.652329495690666</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.60684936062036</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.045x + -11845.224</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.180917416166401e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2394.527931064527</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000134e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8188554601852759</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>178.5699999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.00175e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.41200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1244895923720541</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7789443752369859</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.618069492605652</v>
+      </c>
+      <c r="I8" t="n">
+        <v>109.7542742221394</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.95330561959743</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.41532819728054</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 5.922x + -11434.391</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.053913792970128e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2361.365768513816</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000253e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8190826759879687</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>188.5799999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.00236e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.541</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02914394035866134</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8408035347977428</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.612262370933581</v>
+      </c>
+      <c r="I9" t="n">
+        <v>144.2822449300018</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.21083507529948</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.35126635696295</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 5.882x + -11204.705</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.541374099500187e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2329.457937274167</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000164e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.819332156295854</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>206.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.00323e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5189174118278151</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.214168915191787</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.172152328658639</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.28678920538973</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.34649884336676</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.879x + -11062.347</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.912619760139729e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2298.439170782339</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000010019e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8195950159865549</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>211.2800000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.00425e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.768</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4415845295430562</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.893304348388936</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.129368859957696</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14.91811428563402</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79.96284655099919</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.650x + -10468.778</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.186783077225627e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2269.055220485489</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000006196e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.81985115140063</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-412.6400000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.04334e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.729</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07221102643770386</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8153864675599375</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.523630945438303</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.21598841060984</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51.98606918974787</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.03838653368703</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 29.197x + -67463.805</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.183145902954188e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2686.390486970981</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000018286e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8165520185062216</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>31.78999999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.01775e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.123</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04802972034645723</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.162847846074162</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.071463983561139</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.750417880057738</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.87646600769138</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.006x + -14814.851</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.111474521042406e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2560.684989515539</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000013943e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8168337792095237</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96.92000000000007</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.01436e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1571034666902901</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6680626160459657</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.910836983482066</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.196214401413367</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.50581769194375</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.696x + -13853.593</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.71941888220926e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2516.113398311693</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001757e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.816915519181752</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>129.4199999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.01433e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.358482999663529</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9627377802583735</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.958623020502255</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.857751477583812</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.75069506449455</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.897x + -14143.722</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.457389973645242e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2487.330254789892</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000577437e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8169795429763897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>149.9400000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.01522e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.869</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.497352742750175</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.349833159084221</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.519932584590876</v>
+      </c>
+      <c r="I6" t="n">
+        <v>33.2319258141921</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.30903338794726</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.92128411004097</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 7.045x + -14321.883</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.031497483976484e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2461.543711295295</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000019187e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8170717724703349</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>144.9000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.01607e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1072742295219764</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4619959198776698</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.993346798279628</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.6840425335955</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.68534012519825</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 6.097x + -12160.611</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.727864788294048e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2436.832044872622</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000003428e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8171979482723294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>165.1900000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.01687e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.075</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4043530171562512</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.512388706013889</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.37238199963529</v>
+      </c>
+      <c r="I8" t="n">
+        <v>115.1112371819762</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16.45125575877624</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.57974651930112</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.755x + -13435.873</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.367192601541056e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2412.822244999396</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8173656663243782</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>166.0799999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.01774e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3009057455802208</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9824012355063746</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.834218651502062</v>
+      </c>
+      <c r="I9" t="n">
+        <v>98.11477485825704</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13.55663055230919</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.97047297236134</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.293x + -12348.745</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.054996948110553e-07</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2389.72479508471</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000046243e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8175583319736806</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>173.8199999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.01854e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.241</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2269290068811579</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.101760772814085</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.673655151434051</v>
+      </c>
+      <c r="I10" t="n">
+        <v>117.1986098632979</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.99043955274803</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.91333530017002</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 6.253x + -12155.257</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.024568131383995e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2367.4116501242</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8177651938916631</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.01902e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.33499999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4727134313213929</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.203178740075887</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.972665473997059</v>
+      </c>
+      <c r="I11" t="n">
+        <v>197.3629486900238</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14.42424309320021</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.78016904878108</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 6.161x + -11858.280</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.314009031061219e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2345.958731469249</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8179934978746392</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.01963e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.401</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0547763765681951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7475629351901885</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.738895974210846</v>
+      </c>
+      <c r="I12" t="n">
+        <v>134.7982161970187</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.36322587635323</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80.2745815969581</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 5.835x + -11095.677</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.97857171440006e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2325.072926922543</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000060638e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8182255311758677</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>195.1200000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.02014e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.48699999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5453071387991288</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.007795929683587</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.543924050633056</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14.62491971941346</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80.47932636684661</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 5.963x + -11261.543</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.705364797175104e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2304.474133319054</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000004977e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8184733066684976</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>190.49</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.02064e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.55500000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3444030504286444</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5264318081434376</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.574755172271788</v>
+      </c>
+      <c r="I14" t="n">
+        <v>160.0837812543127</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12.51476857572979</v>
+      </c>
+      <c r="K14" t="n">
+        <v>80.08510871185089</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 5.721x + -10684.111</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.029102557085396e-07</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2284.753928592743</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000340535e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8187178637891661</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>199.9000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.02105e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.63</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.245714806729214</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.071463879186556</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.510289885984</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.561066897228</v>
+      </c>
+      <c r="K15" t="n">
+        <v>80.16381530960258</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 5.768x + -10690.681</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.666552701910998e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2265.661450334293</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8189684566732628</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>206.48</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.02135e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.70399999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3904550772244574</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8634324040443383</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.240531366720148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.01970933529592</v>
+      </c>
+      <c r="K16" t="n">
+        <v>79.82965826704286</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 5.574x + -10226.307</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.761022622635242e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2246.900968461987</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000041311e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8192341039442174</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>212.3400000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.02168e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.77500000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2638232518632726</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8594018518498668</v>
+      </c>
+      <c r="H17" t="n">
+        <v>149.6584194857321</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.359417809749259</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14.83379814423165</v>
+      </c>
+      <c r="K17" t="n">
+        <v>79.51745299937818</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 5.405x + -9811.821</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.314017394173889e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2227.580480675245</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8195014124726352</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>200.28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.02204e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.842</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01007423593638938</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8054758056909639</v>
+      </c>
+      <c r="H18" t="n">
+        <v>105.9799522777741</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.564154106978066</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.08648223889134</v>
+      </c>
+      <c r="K18" t="n">
+        <v>78.85770683064864</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 5.077x + -9094.208</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.099807657802709e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2207.892732821187</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000002956e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8197814386767727</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>228.1200000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.02245e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.932</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7220517471916093</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.335564449736083</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.212643479132743</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16.47982504918808</v>
+      </c>
+      <c r="K19" t="n">
+        <v>78.41101124211923</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 4.876x + -8631.513</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.073916530529249e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2188.466599121697</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8200545176185636</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>230.55</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.02259e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.994</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9302917877483331</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.381184476831069</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.260408880643395</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.1641522587751</v>
+      </c>
+      <c r="K20" t="n">
+        <v>77.78010210306275</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 4.617x + -8066.440</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.222547217124628e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2169.165781966564</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8203296737622451</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>221.3199999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.02283e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.06399999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.01274439153736469</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.084235647129528</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.536558949837817</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.44330511315562</v>
+      </c>
+      <c r="K21" t="n">
+        <v>77.66151198302688</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 4.572x + -7918.459</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.444047766692636e-07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2150.050766356738</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000037755e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8206258426420179</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>227.03</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.02313e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.14</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3239519518475613</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.322944238129567</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.8118744503229</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.48187088756099</v>
+      </c>
+      <c r="K22" t="n">
+        <v>77.64911761277996</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 4.567x + -7840.942</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.738667450564676e-07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2131.369482436101</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000109218e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8209298020088069</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-440.5800000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.05842e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.506</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3528159199901776</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6669320117494155</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.529651980191906</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.103139989096558</v>
+      </c>
+      <c r="J2" t="n">
+        <v>44.89756659844245</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.96484616691941</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 28.141x + -57740.795</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.051247856185267e-07</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2294.017082802051</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000007539e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8181831631597025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-34.09000000000015</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.05331e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.16800000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04660029998507831</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.327850653843779</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.463901758323729</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-69.91631284645814</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = -2.735x + 6209.595</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.712457392977619e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2051.599275085305</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.818895471137981</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>49.31999999999994</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.05269e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3107858070265758</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9096776634867305</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.980938647482868</v>
+      </c>
+      <c r="I4" t="n">
+        <v>61.49764626791477</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.4660026766381</v>
+      </c>
+      <c r="K4" t="n">
+        <v>80.92446931233515</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.260x + -10347.037</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.080458273433676e-07</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1991.722397896727</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000001464e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.819023732765717</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89.18000000000006</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.05424e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.935</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.474339229962512</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.351401500302413</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100.7697835095543</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.936543064069988</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.04559694701835</v>
+      </c>
+      <c r="K5" t="n">
+        <v>80.9611350739129</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.286x + -10223.294</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.410662971559168e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1957.402345524185</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000002396e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8191151929529787</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92.34000000000015</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.05608e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.06999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1597118555682698</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8167215999862497</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.84388588911887</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23.56478560098161</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.11058442340532</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80.12736363966729</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 5.746x + -9147.922</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.912706237936999e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1927.861782576359</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8192422096301489</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.05822e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01618100064961282</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.070121003233528</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.70369905569678</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13.85428694202342</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79.92610058583583</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.629x + -8826.233</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>952.8512276116016</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1779851100.575519</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.231634030276023e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7868628787226625</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>117.74</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0607e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7233808433196347</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.725761784498405</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25.67739654717785</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.696672284942948</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.543562575648232</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.06301893464592</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 5.708x + -8838.228</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>910.5175082169267</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>273617289.6517155</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.584274685941277e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7233923153944689</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>121.54</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0626e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.379</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4088697727430021</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8715005190239302</v>
+      </c>
+      <c r="H9" t="n">
+        <v>116.0786115068044</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.637143637841801</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.98323341364893</v>
+      </c>
+      <c r="K9" t="n">
+        <v>79.41383595310127</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 5.351x + -8135.038</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>906.7673291276271</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>232468487.862025</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6.099039348884555e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.734891437666408</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>131.1299999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.06462e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.465</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7204716997980477</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.839993321069983</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.223868249991634</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.708328117735769</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.05683543241226</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.172x + -7742.104</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>947.4125643243673</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>702965445.5312467</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.240243778522406e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8278783438886272</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.06619e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.54300000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7672461269706286</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.073688639716408</v>
+      </c>
+      <c r="H11" t="n">
+        <v>46.56680091890948</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.671151584716592</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13.67848923597194</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.98136727189252</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.136x + -7586.702</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>943.3992148990433</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>631947814.5222821</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.062665850609764e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8366385479089919</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>27.35999999999967</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.684039999999999e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.73999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2464082806988297</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.065456564382695</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.808311007737921</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.00874385993695</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.60782704804083</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 6.778x + -15727.235</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-15727.23503409055</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.080632580052182e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>173.6199999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000003123e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8161890479173292</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>139.2000000000003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.56945e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.723</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.209911878579621</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5326187816257929</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.74938596575435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.901539909549118</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.711666836141368</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.14125697098204</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 6.416x + -13996.824</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13996.82426852906</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.950350282412593e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>159.9200000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001598e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8165654469945532</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>185.3499999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.54046e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.047</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2981711704284343</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.160196326418705</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.140866704231422</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.990574883511687</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.73160861482086</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 6.881x + -14736.302</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14736.30205345171</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.904923746523607e-07</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8166515681835362</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>203.8699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.52796e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.255</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08881987577638284</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6166760145653803</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.81146618259224</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.043709091954853</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.25908569877066</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 6.504x + -13664.003</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13664.00322933267</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.851785725360481e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>141.4000000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001147e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.816683488194488</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>228.78</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.51974e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.414</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07380040201350339</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9824895076588682</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.094930141534711</v>
+      </c>
+      <c r="I6" t="n">
+        <v>148.6024802247455</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.40948733475846</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.58407020134409</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 6.759x + -14055.146</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14055.14574340741</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.394637800844841e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>128.3400000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8167631230097925</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.515719999999999e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.535</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08900785847456036</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6206488008115633</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.423896995470146</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.76433878048367</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.82287179736515</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 6.190x + -12645.772</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12645.77171301273</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.537950428802318e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>134.6100000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.816862872176645</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>245.6600000000003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.51519e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1719250643571295</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.172215164609002</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.944370792145309</v>
+      </c>
+      <c r="I8" t="n">
+        <v>99.71930588253194</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13.78948298022853</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.77470821132474</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 6.157x + -12428.947</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12428.94669676615</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.424484845822161e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>130.1299999999997</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000022107e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8170062526080324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>251.5600000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.51472e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.78</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3290674210841114</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4609210184406642</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.659266979585766</v>
+      </c>
+      <c r="I9" t="n">
+        <v>123.3816088222879</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.9237346579996</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.54680279413365</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 6.006x + -11963.916</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11963.91581649758</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.218083069425085e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>131.04</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000002113e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8171981026411727</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>255.1100000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.517799999999999e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.869</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1872782362963178</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7056324719965327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.598024832937826</v>
+      </c>
+      <c r="I10" t="n">
+        <v>163.1705869132753</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.20297201633247</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.9499842672588</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 5.642x + -11066.999</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11066.99855074649</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.743955955471329e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>128.0499999999997</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000013692e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8173849821701255</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>275.9199999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.52153e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6237956901773648</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.781425406388826</v>
+      </c>
+      <c r="H11" t="n">
+        <v>178.1658589114167</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.72517974260488</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17.75493996409865</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.19763229919931</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 5.788x + -11253.831</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11253.83144962725</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.620735479876497e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>116.73</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000040143e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8175983326854956</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>81.34705985591967</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 6.571x + -14531.524</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-14531.52379694545</v>
       </c>
       <c r="Y2" t="n">
         <v>4.205509400413091e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2652.816355383428</v>
+        <v>166.6599999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>82.06379504898048</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 7.173x + -15104.066</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15104.06592620119</v>
       </c>
       <c r="Y3" t="n">
         <v>9.926554895992382e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2535.796768424105</v>
+        <v>144.4099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>81.80798960018973</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.946x + -14320.865</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14320.8653249281</v>
       </c>
       <c r="Y4" t="n">
         <v>2.212245093627643e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2490.787529487453</v>
+        <v>141.6999999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>81.7535500828057</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.900x + -14041.210</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14041.20993973961</v>
       </c>
       <c r="Y5" t="n">
         <v>1.344720131362429e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2459.567312157532</v>
+        <v>139.6900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000005e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>81.77058638393777</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.914x + -13919.007</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13919.00672417357</v>
       </c>
       <c r="Y6" t="n">
         <v>1.664310027760281e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2432.208839873017</v>
+        <v>134.8400000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000011593e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>81.32543878358123</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.554x + -13022.089</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13022.08877226029</v>
       </c>
       <c r="Y7" t="n">
         <v>6.900498580002884e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2407.354759170283</v>
+        <v>135.7099999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000071e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>81.29900621639202</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.534x + -12856.937</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12856.93658707621</v>
       </c>
       <c r="Y8" t="n">
         <v>2.052043104068951e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2384.044821637456</v>
+        <v>134.7500000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000201779e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>81.35220862018741</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.575x + -12830.076</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12830.07555650289</v>
       </c>
       <c r="Y9" t="n">
         <v>8.649142491406476e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2362.751824886014</v>
+        <v>130.73</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000009025e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>80.95650726652701</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 6.283x + -12121.902</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12121.9023558993</v>
       </c>
       <c r="Y10" t="n">
         <v>4.908130286251949e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2343.211486301636</v>
+        <v>132.7800000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000067882e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>80.82040280242383</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 6.188x + -11836.707</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11836.7074318425</v>
       </c>
       <c r="Y11" t="n">
         <v>8.05937704701869e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2324.677621349778</v>
+        <v>131.72</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000013e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>81.28144585114816</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 6.521x + -12418.732</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12418.7318184145</v>
       </c>
       <c r="Y12" t="n">
         <v>1.571729883172873e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2306.326090182869</v>
+        <v>122.0999999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000152832e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>80.66582593562056</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 6.084x + -11455.128</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11455.12779674987</v>
       </c>
       <c r="Y13" t="n">
         <v>1.790366233193906e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>2288.712336173526</v>
+        <v>125.7800000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000099389e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>80.70512503046389</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 6.110x + -11419.886</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11419.88564399849</v>
       </c>
       <c r="Y14" t="n">
         <v>1.849710405073938e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2271.346971401868</v>
+        <v>127.1699999999998</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000002183e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>81.01223314878425</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 6.322x + -11759.363</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11759.36320920542</v>
       </c>
       <c r="Y15" t="n">
         <v>9.662643561047096e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2254.441781294051</v>
+        <v>116.73</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000001e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>80.66484607984803</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 6.083x + -11207.444</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11207.44381029402</v>
       </c>
       <c r="Y16" t="n">
         <v>4.025842568782027e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2237.358463198035</v>
+        <v>118.6300000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000327e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>80.5500727252478</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.008x + -10969.497</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10969.49693665093</v>
       </c>
       <c r="Y17" t="n">
         <v>3.506004375871525e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2218.544026680097</v>
+        <v>117.8799999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>80.31281421458912</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 5.858x + -10588.320</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10588.31972299025</v>
       </c>
       <c r="Y18" t="n">
         <v>3.106273292875994e-07</v>
       </c>
       <c r="Z18" t="n">
-        <v>2199.208638576296</v>
+        <v>121.3399999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000030748e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>80.02813702653556</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.688x + -10171.747</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10171.74663262239</v>
       </c>
       <c r="Y19" t="n">
         <v>8.419850187548451e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2179.368621787795</v>
+        <v>120.1699999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>79.44889331479698</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 5.369x + -9480.571</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9480.57087492682</v>
       </c>
       <c r="Y20" t="n">
         <v>1.047130096172059e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2160.272712394857</v>
+        <v>126.8699999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000263e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>79.91750698976013</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 5.624x + -9881.313</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9881.312596649015</v>
       </c>
       <c r="Y21" t="n">
         <v>9.687192281668998e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2140.873516812504</v>
+        <v>109.6699999999998</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000120302e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>79.26125899409929</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 5.273x + -9141.055</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9141.055117616663</v>
       </c>
       <c r="Y22" t="n">
         <v>1.264954517345809e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2120.860802679746</v>
+        <v>106.01</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>97.19999999999982</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.624929999999999e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.541</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2199663514713317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5430347125919821</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.559088863125198</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.859277521977673</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.371781080523672</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.16861795734711</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 6.436x + -14030.212</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-14030.21229415085</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.539789015139256e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>164.5500000000002</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8172228647327775</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>172.2999999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.5979e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2190206085376029</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8063177372918047</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.442064191158716</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.442142867555391</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.43477619218186</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 6.639x + -13842.957</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13842.95666542388</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.272677860425834e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>141.5900000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000063277e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8174399678725334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>201.47</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.58995e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.39700000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1882749671647599</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6417509285887323</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.011960917883008</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.202052621258274</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.27911746970352</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 6.519x + -13344.153</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13344.15301216381</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.053543146997756e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>136.98</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8175077489775567</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>223.8900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.586429999999999e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.54900000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3725479276760159</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5033974455550557</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.133273462211748</v>
+      </c>
+      <c r="I5" t="n">
+        <v>106.2929094236003</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.70292033046309</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.08890683592003</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 6.378x + -12883.510</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12883.50979965216</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.187792751825158e-07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>128.3600000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8175913762229218</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>237.5700000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.58898e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.67700000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5255914365273067</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8388112922987668</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.471447849005576</v>
+      </c>
+      <c r="I6" t="n">
+        <v>117.3699782833126</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.33176626959156</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80.94242132094284</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 6.273x + -12517.651</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12517.65074811471</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.148872642765337e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>126.4699999999998</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000021354e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8177127484635036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>243.9200000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.59227e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5263957367283191</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6994297570443527</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.374158659249447</v>
+      </c>
+      <c r="I7" t="n">
+        <v>38.83990851865718</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.04528357771289</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.66544031910878</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 6.084x + -11979.179</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11979.17933148436</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.544833179621391e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>124.8999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000011275e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8178621643413874</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>248.9699999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.594530000000001e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.88800000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1159678631247716</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.268364515548442</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.672799835271107</v>
+      </c>
+      <c r="I8" t="n">
+        <v>187.9770402029174</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12.66675223498165</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.33828804435977</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 5.874x + -11402.412</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11402.41242944528</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.479426259798415e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000386943e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8180559343544889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>267.0999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.5998e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5637077412034458</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.194641851154163</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.142102675327511</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16.26723134778424</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.14307853878834</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 5.755x + -11034.876</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11034.8764813468</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.567897819944889e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>114.77</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8182605588147898</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.60494e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.10599999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2047974902549611</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8174481656248804</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.023114955504484</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.87641558853618</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.73537743298156</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 5.522x + -10435.688</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10435.68750078583</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.581782967803718e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>119.3599999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000162e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.818483972974807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>263.45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.61057e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.18600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07314627817032779</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8182027167092857</v>
+      </c>
+      <c r="H11" t="n">
+        <v>108.4230324087155</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.117450240086721</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17.66604575329081</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.91863691543492</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 5.106x + -9489.317</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9489.317125955242</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.878165230200405e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>129.7199999999998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000086677e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8187105035549397</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>276.29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.61588e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.274</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09275825574913091</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.229632643733593</v>
+      </c>
+      <c r="H12" t="n">
+        <v>34.67232430408463</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.760114879320008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14.77705265714258</v>
+      </c>
+      <c r="K12" t="n">
+        <v>78.83031336632652</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 5.064x + -9310.968</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9310.967628059669</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.898394540780897e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>120.6400000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000043942e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8189553136926873</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>284.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.61873e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.36499999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2962648364452972</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9005835056790648</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.355019783095714</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.607634364717111</v>
+      </c>
+      <c r="K13" t="n">
+        <v>78.25862137758851</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 4.811x + -8720.505</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8720.504584108672</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.073144087203971e-11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>117.98</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8192201606935929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>290.9300000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.62606e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.444</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.06492433219232048</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.014310593005116</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.239716276678986</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.01935456888561009</v>
+      </c>
+      <c r="K14" t="n">
+        <v>77.51182730448956</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 4.515x + -8058.744</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8058.743922769041</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.525846042948044e-07</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>113.9400000000001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000005142e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8194724802478264</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>305.8699999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.63104e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.52200000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.0570368241408</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.227897346711024</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.285076205876169</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.80312841820791</v>
+      </c>
+      <c r="K15" t="n">
+        <v>75.80413585887663</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 3.953x + -6893.844</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-6893.843963403062</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.496748599831116e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>101.8300000000002</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8197406873615102</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>308.3600000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.632859999999999e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8189765562806439</v>
+      </c>
+      <c r="G16" t="n">
+        <v>218.4355551746952</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.482146482319791</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.169630458842067</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13.91899362428572</v>
+      </c>
+      <c r="K16" t="n">
+        <v>74.70374740596479</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 3.656x + -6260.119</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-6260.118745598808</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.809198738748828e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000023577e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8200099863063431</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>301.1500000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.638560000000001e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.67</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2092596657023919</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.893030789528475</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.750432008183268</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.902189719805582</v>
+      </c>
+      <c r="K17" t="n">
+        <v>75.59641130130557</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 3.894x + -6659.138</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-6659.137677013047</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.056410063579411e-07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000104934e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8202854958693423</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>316.3700000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.642870000000001e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.73999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4349214832108929</v>
+      </c>
+      <c r="G18" t="n">
+        <v>200.7162704063553</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.310032999613516</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.163314272649033</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.80518441346568</v>
+      </c>
+      <c r="K18" t="n">
+        <v>71.97983678564529</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 3.074x + -5059.278</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-5059.27801755262</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.12674484447922e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000056875e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8205908934782528</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>319.3099999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.645660000000001e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.81999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3701394717652773</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.335929102145418</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.004489859244035</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>71.96496809531085</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 3.071x + -5013.089</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-5013.089439330403</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.406894532279455e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>102.3600000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000017028e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8208824224879117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>316.3399999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.64629e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.883</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3223559499627363</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.898546098295892</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.56112116579276</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>71.66015199783415</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 3.017x + -4872.549</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-4872.548960438281</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.05216978310343e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>107.6700000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8211788291260644</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>329.8100000000002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.64984e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="F21" t="n">
+        <v>121.3816997576813</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7126119870318681</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.64866864389906</v>
+      </c>
+      <c r="I21" t="n">
+        <v>39.14406202042679</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21.41592926820701</v>
+      </c>
+      <c r="K21" t="n">
+        <v>66.96628715035813</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 2.352x + -3613.794</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-3613.793524151322</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.736925042440009e-07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>102.0899999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000390443e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.82146872071185</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.652589999999999e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.023</v>
+      </c>
+      <c r="F22" t="n">
+        <v>171.0113492104345</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7416526651963362</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.823918039892177</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.660707813994264</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>66.90489445212472</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 2.345x + -3575.397</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-3575.396579701583</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.881813102626941e-07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>103.53</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000004022e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.821758690607435</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>88.09430783337544</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 30.055x + -78760.157</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-78760.15730880057</v>
       </c>
       <c r="Y2" t="n">
         <v>1.786831553088973e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>3011.390085308609</v>
+        <v>353.1399999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000232958e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>84.09575976678013</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.670x + -21089.865</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-21089.8647949108</v>
       </c>
       <c r="Y3" t="n">
         <v>1.233518091867686e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2717.953516990817</v>
+        <v>154.3499999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001024e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>81.88686765536133</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 7.015x + -15220.715</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15220.71470400804</v>
       </c>
       <c r="Y4" t="n">
         <v>9.434306613700836e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2640.42276538133</v>
+        <v>148.0599999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000028616e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>82.12892926366001</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 7.233x + -15445.573</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15445.57309959872</v>
       </c>
       <c r="Y5" t="n">
         <v>2.711065944226108e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>2592.826133116453</v>
+        <v>135</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000041606e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>81.41976774629789</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.628x + -13852.937</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13852.93701736268</v>
       </c>
       <c r="Y6" t="n">
         <v>4.807054464653887e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2551.09613769508</v>
+        <v>139.8099999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000016451e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>81.17035524019785</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.438x + -13236.676</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13236.67640537149</v>
       </c>
       <c r="Y7" t="n">
         <v>8.612455610070082e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2512.0231756733</v>
+        <v>132.02</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000107133e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>80.75572285552995</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.144x + -12411.653</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12411.65283345398</v>
       </c>
       <c r="Y8" t="n">
         <v>3.679975798242193e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>2475.294392573575</v>
+        <v>134.96</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000904e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>80.57165800571153</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.022x + -11990.813</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11990.81323150786</v>
       </c>
       <c r="Y9" t="n">
         <v>5.294722738196046e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2440.997626481409</v>
+        <v>131.02</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000016248e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>79.89208914264633</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.609x + -10973.140</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10973.14047150493</v>
       </c>
       <c r="Y10" t="n">
         <v>2.160217842635149e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2409.05635538728</v>
+        <v>132.9299999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000025692e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>80.04006496451282</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.695x + -11021.412</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11021.41217326432</v>
       </c>
       <c r="Y11" t="n">
         <v>1.799878448228988e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2379.12308594633</v>
+        <v>123.8399999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000042e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>-85.82040409444005</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = -13.684x + 33683.172</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>33683.17202914214</v>
       </c>
       <c r="Y2" t="n">
         <v>4.001697785037651e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2674.284493773773</v>
+        <v>159.46</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000008e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>81.46238613246548</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 6.661x + -13909.111</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13909.11086847288</v>
       </c>
       <c r="Y3" t="n">
         <v>2.527194843870823e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2543.438231911937</v>
+        <v>143.0599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>81.73056589589275</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.880x + -14127.828</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14127.82846524425</v>
       </c>
       <c r="Y4" t="n">
         <v>7.73755727272483e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2498.320323195103</v>
+        <v>127.7799999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>80.77018552246251</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.154x + -12395.112</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12395.1122341742</v>
       </c>
       <c r="Y5" t="n">
         <v>2.417716927405043e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>2468.881075696555</v>
+        <v>135.3900000000003</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000226e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>80.73905095853198</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.133x + -12233.196</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12233.19593743782</v>
       </c>
       <c r="Y6" t="n">
         <v>2.771905265476392e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2444.66050228381</v>
+        <v>131.6100000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004754e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>80.42384485326912</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.927x + -11690.927</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11690.92654999617</v>
       </c>
       <c r="Y7" t="n">
         <v>1.054545805753066e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2422.261225547426</v>
+        <v>132.6300000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018646e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>80.24359187525593</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 5.816x + -11359.064</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11359.06371320082</v>
       </c>
       <c r="Y8" t="n">
         <v>2.967864930265573e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2401.760521299128</v>
+        <v>129.98</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001124e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>80.22458941476644</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 5.804x + -11257.414</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11257.41373524666</v>
       </c>
       <c r="Y9" t="n">
         <v>4.151262931802478e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2382.859112404922</v>
+        <v>119.4300000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000081e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>79.97780457130467</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.658x + -10869.387</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10869.38676452248</v>
       </c>
       <c r="Y10" t="n">
         <v>9.276352370959234e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2364.158321890183</v>
+        <v>121.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>79.71579786482299</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.511x + -10490.285</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10490.28538429595</v>
       </c>
       <c r="Y11" t="n">
         <v>1.213274958644838e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>2346.350680881624</v>
+        <v>116.0600000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000037979e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>79.30153815519702</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 5.293x + -9976.290</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9976.289598617124</v>
       </c>
       <c r="Y12" t="n">
         <v>1.285735264623511e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>2328.743438180887</v>
+        <v>117.1500000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000062752e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>79.22364525887699</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 5.254x + -9821.919</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9821.918907996078</v>
       </c>
       <c r="Y13" t="n">
         <v>5.501943032585831e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2311.154004215749</v>
+        <v>118.6899999999998</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000003e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>78.61445943814785</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 4.966x + -9178.377</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9178.377094020414</v>
       </c>
       <c r="Y14" t="n">
         <v>1.082177876915714e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2294.221169055784</v>
+        <v>111.8000000000002</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000020636e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>78.30266259639752</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 4.830x + -8839.225</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8839.225052122372</v>
       </c>
       <c r="Y15" t="n">
         <v>1.708787579501874e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2276.695625055484</v>
+        <v>123.1000000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000275e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>77.5568465763868</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 4.532x + -8187.162</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8187.16246258248</v>
       </c>
       <c r="Y16" t="n">
         <v>3.867870865145007e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2259.213562200337</v>
+        <v>110.3799999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.00000000000057e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>76.80255617255989</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 4.264x + -7598.949</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7598.949092311984</v>
       </c>
       <c r="Y17" t="n">
         <v>6.6082566251541e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2240.449683571833</v>
+        <v>106.3900000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>76.08746304544461</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 4.037x + -7095.700</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7095.70000561196</v>
       </c>
       <c r="Y18" t="n">
         <v>2.582652997610923e-07</v>
       </c>
       <c r="Z18" t="n">
-        <v>2221.403972757881</v>
+        <v>107.0999999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000073e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>74.42830302001586</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 3.588x + -6174.368</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-6174.36839395098</v>
       </c>
       <c r="Y19" t="n">
         <v>2.218837313543849e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2201.693149781671</v>
+        <v>102.9400000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>75.7245552548771</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 3.930x + -6777.427</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6777.427021364794</v>
       </c>
       <c r="Y20" t="n">
         <v>1.369674985823065e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2182.224619966437</v>
+        <v>111.5200000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>71.47192935793714</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 2.984x + -4924.698</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-4924.697935117063</v>
       </c>
       <c r="Y21" t="n">
         <v>2.751548373145456e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2162.633245764146</v>
+        <v>100.4000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000292301e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>74.51123344201001</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 3.609x + -6064.797</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-6064.797403531207</v>
       </c>
       <c r="Y22" t="n">
         <v>2.608922912703149e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>2142.888228635001</v>
+        <v>116.1900000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>87.96324123033871</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 28.119x + -71616.065</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-71616.06502077462</v>
       </c>
       <c r="Y2" t="n">
         <v>2.117751497835266e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2936.677572140641</v>
+        <v>468.4699999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000012968e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>87.13931916918921</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 20.012x + -45061.820</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-45061.81952303981</v>
       </c>
       <c r="Y3" t="n">
         <v>1.958086466774596e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2692.242874545106</v>
+        <v>163.54</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000014577e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>81.88833678925752</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 7.016x + -15106.113</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15106.11296741202</v>
       </c>
       <c r="Y4" t="n">
         <v>1.247089447767962e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2618.150634152249</v>
+        <v>146.96</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000153e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>81.39979066064795</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.612x + -13932.589</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13932.58900800227</v>
       </c>
       <c r="Y5" t="n">
         <v>3.635158269243158e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>2572.52477865014</v>
+        <v>149.8600000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000034e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>81.43435707413214</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.639x + -13786.633</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13786.63331417237</v>
       </c>
       <c r="Y6" t="n">
         <v>4.416893742440481e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2533.289867695818</v>
+        <v>137.5100000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000174e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>81.6869081072623</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.844x + -14050.344</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14050.34403228993</v>
       </c>
       <c r="Y7" t="n">
         <v>1.678018887649372e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2495.576749485846</v>
+        <v>126.6100000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001539e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>80.52929401056504</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 5.995x + -12026.518</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12026.51762871698</v>
       </c>
       <c r="Y8" t="n">
         <v>3.064094262318908e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2459.577970474297</v>
+        <v>136.8600000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>80.56663963579884</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.019x + -11913.143</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11913.14283832148</v>
       </c>
       <c r="Y9" t="n">
         <v>7.39092983260449e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2424.696558775766</v>
+        <v>136.47</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000007224e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>80.45632785736454</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.948x + -11610.493</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11610.49288341105</v>
       </c>
       <c r="Y10" t="n">
         <v>2.211950006983975e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2392.166845779026</v>
+        <v>129.9399999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000021e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>80.50804722548756</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.981x + -11537.817</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11537.81654469432</v>
       </c>
       <c r="Y11" t="n">
         <v>2.579255153750097e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2361.411093080482</v>
+        <v>121.9299999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000105e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>87.09007767888573</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 19.673x + -44562.783</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-44562.78278374775</v>
       </c>
       <c r="Y2" t="n">
         <v>8.402656826550151e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2685.379793263403</v>
+        <v>173.4499999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000025999e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>81.84538930699718</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 6.979x + -14698.110</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14698.11016432498</v>
       </c>
       <c r="Y3" t="n">
         <v>7.230863358269388e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2556.398313011775</v>
+        <v>142.27</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000461458e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>81.69939753094116</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.854x + -14157.445</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14157.44454605444</v>
       </c>
       <c r="Y4" t="n">
         <v>2.793223466398135e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2512.416219146788</v>
+        <v>132.4899999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000101e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>81.33003173151414</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.558x + -13346.764</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13346.76369863253</v>
       </c>
       <c r="Y5" t="n">
         <v>1.160967592451774e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2482.432594083486</v>
+        <v>134.4500000000003</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000055893e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>81.23911844931203</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.489x + -13058.470</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13058.46990651315</v>
       </c>
       <c r="Y6" t="n">
         <v>3.488412954610819e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2456.274889146551</v>
+        <v>131.4500000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>80.60546996201529</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.044x + -11989.416</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11989.41641045902</v>
       </c>
       <c r="Y7" t="n">
         <v>1.680785128129256e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2431.055510540169</v>
+        <v>134.01</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000118768e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>81.02813574746196</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.334x + -12487.465</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12487.46503069001</v>
       </c>
       <c r="Y8" t="n">
         <v>2.275129944872111e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>2407.007506266758</v>
+        <v>125.3000000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.0000000000002e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>80.65532393194952</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.077x + -11839.364</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11839.36444176706</v>
       </c>
       <c r="Y9" t="n">
         <v>4.338815598007196e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2383.483686951633</v>
+        <v>123.8500000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000079e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>80.60168176755981</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 6.042x + -11661.338</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11661.33753679387</v>
       </c>
       <c r="Y10" t="n">
         <v>1.146485842324968e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2361.323694518063</v>
+        <v>122.5000000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>79.95085488340752</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.643x + -10739.335</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10739.33531980895</v>
       </c>
       <c r="Y11" t="n">
         <v>2.095200877837401e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2339.502033475297</v>
+        <v>128.79</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000026e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>79.96308992866611</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 5.650x + -10669.779</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10669.77870015526</v>
       </c>
       <c r="Y12" t="n">
         <v>9.424735591807638e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2318.517083546198</v>
+        <v>111.3300000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000043376e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>79.46950916523271</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 5.380x + -10029.733</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10029.73288370191</v>
       </c>
       <c r="Y13" t="n">
         <v>3.804969955157933e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>2297.534806654126</v>
+        <v>125.3299999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000059e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>79.31465910136225</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 5.300x + -9788.442</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9788.442375689649</v>
       </c>
       <c r="Y14" t="n">
         <v>2.747167029613001e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2277.033258264069</v>
+        <v>112</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000099e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>78.85400274089908</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 5.075x + -9265.581</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9265.580539951061</v>
       </c>
       <c r="Y15" t="n">
         <v>4.505443976199296e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2256.68389540495</v>
+        <v>116.1299999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000001436e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>78.36099238823104</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 4.855x + -8755.208</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8755.207892042818</v>
       </c>
       <c r="Y16" t="n">
         <v>3.171452398963669e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2237.076718461622</v>
+        <v>118.8</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000634e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>78.17445881809338</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 4.776x + -8527.548</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8527.547761122863</v>
       </c>
       <c r="Y17" t="n">
         <v>1.623683741287399e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>2217.190969365798</v>
+        <v>121.8899999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000005e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>77.64146237975108</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 4.564x + -8047.945</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8047.945031695579</v>
       </c>
       <c r="Y18" t="n">
         <v>6.027216755665779e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2197.636825311049</v>
+        <v>114.6599999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000001e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>76.52796988685211</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 4.174x + -7235.633</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7235.633427636122</v>
       </c>
       <c r="Y19" t="n">
         <v>9.143263996301135e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2178.145451127642</v>
+        <v>107.78</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000001557e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>75.90669352731483</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 3.983x + -6817.737</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6817.736554585192</v>
       </c>
       <c r="Y20" t="n">
         <v>2.118932855856586e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2158.628595517052</v>
+        <v>107.2700000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000026e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>75.45103271350774</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 3.853x + -6511.877</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-6511.877174778572</v>
       </c>
       <c r="Y21" t="n">
         <v>1.233822405465896e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2139.201116971368</v>
+        <v>108.1199999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>75.66571386144132</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 3.913x + -6573.575</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-6573.57496791219</v>
       </c>
       <c r="Y22" t="n">
         <v>1.555134227633539e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2119.861688745518</v>
+        <v>117.5500000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>87.51033630518397</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 22.999x + -53974.720</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-53974.71950945709</v>
       </c>
       <c r="Y2" t="n">
         <v>1.251675918735745e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2722.482513789381</v>
+        <v>614.54</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000017296e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>86.74904427002542</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.605x + -37551.050</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-37551.0497807443</v>
       </c>
       <c r="Y3" t="n">
         <v>3.754931479180862e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2559.186523764559</v>
+        <v>147.1199999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000242e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>81.9062215115754</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 7.032x + -14514.852</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14514.85180401859</v>
       </c>
       <c r="Y4" t="n">
         <v>5.105581795386281e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2502.965694501199</v>
+        <v>134.8899999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000528e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>81.49194910206108</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.685x + -13542.283</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13542.28276559242</v>
       </c>
       <c r="Y5" t="n">
         <v>2.840245649741695e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2463.981582635214</v>
+        <v>135.8600000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>80.99987116188733</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.314x + -12568.921</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12568.92099399804</v>
       </c>
       <c r="Y6" t="n">
         <v>3.387716667712425e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2429.137587880458</v>
+        <v>133.0700000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>80.60684936062036</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.045x + -11845.224</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11845.22419483523</v>
       </c>
       <c r="Y7" t="n">
         <v>2.180917416166401e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2394.527931064527</v>
+        <v>134.6600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000134e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>80.41532819728054</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 5.922x + -11434.391</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11434.39076983167</v>
       </c>
       <c r="Y8" t="n">
         <v>6.053913792970128e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2361.365768513816</v>
+        <v>128.0400000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000253e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>80.35126635696295</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 5.882x + -11204.705</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11204.7051286297</v>
       </c>
       <c r="Y9" t="n">
         <v>4.541374099500187e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2329.457937274167</v>
+        <v>126.5100000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000164e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>80.34649884336676</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.879x + -11062.347</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11062.34664654996</v>
       </c>
       <c r="Y10" t="n">
         <v>9.912619760139729e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2298.439170782339</v>
+        <v>114.76</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000010019e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>79.96284655099919</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.650x + -10468.778</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10468.77814691912</v>
       </c>
       <c r="Y11" t="n">
         <v>1.186783077225627e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>2269.055220485489</v>
+        <v>116.54</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000006196e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>88.03838653368703</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 29.197x + -67463.805</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-67463.80481688313</v>
       </c>
       <c r="Y2" t="n">
         <v>1.183145902954188e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2686.390486970981</v>
+        <v>412.6400000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000018286e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>81.87646600769138</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 7.006x + -14814.851</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14814.85070680051</v>
       </c>
       <c r="Y3" t="n">
         <v>1.111474521042406e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2560.684989515539</v>
+        <v>145.29</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000013943e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>81.50581769194375</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.696x + -13853.593</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13853.59290068857</v>
       </c>
       <c r="Y4" t="n">
         <v>1.71941888220926e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2516.113398311693</v>
+        <v>144.0599999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001757e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>81.75069506449455</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.897x + -14143.722</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14143.72172759192</v>
       </c>
       <c r="Y5" t="n">
         <v>4.457389973645242e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2487.330254789892</v>
+        <v>131.4100000000003</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000577437e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>81.92128411004097</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 7.045x + -14321.883</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14321.88272867534</v>
       </c>
       <c r="Y6" t="n">
         <v>5.031497483976484e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2461.543711295295</v>
+        <v>123.25</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000019187e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>80.68534012519825</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 6.097x + -12160.611</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12160.6112450819</v>
       </c>
       <c r="Y7" t="n">
         <v>3.727864788294048e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2436.832044872622</v>
+        <v>137.8900000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003428e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>81.57974651930112</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.755x + -13435.873</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13435.87290284801</v>
       </c>
       <c r="Y8" t="n">
         <v>9.367192601541056e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2412.822244999396</v>
+        <v>121.1900000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000013e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>80.97047297236134</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.293x + -12348.745</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12348.74472933945</v>
       </c>
       <c r="Y9" t="n">
         <v>1.054996948110553e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>2389.72479508471</v>
+        <v>126.49</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000046243e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>80.91333530017002</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 6.253x + -12155.257</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12155.25681238084</v>
       </c>
       <c r="Y10" t="n">
         <v>1.024568131383995e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>2367.4116501242</v>
+        <v>121.6800000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000006e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>80.78016904878108</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 6.161x + -11858.280</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11858.280242979</v>
       </c>
       <c r="Y11" t="n">
         <v>1.314009031061219e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>2345.958731469249</v>
+        <v>119.3899999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000032e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>80.2745815969581</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 5.835x + -11095.677</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11095.67692918065</v>
       </c>
       <c r="Y12" t="n">
         <v>6.97857171440006e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2325.072926922543</v>
+        <v>125.7099999999998</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000060638e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>80.47932636684661</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 5.963x + -11261.543</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11261.54318003224</v>
       </c>
       <c r="Y13" t="n">
         <v>1.705364797175104e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2304.474133319054</v>
+        <v>112.8399999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000004977e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>80.08510871185089</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 5.721x + -10684.111</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10684.11138840195</v>
       </c>
       <c r="Y14" t="n">
         <v>1.029102557085396e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>2284.753928592743</v>
+        <v>119.0899999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000340535e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>80.16381530960258</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 5.768x + -10690.681</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10690.68072800848</v>
       </c>
       <c r="Y15" t="n">
         <v>4.666552701910998e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>2265.661450334293</v>
+        <v>114.3799999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000002183e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>79.82965826704286</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 5.574x + -10226.307</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10226.30673371317</v>
       </c>
       <c r="Y16" t="n">
         <v>4.761022622635242e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2246.900968461987</v>
+        <v>112.29</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000041311e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>79.51745299937818</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 5.405x + -9811.821</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9811.820734313953</v>
       </c>
       <c r="Y17" t="n">
         <v>8.314017394173889e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2227.580480675245</v>
+        <v>109.5599999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>78.85770683064864</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 5.077x + -9094.208</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9094.208120553181</v>
       </c>
       <c r="Y18" t="n">
         <v>8.099807657802709e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2207.892732821187</v>
+        <v>121.8299999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002956e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>78.41101124211923</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 4.876x + -8631.513</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8631.513384457108</v>
       </c>
       <c r="Y19" t="n">
         <v>2.073916530529249e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2188.466599121697</v>
+        <v>103.1299999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>77.78010210306275</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 4.617x + -8066.440</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8066.439876583923</v>
       </c>
       <c r="Y20" t="n">
         <v>4.222547217124628e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>2169.165781966564</v>
+        <v>101.1600000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000011e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>77.66151198302688</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 4.572x + -7918.459</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7918.459157029197</v>
       </c>
       <c r="Y21" t="n">
         <v>3.444047766692636e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>2150.050766356738</v>
+        <v>112.04</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000037755e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>77.64911761277996</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 4.567x + -7840.942</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7840.941613102235</v>
       </c>
       <c r="Y22" t="n">
         <v>1.738667450564676e-07</v>
       </c>
       <c r="Z22" t="n">
-        <v>2131.369482436101</v>
+        <v>109.8099999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000109218e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>87.96484616691941</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 28.141x + -57740.795</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-57740.79517774256</v>
       </c>
       <c r="Y2" t="n">
         <v>2.051247856185267e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>2294.017082802051</v>
+        <v>440.5800000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000007539e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>-69.91631284645814</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = -2.735x + 6209.595</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>6209.594969437313</v>
       </c>
       <c r="Y3" t="n">
         <v>1.712457392977619e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2051.599275085305</v>
+        <v>128.6400000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000011e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>80.92446931233515</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.260x + -10347.037</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10347.03658303436</v>
       </c>
       <c r="Y4" t="n">
         <v>1.080458273433676e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1991.722397896727</v>
+        <v>119.6400000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000001464e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>80.9611350739129</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.286x + -10223.294</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10223.29399243064</v>
       </c>
       <c r="Y5" t="n">
         <v>3.410662971559168e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1957.402345524185</v>
+        <v>107.98</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002396e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>80.12736363966729</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 5.746x + -9147.922</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9147.921927695401</v>
       </c>
       <c r="Y6" t="n">
         <v>1.912706237936999e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>1927.861782576359</v>
+        <v>116.1899999999998</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>79.92610058583583</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.629x + -8826.233</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8826.232647253944</v>
       </c>
       <c r="Y7" t="n">
         <v>952.8512276116016</v>
       </c>
       <c r="Z7" t="n">
-        <v>1779851100.575519</v>
+        <v>114.1600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>4.231634030276023e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>80.06301893464592</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 5.708x + -8838.228</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8838.227600150214</v>
       </c>
       <c r="Y8" t="n">
         <v>910.5175082169267</v>
       </c>
       <c r="Z8" t="n">
-        <v>273617289.6517155</v>
+        <v>101.01</v>
       </c>
       <c r="AA8" t="n">
         <v>6.584274685941277e-07</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>79.41383595310127</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 5.351x + -8135.038</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8135.038187212838</v>
       </c>
       <c r="Y9" t="n">
         <v>906.7673291276271</v>
       </c>
       <c r="Z9" t="n">
-        <v>232468487.862025</v>
+        <v>104.28</v>
       </c>
       <c r="AA9" t="n">
         <v>6.099039348884555e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>79.05683543241226</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.172x + -7742.104</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7742.103527652958</v>
       </c>
       <c r="Y10" t="n">
         <v>947.4125643243673</v>
       </c>
       <c r="Z10" t="n">
-        <v>702965445.5312467</v>
+        <v>97.11000000000013</v>
       </c>
       <c r="AA10" t="n">
         <v>3.240243778522406e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>78.98136727189252</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.136x + -7586.702</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7586.701877014153</v>
       </c>
       <c r="Y11" t="n">
         <v>943.3992148990433</v>
       </c>
       <c r="Z11" t="n">
-        <v>631947814.5222821</v>
+        <v>100.23</v>
       </c>
       <c r="AA11" t="n">
         <v>3.062665850609764e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>81.60782704804083</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.778x + -15727.235</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.778394084486807</v>
       </c>
       <c r="X2" t="n">
         <v>-15727.23503409055</v>
@@ -600,7 +598,7 @@
         <v>1.080632580052182e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.6199999999999</v>
+        <v>2802.239453311308</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003123e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>81.14125697098204</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 6.416x + -13996.824</t>
-        </is>
+      <c r="W3" t="n">
+        <v>6.416089444416845</v>
       </c>
       <c r="X3" t="n">
         <v>-13996.82426852906</v>
@@ -652,7 +648,7 @@
         <v>6.950350282412593e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>159.9200000000001</v>
+        <v>2667.026421529901</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001598e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>81.73160861482086</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.881x + -14736.302</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.881324863281834</v>
       </c>
       <c r="X4" t="n">
         <v>-14736.30205345171</v>
@@ -704,7 +698,7 @@
         <v>2.904923746523607e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>140.75</v>
+        <v>2610.015283176012</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000101e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>81.25908569877066</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.504x + -13664.003</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.503963809243431</v>
       </c>
       <c r="X5" t="n">
         <v>-13664.00322933267</v>
@@ -756,7 +748,7 @@
         <v>3.851785725360481e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>141.4000000000001</v>
+        <v>2570.230175119998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001147e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>81.58407020134409</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.759x + -14055.146</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.75898291607694</v>
       </c>
       <c r="X6" t="n">
         <v>-14055.14574340741</v>
@@ -808,7 +798,7 @@
         <v>3.394637800844841e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>128.3400000000001</v>
+        <v>2536.645633999365</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>80.82287179736515</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.190x + -12645.772</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.189841522509957</v>
       </c>
       <c r="X7" t="n">
         <v>-12645.77171301273</v>
@@ -860,7 +848,7 @@
         <v>4.537950428802318e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>134.6100000000001</v>
+        <v>2504.78040946881</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>80.77470821132474</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.157x + -12428.947</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.156964600332436</v>
       </c>
       <c r="X8" t="n">
         <v>-12428.94669676615</v>
@@ -912,7 +898,7 @@
         <v>3.424484845822161e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>130.1299999999997</v>
+        <v>2474.504905996447</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000022107e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>80.54680279413365</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.006x + -11963.916</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.005898305563314</v>
       </c>
       <c r="X9" t="n">
         <v>-11963.91581649758</v>
@@ -964,7 +948,7 @@
         <v>1.218083069425085e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>131.04</v>
+        <v>2445.117948601374</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002113e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>79.9499842672588</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.642x + -11066.999</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.642474761899186</v>
       </c>
       <c r="X10" t="n">
         <v>-11066.99855074649</v>
@@ -1016,7 +998,7 @@
         <v>3.743955955471329e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>128.0499999999997</v>
+        <v>2416.910632523549</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000013692e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>80.19763229919931</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.788x + -11253.831</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.787956472433362</v>
       </c>
       <c r="X11" t="n">
         <v>-11253.83144962725</v>
@@ -1068,7 +1048,7 @@
         <v>5.620735479876497e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>116.73</v>
+        <v>2389.6198397595</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000040143e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>81.34705985591967</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.571x + -14531.524</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.571121395343384</v>
       </c>
       <c r="X2" t="n">
         <v>-14531.52379694545</v>
@@ -1266,7 +1244,7 @@
         <v>4.205509400413091e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>166.6599999999999</v>
+        <v>2652.816355383428</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>82.06379504898048</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 7.173x + -15104.066</t>
-        </is>
+      <c r="W3" t="n">
+        <v>7.173313701032324</v>
       </c>
       <c r="X3" t="n">
         <v>-15104.06592620119</v>
@@ -1318,7 +1294,7 @@
         <v>9.926554895992382e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>144.4099999999999</v>
+        <v>2535.796768424105</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>81.80798960018973</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.946x + -14320.865</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.946380567912005</v>
       </c>
       <c r="X4" t="n">
         <v>-14320.8653249281</v>
@@ -1370,7 +1344,7 @@
         <v>2.212245093627643e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>141.6999999999998</v>
+        <v>2490.787529487453</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>81.7535500828057</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.900x + -14041.210</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.89989047036303</v>
       </c>
       <c r="X5" t="n">
         <v>-14041.20993973961</v>
@@ -1422,7 +1394,7 @@
         <v>1.344720131362429e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>139.6900000000001</v>
+        <v>2459.567312157532</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000005e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>81.77058638393777</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.914x + -13919.007</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.914373410095767</v>
       </c>
       <c r="X6" t="n">
         <v>-13919.00672417357</v>
@@ -1474,7 +1444,7 @@
         <v>1.664310027760281e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>134.8400000000001</v>
+        <v>2432.208839873017</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000011593e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>81.32543878358123</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.554x + -13022.089</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.554491053336548</v>
       </c>
       <c r="X7" t="n">
         <v>-13022.08877226029</v>
@@ -1526,7 +1494,7 @@
         <v>6.900498580002884e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>135.7099999999998</v>
+        <v>2407.354759170283</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000071e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>81.29900621639202</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.534x + -12856.937</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.53427126770334</v>
       </c>
       <c r="X8" t="n">
         <v>-12856.93658707621</v>
@@ -1578,7 +1544,7 @@
         <v>2.052043104068951e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>134.7500000000002</v>
+        <v>2384.044821637456</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000201779e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>81.35220862018741</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.575x + -12830.076</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.575093850844786</v>
       </c>
       <c r="X9" t="n">
         <v>-12830.07555650289</v>
@@ -1630,7 +1594,7 @@
         <v>8.649142491406476e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>130.73</v>
+        <v>2362.751824886014</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000009025e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>80.95650726652701</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 6.283x + -12121.902</t>
-        </is>
+      <c r="W10" t="n">
+        <v>6.282880365670981</v>
       </c>
       <c r="X10" t="n">
         <v>-12121.9023558993</v>
@@ -1682,7 +1644,7 @@
         <v>4.908130286251949e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>132.7800000000002</v>
+        <v>2343.211486301636</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000067882e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>80.82040280242383</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 6.188x + -11836.707</t>
-        </is>
+      <c r="W11" t="n">
+        <v>6.188147845855583</v>
       </c>
       <c r="X11" t="n">
         <v>-11836.7074318425</v>
@@ -1734,7 +1694,7 @@
         <v>8.05937704701869e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>131.72</v>
+        <v>2324.677621349778</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000013e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>81.28144585114816</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 6.521x + -12418.732</t>
-        </is>
+      <c r="W12" t="n">
+        <v>6.520905598763334</v>
       </c>
       <c r="X12" t="n">
         <v>-12418.7318184145</v>
@@ -1786,7 +1744,7 @@
         <v>1.571729883172873e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>122.0999999999999</v>
+        <v>2306.326090182869</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000152832e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>80.66582593562056</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 6.084x + -11455.128</t>
-        </is>
+      <c r="W13" t="n">
+        <v>6.083880243086495</v>
       </c>
       <c r="X13" t="n">
         <v>-11455.12779674987</v>
@@ -1838,7 +1794,7 @@
         <v>1.790366233193906e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>125.7800000000002</v>
+        <v>2288.712336173526</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000099389e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>80.70512503046389</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 6.110x + -11419.886</t>
-        </is>
+      <c r="W14" t="n">
+        <v>6.110062979920581</v>
       </c>
       <c r="X14" t="n">
         <v>-11419.88564399849</v>
@@ -1890,7 +1844,7 @@
         <v>1.849710405073938e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>127.1699999999998</v>
+        <v>2271.346971401868</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000002183e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>81.01223314878425</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 6.322x + -11759.363</t>
-        </is>
+      <c r="W15" t="n">
+        <v>6.322487996767297</v>
       </c>
       <c r="X15" t="n">
         <v>-11759.36320920542</v>
@@ -1942,7 +1894,7 @@
         <v>9.662643561047096e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>116.73</v>
+        <v>2254.441781294051</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000001e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>80.66484607984803</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.083x + -11207.444</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.083230213197538</v>
       </c>
       <c r="X16" t="n">
         <v>-11207.44381029402</v>
@@ -1994,7 +1944,7 @@
         <v>4.025842568782027e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>118.6300000000001</v>
+        <v>2237.358463198035</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000327e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>80.5500727252478</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.008x + -10969.497</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.008014701821815</v>
       </c>
       <c r="X17" t="n">
         <v>-10969.49693665093</v>
@@ -2046,7 +1994,7 @@
         <v>3.506004375871525e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>117.8799999999999</v>
+        <v>2218.544026680097</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>80.31281421458912</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 5.858x + -10588.320</t>
-        </is>
+      <c r="W18" t="n">
+        <v>5.858129429053886</v>
       </c>
       <c r="X18" t="n">
         <v>-10588.31972299025</v>
@@ -2098,7 +2044,7 @@
         <v>3.106273292875994e-07</v>
       </c>
       <c r="Z18" t="n">
-        <v>121.3399999999999</v>
+        <v>2199.208638576296</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000030748e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>80.02813702653556</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.688x + -10171.747</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.687613330801211</v>
       </c>
       <c r="X19" t="n">
         <v>-10171.74663262239</v>
@@ -2150,7 +2094,7 @@
         <v>8.419850187548451e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>120.1699999999998</v>
+        <v>2179.368621787795</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>79.44889331479698</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 5.369x + -9480.571</t>
-        </is>
+      <c r="W20" t="n">
+        <v>5.368786864273599</v>
       </c>
       <c r="X20" t="n">
         <v>-9480.57087492682</v>
@@ -2202,7 +2144,7 @@
         <v>1.047130096172059e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>126.8699999999999</v>
+        <v>2160.272712394857</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000263e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>79.91750698976013</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 5.624x + -9881.313</t>
-        </is>
+      <c r="W21" t="n">
+        <v>5.623920632195568</v>
       </c>
       <c r="X21" t="n">
         <v>-9881.312596649015</v>
@@ -2254,7 +2194,7 @@
         <v>9.687192281668998e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>109.6699999999998</v>
+        <v>2140.873516812504</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000120302e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>79.26125899409929</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 5.273x + -9141.055</t>
-        </is>
+      <c r="W22" t="n">
+        <v>5.272805740264764</v>
       </c>
       <c r="X22" t="n">
         <v>-9141.055117616663</v>
@@ -2306,7 +2244,7 @@
         <v>1.264954517345809e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>106.01</v>
+        <v>2120.860802679746</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>81.16861795734711</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.436x + -14030.212</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.436287350390533</v>
       </c>
       <c r="X2" t="n">
         <v>-14030.21229415085</v>
@@ -2504,7 +2440,7 @@
         <v>8.539789015139256e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>164.5500000000002</v>
+        <v>2645.4919457626</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>81.43477619218186</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 6.639x + -13842.957</t>
-        </is>
+      <c r="W3" t="n">
+        <v>6.639445107112255</v>
       </c>
       <c r="X3" t="n">
         <v>-13842.95666542388</v>
@@ -2556,7 +2490,7 @@
         <v>3.272677860425834e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>141.5900000000001</v>
+        <v>2543.218713457283</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000063277e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>81.27911746970352</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.519x + -13344.153</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.519137415136154</v>
       </c>
       <c r="X4" t="n">
         <v>-13344.15301216381</v>
@@ -2608,7 +2540,7 @@
         <v>3.053543146997756e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>136.98</v>
+        <v>2501.368026914175</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000022e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>81.08890683592003</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.378x + -12883.510</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.377787459526253</v>
       </c>
       <c r="X5" t="n">
         <v>-12883.50979965216</v>
@@ -2660,7 +2590,7 @@
         <v>3.187792751825158e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>128.3600000000001</v>
+        <v>2471.099133070812</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000182e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>80.94242132094284</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.273x + -12517.651</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.272945191355327</v>
       </c>
       <c r="X6" t="n">
         <v>-12517.65074811471</v>
@@ -2712,7 +2640,7 @@
         <v>1.148872642765337e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>126.4699999999998</v>
+        <v>2441.483833096495</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000021354e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>80.66544031910878</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.084x + -11979.179</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.083624411482382</v>
       </c>
       <c r="X7" t="n">
         <v>-11979.17933148436</v>
@@ -2764,7 +2690,7 @@
         <v>1.544833179621391e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>124.8999999999999</v>
+        <v>2412.493819432607</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000011275e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>80.33828804435977</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.874x + -11402.412</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.873872752663535</v>
       </c>
       <c r="X8" t="n">
         <v>-11402.41242944528</v>
@@ -2816,7 +2740,7 @@
         <v>2.479426259798415e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>126.75</v>
+        <v>2383.802378626948</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000386943e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>80.14307853878834</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 5.755x + -11034.876</t>
-        </is>
+      <c r="W9" t="n">
+        <v>5.755287158325647</v>
       </c>
       <c r="X9" t="n">
         <v>-11034.8764813468</v>
@@ -2868,7 +2790,7 @@
         <v>7.567897819944889e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>114.77</v>
+        <v>2355.290814508071</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000021e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>79.73537743298156</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.522x + -10435.688</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.522023777319139</v>
       </c>
       <c r="X10" t="n">
         <v>-10435.68750078583</v>
@@ -2920,7 +2840,7 @@
         <v>2.581782967803718e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>119.3599999999999</v>
+        <v>2328.69973597662</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000162e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>78.91863691543492</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.106x + -9489.317</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.105833053084565</v>
       </c>
       <c r="X11" t="n">
         <v>-9489.317125955242</v>
@@ -2972,7 +2890,7 @@
         <v>5.878165230200405e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>129.7199999999998</v>
+        <v>2303.031856226592</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000086677e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>78.83031336632652</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 5.064x + -9310.968</t>
-        </is>
+      <c r="W12" t="n">
+        <v>5.064430218133074</v>
       </c>
       <c r="X12" t="n">
         <v>-9310.967628059669</v>
@@ -3024,7 +2940,7 @@
         <v>5.898394540780897e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>120.6400000000001</v>
+        <v>2277.953342403202</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000043942e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>78.25862137758851</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 4.811x + -8720.505</t>
-        </is>
+      <c r="W13" t="n">
+        <v>4.811316464110353</v>
       </c>
       <c r="X13" t="n">
         <v>-8720.504584108672</v>
@@ -3076,7 +2990,7 @@
         <v>6.073144087203971e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>117.98</v>
+        <v>2254.016424429858</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>77.51182730448956</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 4.515x + -8058.744</t>
-        </is>
+      <c r="W14" t="n">
+        <v>4.515119068603103</v>
       </c>
       <c r="X14" t="n">
         <v>-8058.743922769041</v>
@@ -3128,7 +3040,7 @@
         <v>1.525846042948044e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>113.9400000000001</v>
+        <v>2231.339076593582</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000005142e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>75.80413585887663</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 3.953x + -6893.844</t>
-        </is>
+      <c r="W15" t="n">
+        <v>3.95316142324273</v>
       </c>
       <c r="X15" t="n">
         <v>-6893.843963403062</v>
@@ -3180,7 +3090,7 @@
         <v>1.496748599831116e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>101.8300000000002</v>
+        <v>2208.739228182183</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>74.70374740596479</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 3.656x + -6260.119</t>
-        </is>
+      <c r="W16" t="n">
+        <v>3.656323908945197</v>
       </c>
       <c r="X16" t="n">
         <v>-6260.118745598808</v>
@@ -3232,7 +3140,7 @@
         <v>1.809198738748828e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>101.22</v>
+        <v>2186.912322818807</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000023577e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>75.59641130130557</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 3.894x + -6659.138</t>
-        </is>
+      <c r="W17" t="n">
+        <v>3.89373036157181</v>
       </c>
       <c r="X17" t="n">
         <v>-6659.137677013047</v>
@@ -3284,7 +3190,7 @@
         <v>1.056410063579411e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>112.55</v>
+        <v>2165.798788532495</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000104934e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>71.97983678564529</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 3.074x + -5059.278</t>
-        </is>
+      <c r="W18" t="n">
+        <v>3.074002227919823</v>
       </c>
       <c r="X18" t="n">
         <v>-5059.27801755262</v>
@@ -3336,7 +3240,7 @@
         <v>9.12674484447922e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>100.96</v>
+        <v>2145.633565072945</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000056875e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>71.96496809531085</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 3.071x + -5013.089</t>
-        </is>
+      <c r="W19" t="n">
+        <v>3.071292667337166</v>
       </c>
       <c r="X19" t="n">
         <v>-5013.089439330403</v>
@@ -3388,7 +3290,7 @@
         <v>4.406894532279455e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>102.3600000000001</v>
+        <v>2125.834182320692</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000017028e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>71.66015199783415</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.017x + -4872.549</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.016681303761611</v>
       </c>
       <c r="X20" t="n">
         <v>-4872.548960438281</v>
@@ -3440,7 +3340,7 @@
         <v>4.05216978310343e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>107.6700000000001</v>
+        <v>2106.696269590566</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000059e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>66.96628715035813</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 2.352x + -3613.794</t>
-        </is>
+      <c r="W21" t="n">
+        <v>2.352003655164078</v>
       </c>
       <c r="X21" t="n">
         <v>-3613.793524151322</v>
@@ -3492,7 +3390,7 @@
         <v>2.736925042440009e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>102.0899999999999</v>
+        <v>2087.687086759841</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000390443e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>66.90489445212472</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 2.345x + -3575.397</t>
-        </is>
+      <c r="W22" t="n">
+        <v>2.345022262484005</v>
       </c>
       <c r="X22" t="n">
         <v>-3575.396579701583</v>
@@ -3544,7 +3440,7 @@
         <v>1.881813102626941e-07</v>
       </c>
       <c r="Z22" t="n">
-        <v>103.53</v>
+        <v>2069.025207331233</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000004022e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>88.09430783337544</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 30.055x + -78760.157</t>
-        </is>
+      <c r="W2" t="n">
+        <v>30.05451289616062</v>
       </c>
       <c r="X2" t="n">
         <v>-78760.15730880057</v>
@@ -3742,7 +3636,7 @@
         <v>1.786831553088973e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>353.1399999999999</v>
+        <v>3011.390085308609</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000232958e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.09575976678013</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.670x + -21089.865</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.669801019728071</v>
       </c>
       <c r="X3" t="n">
         <v>-21089.8647949108</v>
@@ -3794,7 +3686,7 @@
         <v>1.233518091867686e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>154.3499999999999</v>
+        <v>2717.953516990817</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001024e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>81.88686765536133</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 7.015x + -15220.715</t>
-        </is>
+      <c r="W4" t="n">
+        <v>7.014839894666415</v>
       </c>
       <c r="X4" t="n">
         <v>-15220.71470400804</v>
@@ -3846,7 +3736,7 @@
         <v>9.434306613700836e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>148.0599999999999</v>
+        <v>2640.42276538133</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000028616e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>82.12892926366001</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 7.233x + -15445.573</t>
-        </is>
+      <c r="W5" t="n">
+        <v>7.233436821182334</v>
       </c>
       <c r="X5" t="n">
         <v>-15445.57309959872</v>
@@ -3898,7 +3786,7 @@
         <v>2.711065944226108e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>135</v>
+        <v>2592.826133116453</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000041606e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>81.41976774629789</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.628x + -13852.937</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.62765646336601</v>
       </c>
       <c r="X6" t="n">
         <v>-13852.93701736268</v>
@@ -3950,7 +3836,7 @@
         <v>4.807054464653887e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>139.8099999999999</v>
+        <v>2551.09613769508</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000016451e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>81.17035524019785</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.438x + -13236.676</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.437574006989479</v>
       </c>
       <c r="X7" t="n">
         <v>-13236.67640537149</v>
@@ -4002,7 +3886,7 @@
         <v>8.612455610070082e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>132.02</v>
+        <v>2512.0231756733</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000107133e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>80.75572285552995</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.144x + -12411.653</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.144098341469087</v>
       </c>
       <c r="X8" t="n">
         <v>-12411.65283345398</v>
@@ -4054,7 +3936,7 @@
         <v>3.679975798242193e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>134.96</v>
+        <v>2475.294392573575</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000904e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>80.57165800571153</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.022x + -11990.813</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.022021829632053</v>
       </c>
       <c r="X9" t="n">
         <v>-11990.81323150786</v>
@@ -4106,7 +3986,7 @@
         <v>5.294722738196046e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>131.02</v>
+        <v>2440.997626481409</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000016248e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>79.89208914264633</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.609x + -10973.140</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.609481839932464</v>
       </c>
       <c r="X10" t="n">
         <v>-10973.14047150493</v>
@@ -4158,7 +4036,7 @@
         <v>2.160217842635149e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>132.9299999999998</v>
+        <v>2409.05635538728</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000025692e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>80.04006496451282</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.695x + -11021.412</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.694564204306438</v>
       </c>
       <c r="X11" t="n">
         <v>-11021.41217326432</v>
@@ -4210,7 +4086,7 @@
         <v>1.799878448228988e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>123.8399999999999</v>
+        <v>2379.12308594633</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000042e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>-85.82040409444005</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = -13.684x + 33683.172</t>
-        </is>
+      <c r="W2" t="n">
+        <v>-13.68412499268006</v>
       </c>
       <c r="X2" t="n">
         <v>33683.17202914214</v>
@@ -4408,7 +4282,7 @@
         <v>4.001697785037651e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>159.46</v>
+        <v>2674.284493773773</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000008e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>81.46238613246548</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 6.661x + -13909.111</t>
-        </is>
+      <c r="W3" t="n">
+        <v>6.661239260371824</v>
       </c>
       <c r="X3" t="n">
         <v>-13909.11086847288</v>
@@ -4460,7 +4332,7 @@
         <v>2.527194843870823e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>143.0599999999999</v>
+        <v>2543.438231911937</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>81.73056589589275</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.880x + -14127.828</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.8804450097968</v>
       </c>
       <c r="X4" t="n">
         <v>-14127.82846524425</v>
@@ -4512,7 +4382,7 @@
         <v>7.73755727272483e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>127.7799999999997</v>
+        <v>2498.320323195103</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>80.77018552246251</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.154x + -12395.112</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.153894840862897</v>
       </c>
       <c r="X5" t="n">
         <v>-12395.1122341742</v>
@@ -4564,7 +4432,7 @@
         <v>2.417716927405043e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>135.3900000000003</v>
+        <v>2468.881075696555</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000226e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>80.73905095853198</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.133x + -12233.196</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.132843024214359</v>
       </c>
       <c r="X6" t="n">
         <v>-12233.19593743782</v>
@@ -4616,7 +4482,7 @@
         <v>2.771905265476392e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>131.6100000000001</v>
+        <v>2444.66050228381</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004754e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>80.42384485326912</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.927x + -11690.927</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.927355759885804</v>
       </c>
       <c r="X7" t="n">
         <v>-11690.92654999617</v>
@@ -4668,7 +4532,7 @@
         <v>1.054545805753066e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>132.6300000000001</v>
+        <v>2422.261225547426</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018646e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>80.24359187525593</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.816x + -11359.064</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.815759951450092</v>
       </c>
       <c r="X8" t="n">
         <v>-11359.06371320082</v>
@@ -4720,7 +4582,7 @@
         <v>2.967864930265573e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>129.98</v>
+        <v>2401.760521299128</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001124e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>80.22458941476644</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 5.804x + -11257.414</t>
-        </is>
+      <c r="W9" t="n">
+        <v>5.804232923996405</v>
       </c>
       <c r="X9" t="n">
         <v>-11257.41373524666</v>
@@ -4772,7 +4632,7 @@
         <v>4.151262931802478e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>119.4300000000001</v>
+        <v>2382.859112404922</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000081e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>79.97780457130467</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.658x + -10869.387</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.658463019198656</v>
       </c>
       <c r="X10" t="n">
         <v>-10869.38676452248</v>
@@ -4824,7 +4682,7 @@
         <v>9.276352370959234e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>121.3</v>
+        <v>2364.158321890183</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>79.71579786482299</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.511x + -10490.285</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.511282095653958</v>
       </c>
       <c r="X11" t="n">
         <v>-10490.28538429595</v>
@@ -4876,7 +4732,7 @@
         <v>1.213274958644838e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>116.0600000000002</v>
+        <v>2346.350680881624</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000037979e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>79.30153815519702</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 5.293x + -9976.290</t>
-        </is>
+      <c r="W12" t="n">
+        <v>5.293129337561722</v>
       </c>
       <c r="X12" t="n">
         <v>-9976.289598617124</v>
@@ -4928,7 +4782,7 @@
         <v>1.285735264623511e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>117.1500000000001</v>
+        <v>2328.743438180887</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000062752e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>79.22364525887699</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 5.254x + -9821.919</t>
-        </is>
+      <c r="W13" t="n">
+        <v>5.253962609440527</v>
       </c>
       <c r="X13" t="n">
         <v>-9821.918907996078</v>
@@ -4980,7 +4832,7 @@
         <v>5.501943032585831e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>118.6899999999998</v>
+        <v>2311.154004215749</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000003e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>78.61445943814785</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 4.966x + -9178.377</t>
-        </is>
+      <c r="W14" t="n">
+        <v>4.965915012758859</v>
       </c>
       <c r="X14" t="n">
         <v>-9178.377094020414</v>
@@ -5032,7 +4882,7 @@
         <v>1.082177876915714e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>111.8000000000002</v>
+        <v>2294.221169055784</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000020636e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>78.30266259639752</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 4.830x + -8839.225</t>
-        </is>
+      <c r="W15" t="n">
+        <v>4.829947665105149</v>
       </c>
       <c r="X15" t="n">
         <v>-8839.225052122372</v>
@@ -5084,7 +4932,7 @@
         <v>1.708787579501874e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>123.1000000000001</v>
+        <v>2276.695625055484</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000275e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>77.5568465763868</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 4.532x + -8187.162</t>
-        </is>
+      <c r="W16" t="n">
+        <v>4.531982853826364</v>
       </c>
       <c r="X16" t="n">
         <v>-8187.16246258248</v>
@@ -5136,7 +4982,7 @@
         <v>3.867870865145007e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>110.3799999999999</v>
+        <v>2259.213562200337</v>
       </c>
       <c r="AA16" t="n">
         <v>1.00000000000057e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>76.80255617255989</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 4.264x + -7598.949</t>
-        </is>
+      <c r="W17" t="n">
+        <v>4.264377502545075</v>
       </c>
       <c r="X17" t="n">
         <v>-7598.949092311984</v>
@@ -5188,7 +5032,7 @@
         <v>6.6082566251541e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>106.3900000000001</v>
+        <v>2240.449683571833</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>76.08746304544461</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 4.037x + -7095.700</t>
-        </is>
+      <c r="W18" t="n">
+        <v>4.037024273282904</v>
       </c>
       <c r="X18" t="n">
         <v>-7095.70000561196</v>
@@ -5240,7 +5082,7 @@
         <v>2.582652997610923e-07</v>
       </c>
       <c r="Z18" t="n">
-        <v>107.0999999999999</v>
+        <v>2221.403972757881</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000073e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>74.42830302001586</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 3.588x + -6174.368</t>
-        </is>
+      <c r="W19" t="n">
+        <v>3.588440331864283</v>
       </c>
       <c r="X19" t="n">
         <v>-6174.36839395098</v>
@@ -5292,7 +5132,7 @@
         <v>2.218837313543849e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>102.9400000000001</v>
+        <v>2201.693149781671</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>75.7245552548771</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.930x + -6777.427</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.93019288369934</v>
       </c>
       <c r="X20" t="n">
         <v>-6777.427021364794</v>
@@ -5344,7 +5182,7 @@
         <v>1.369674985823065e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>111.5200000000002</v>
+        <v>2182.224619966437</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>71.47192935793714</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 2.984x + -4924.698</t>
-        </is>
+      <c r="W21" t="n">
+        <v>2.983826024096705</v>
       </c>
       <c r="X21" t="n">
         <v>-4924.697935117063</v>
@@ -5396,7 +5232,7 @@
         <v>2.751548373145456e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>100.4000000000001</v>
+        <v>2162.633245764146</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000292301e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>74.51123344201001</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.609x + -6064.797</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.608630768459387</v>
       </c>
       <c r="X22" t="n">
         <v>-6064.797403531207</v>
@@ -5448,7 +5282,7 @@
         <v>2.608922912703149e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>116.1900000000001</v>
+        <v>2142.888228635001</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>87.96324123033871</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 28.119x + -71616.065</t>
-        </is>
+      <c r="W2" t="n">
+        <v>28.11901144093827</v>
       </c>
       <c r="X2" t="n">
         <v>-71616.06502077462</v>
@@ -5646,7 +5478,7 @@
         <v>2.117751497835266e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>468.4699999999998</v>
+        <v>2936.677572140641</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000012968e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>87.13931916918921</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 20.012x + -45061.820</t>
-        </is>
+      <c r="W3" t="n">
+        <v>20.01207591544794</v>
       </c>
       <c r="X3" t="n">
         <v>-45061.81952303981</v>
@@ -5698,7 +5528,7 @@
         <v>1.958086466774596e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>163.54</v>
+        <v>2692.242874545106</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000014577e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>81.88833678925752</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 7.016x + -15106.113</t>
-        </is>
+      <c r="W4" t="n">
+        <v>7.016127520282379</v>
       </c>
       <c r="X4" t="n">
         <v>-15106.11296741202</v>
@@ -5750,7 +5578,7 @@
         <v>1.247089447767962e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>146.96</v>
+        <v>2618.150634152249</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000153e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>81.39979066064795</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.612x + -13932.589</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.612028470594559</v>
       </c>
       <c r="X5" t="n">
         <v>-13932.58900800227</v>
@@ -5802,7 +5628,7 @@
         <v>3.635158269243158e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>149.8600000000001</v>
+        <v>2572.52477865014</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000034e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>81.43435707413214</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.639x + -13786.633</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.639115347060015</v>
       </c>
       <c r="X6" t="n">
         <v>-13786.63331417237</v>
@@ -5854,7 +5678,7 @@
         <v>4.416893742440481e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>137.5100000000002</v>
+        <v>2533.289867695818</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000174e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>81.6869081072623</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.844x + -14050.344</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.843802973259718</v>
       </c>
       <c r="X7" t="n">
         <v>-14050.34403228993</v>
@@ -5906,7 +5728,7 @@
         <v>1.678018887649372e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>126.6100000000001</v>
+        <v>2495.576749485846</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001539e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>80.52929401056504</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.995x + -12026.518</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.99459073920224</v>
       </c>
       <c r="X8" t="n">
         <v>-12026.51762871698</v>
@@ -5958,7 +5778,7 @@
         <v>3.064094262318908e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>136.8600000000001</v>
+        <v>2459.577970474297</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>80.56663963579884</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.019x + -11913.143</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.018759639972834</v>
       </c>
       <c r="X9" t="n">
         <v>-11913.14283832148</v>
@@ -6010,7 +5828,7 @@
         <v>7.39092983260449e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>136.47</v>
+        <v>2424.696558775766</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000007224e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>80.45632785736454</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.948x + -11610.493</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.947910219392215</v>
       </c>
       <c r="X10" t="n">
         <v>-11610.49288341105</v>
@@ -6062,7 +5878,7 @@
         <v>2.211950006983975e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>129.9399999999998</v>
+        <v>2392.166845779026</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000021e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>80.50804722548756</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.981x + -11537.817</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.980924602514635</v>
       </c>
       <c r="X11" t="n">
         <v>-11537.81654469432</v>
@@ -6114,7 +5928,7 @@
         <v>2.579255153750097e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>121.9299999999998</v>
+        <v>2361.411093080482</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000105e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>87.09007767888573</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 19.673x + -44562.783</t>
-        </is>
+      <c r="W2" t="n">
+        <v>19.67286475166236</v>
       </c>
       <c r="X2" t="n">
         <v>-44562.78278374775</v>
@@ -6312,7 +6124,7 @@
         <v>8.402656826550151e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.4499999999998</v>
+        <v>2685.379793263403</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000025999e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>81.84538930699718</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 6.979x + -14698.110</t>
-        </is>
+      <c r="W3" t="n">
+        <v>6.978676287053522</v>
       </c>
       <c r="X3" t="n">
         <v>-14698.11016432498</v>
@@ -6364,7 +6174,7 @@
         <v>7.230863358269388e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>142.27</v>
+        <v>2556.398313011775</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000461458e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>81.69939753094116</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.854x + -14157.445</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.854246276422602</v>
       </c>
       <c r="X4" t="n">
         <v>-14157.44454605444</v>
@@ -6416,7 +6224,7 @@
         <v>2.793223466398135e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>132.4899999999998</v>
+        <v>2512.416219146788</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000101e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>81.33003173151414</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.558x + -13346.764</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.558016938701641</v>
       </c>
       <c r="X5" t="n">
         <v>-13346.76369863253</v>
@@ -6468,7 +6274,7 @@
         <v>1.160967592451774e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>134.4500000000003</v>
+        <v>2482.432594083486</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000055893e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>81.23911844931203</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.489x + -13058.470</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.488907595617004</v>
       </c>
       <c r="X6" t="n">
         <v>-13058.46990651315</v>
@@ -6520,7 +6324,7 @@
         <v>3.488412954610819e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>131.4500000000003</v>
+        <v>2456.274889146551</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>80.60546996201529</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.044x + -11989.416</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.044091305916541</v>
       </c>
       <c r="X7" t="n">
         <v>-11989.41641045902</v>
@@ -6572,7 +6374,7 @@
         <v>1.680785128129256e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>134.01</v>
+        <v>2431.055510540169</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000118768e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>81.02813574746196</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.334x + -12487.465</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.333880392911789</v>
       </c>
       <c r="X8" t="n">
         <v>-12487.46503069001</v>
@@ -6624,7 +6424,7 @@
         <v>2.275129944872111e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>125.3000000000002</v>
+        <v>2407.007506266758</v>
       </c>
       <c r="AA8" t="n">
         <v>1.0000000000002e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>80.65532393194952</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.077x + -11839.364</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.076920319123904</v>
       </c>
       <c r="X9" t="n">
         <v>-11839.36444176706</v>
@@ -6676,7 +6474,7 @@
         <v>4.338815598007196e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>123.8500000000001</v>
+        <v>2383.483686951633</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000079e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>80.60168176755981</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 6.042x + -11661.338</t>
-        </is>
+      <c r="W10" t="n">
+        <v>6.041610877417288</v>
       </c>
       <c r="X10" t="n">
         <v>-11661.33753679387</v>
@@ -6728,7 +6524,7 @@
         <v>1.146485842324968e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>122.5000000000002</v>
+        <v>2361.323694518063</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>79.95085488340752</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.643x + -10739.335</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.642973774707093</v>
       </c>
       <c r="X11" t="n">
         <v>-10739.33531980895</v>
@@ -6780,7 +6574,7 @@
         <v>2.095200877837401e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>128.79</v>
+        <v>2339.502033475297</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000026e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>79.96308992866611</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 5.650x + -10669.779</t>
-        </is>
+      <c r="W12" t="n">
+        <v>5.649995623016379</v>
       </c>
       <c r="X12" t="n">
         <v>-10669.77870015526</v>
@@ -6832,7 +6624,7 @@
         <v>9.424735591807638e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>111.3300000000002</v>
+        <v>2318.517083546198</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000043376e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>79.46950916523271</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 5.380x + -10029.733</t>
-        </is>
+      <c r="W13" t="n">
+        <v>5.379538695557694</v>
       </c>
       <c r="X13" t="n">
         <v>-10029.73288370191</v>
@@ -6884,7 +6674,7 @@
         <v>3.804969955157933e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>125.3299999999999</v>
+        <v>2297.534806654126</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000059e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>79.31465910136225</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 5.300x + -9788.442</t>
-        </is>
+      <c r="W14" t="n">
+        <v>5.29978245289024</v>
       </c>
       <c r="X14" t="n">
         <v>-9788.442375689649</v>
@@ -6936,7 +6724,7 @@
         <v>2.747167029613001e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>112</v>
+        <v>2277.033258264069</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000099e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>78.85400274089908</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 5.075x + -9265.581</t>
-        </is>
+      <c r="W15" t="n">
+        <v>5.075471343248195</v>
       </c>
       <c r="X15" t="n">
         <v>-9265.580539951061</v>
@@ -6988,7 +6774,7 @@
         <v>4.505443976199296e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>116.1299999999999</v>
+        <v>2256.68389540495</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000001436e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>78.36099238823104</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 4.855x + -8755.208</t>
-        </is>
+      <c r="W16" t="n">
+        <v>4.854837506900851</v>
       </c>
       <c r="X16" t="n">
         <v>-8755.207892042818</v>
@@ -7040,7 +6824,7 @@
         <v>3.171452398963669e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>118.8</v>
+        <v>2237.076718461622</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000634e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>78.17445881809338</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 4.776x + -8527.548</t>
-        </is>
+      <c r="W17" t="n">
+        <v>4.776092922867646</v>
       </c>
       <c r="X17" t="n">
         <v>-8527.547761122863</v>
@@ -7092,7 +6874,7 @@
         <v>1.623683741287399e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>121.8899999999999</v>
+        <v>2217.190969365798</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000005e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>77.64146237975108</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 4.564x + -8047.945</t>
-        </is>
+      <c r="W18" t="n">
+        <v>4.564006334416027</v>
       </c>
       <c r="X18" t="n">
         <v>-8047.945031695579</v>
@@ -7144,7 +6924,7 @@
         <v>6.027216755665779e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>114.6599999999999</v>
+        <v>2197.636825311049</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000001e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>76.52796988685211</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 4.174x + -7235.633</t>
-        </is>
+      <c r="W19" t="n">
+        <v>4.174275743988929</v>
       </c>
       <c r="X19" t="n">
         <v>-7235.633427636122</v>
@@ -7196,7 +6974,7 @@
         <v>9.143263996301135e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>107.78</v>
+        <v>2178.145451127642</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000001557e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>75.90669352731483</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.983x + -6817.737</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.983136241071378</v>
       </c>
       <c r="X20" t="n">
         <v>-6817.736554585192</v>
@@ -7248,7 +7024,7 @@
         <v>2.118932855856586e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>107.2700000000002</v>
+        <v>2158.628595517052</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000026e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>75.45103271350774</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 3.853x + -6511.877</t>
-        </is>
+      <c r="W21" t="n">
+        <v>3.85312522429649</v>
       </c>
       <c r="X21" t="n">
         <v>-6511.877174778572</v>
@@ -7300,7 +7074,7 @@
         <v>1.233822405465896e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>108.1199999999999</v>
+        <v>2139.201116971368</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>75.66571386144132</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.913x + -6573.575</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.913370700239529</v>
       </c>
       <c r="X22" t="n">
         <v>-6573.57496791219</v>
@@ -7352,7 +7124,7 @@
         <v>1.555134227633539e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>117.5500000000002</v>
+        <v>2119.861688745518</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>87.51033630518397</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.999x + -53974.720</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.99897536986291</v>
       </c>
       <c r="X2" t="n">
         <v>-53974.71950945709</v>
@@ -7550,7 +7320,7 @@
         <v>1.251675918735745e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>614.54</v>
+        <v>2722.482513789381</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000017296e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>86.74904427002542</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.605x + -37551.050</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.60537047733306</v>
       </c>
       <c r="X3" t="n">
         <v>-37551.0497807443</v>
@@ -7602,7 +7370,7 @@
         <v>3.754931479180862e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>147.1199999999999</v>
+        <v>2559.186523764559</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000242e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>81.9062215115754</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 7.032x + -14514.852</t>
-        </is>
+      <c r="W4" t="n">
+        <v>7.031839855797516</v>
       </c>
       <c r="X4" t="n">
         <v>-14514.85180401859</v>
@@ -7654,7 +7420,7 @@
         <v>5.105581795386281e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>134.8899999999999</v>
+        <v>2502.965694501199</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000528e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>81.49194910206108</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.685x + -13542.283</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.68473070198293</v>
       </c>
       <c r="X5" t="n">
         <v>-13542.28276559242</v>
@@ -7706,7 +7470,7 @@
         <v>2.840245649741695e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>135.8600000000001</v>
+        <v>2463.981582635214</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>80.99987116188733</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.314x + -12568.921</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.313659628394239</v>
       </c>
       <c r="X6" t="n">
         <v>-12568.92099399804</v>
@@ -7758,7 +7520,7 @@
         <v>3.387716667712425e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>133.0700000000002</v>
+        <v>2429.137587880458</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>80.60684936062036</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.045x + -11845.224</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.044994998973135</v>
       </c>
       <c r="X7" t="n">
         <v>-11845.22419483523</v>
@@ -7810,7 +7570,7 @@
         <v>2.180917416166401e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>134.6600000000001</v>
+        <v>2394.527931064527</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000134e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>80.41532819728054</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.922x + -11434.391</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.921989464303661</v>
       </c>
       <c r="X8" t="n">
         <v>-11434.39076983167</v>
@@ -7862,7 +7620,7 @@
         <v>6.053913792970128e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>128.0400000000002</v>
+        <v>2361.365768513816</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000253e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>80.35126635696295</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 5.882x + -11204.705</t>
-        </is>
+      <c r="W9" t="n">
+        <v>5.881925263315612</v>
       </c>
       <c r="X9" t="n">
         <v>-11204.7051286297</v>
@@ -7914,7 +7670,7 @@
         <v>4.541374099500187e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>126.5100000000002</v>
+        <v>2329.457937274167</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000164e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>80.34649884336676</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.879x + -11062.347</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.878964724563564</v>
       </c>
       <c r="X10" t="n">
         <v>-11062.34664654996</v>
@@ -7966,7 +7720,7 @@
         <v>9.912619760139729e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>114.76</v>
+        <v>2298.439170782339</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000010019e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>79.96284655099919</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.650x + -10468.778</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.649855780309382</v>
       </c>
       <c r="X11" t="n">
         <v>-10468.77814691912</v>
@@ -8018,7 +7770,7 @@
         <v>1.186783077225627e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>116.54</v>
+        <v>2269.055220485489</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000006196e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>88.03838653368703</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 29.197x + -67463.805</t>
-        </is>
+      <c r="W2" t="n">
+        <v>29.19708312213158</v>
       </c>
       <c r="X2" t="n">
         <v>-67463.80481688313</v>
@@ -8216,7 +7966,7 @@
         <v>1.183145902954188e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>412.6400000000003</v>
+        <v>2686.390486970981</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000018286e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>81.87646600769138</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 7.006x + -14814.851</t>
-        </is>
+      <c r="W3" t="n">
+        <v>7.005736580532762</v>
       </c>
       <c r="X3" t="n">
         <v>-14814.85070680051</v>
@@ -8268,7 +8016,7 @@
         <v>1.111474521042406e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>145.29</v>
+        <v>2560.684989515539</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000013943e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>81.50581769194375</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.696x + -13853.593</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.695806946384173</v>
       </c>
       <c r="X4" t="n">
         <v>-13853.59290068857</v>
@@ -8320,7 +8066,7 @@
         <v>1.71941888220926e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>144.0599999999999</v>
+        <v>2516.113398311693</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001757e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>81.75069506449455</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.897x + -14143.722</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.897469167641519</v>
       </c>
       <c r="X5" t="n">
         <v>-14143.72172759192</v>
@@ -8372,7 +8116,7 @@
         <v>4.457389973645242e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>131.4100000000003</v>
+        <v>2487.330254789892</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000577437e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>81.92128411004097</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 7.045x + -14321.883</t>
-        </is>
+      <c r="W6" t="n">
+        <v>7.045126467469285</v>
       </c>
       <c r="X6" t="n">
         <v>-14321.88272867534</v>
@@ -8424,7 +8166,7 @@
         <v>5.031497483976484e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>123.25</v>
+        <v>2461.543711295295</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000019187e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>80.68534012519825</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.097x + -12160.611</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.096854058715722</v>
       </c>
       <c r="X7" t="n">
         <v>-12160.6112450819</v>
@@ -8476,7 +8216,7 @@
         <v>3.727864788294048e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>137.8900000000001</v>
+        <v>2436.832044872622</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003428e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>81.57974651930112</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.755x + -13435.873</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.755461832548046</v>
       </c>
       <c r="X8" t="n">
         <v>-13435.87290284801</v>
@@ -8528,7 +8266,7 @@
         <v>9.367192601541056e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>121.1900000000001</v>
+        <v>2412.822244999396</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000013e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>80.97047297236134</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.293x + -12348.745</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.292761078618605</v>
       </c>
       <c r="X9" t="n">
         <v>-12348.74472933945</v>
@@ -8580,7 +8316,7 @@
         <v>1.054996948110553e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>126.49</v>
+        <v>2389.72479508471</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000046243e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>80.91333530017002</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 6.253x + -12155.257</t>
-        </is>
+      <c r="W10" t="n">
+        <v>6.252526741927878</v>
       </c>
       <c r="X10" t="n">
         <v>-12155.25681238084</v>
@@ -8632,7 +8366,7 @@
         <v>1.024568131383995e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>121.6800000000001</v>
+        <v>2367.4116501242</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000006e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>80.78016904878108</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 6.161x + -11858.280</t>
-        </is>
+      <c r="W11" t="n">
+        <v>6.160675103707614</v>
       </c>
       <c r="X11" t="n">
         <v>-11858.280242979</v>
@@ -8684,7 +8416,7 @@
         <v>1.314009031061219e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>119.3899999999999</v>
+        <v>2345.958731469249</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000032e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>80.2745815969581</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 5.835x + -11095.677</t>
-        </is>
+      <c r="W12" t="n">
+        <v>5.834654230646167</v>
       </c>
       <c r="X12" t="n">
         <v>-11095.67692918065</v>
@@ -8736,7 +8466,7 @@
         <v>6.97857171440006e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>125.7099999999998</v>
+        <v>2325.072926922543</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000060638e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>80.47932636684661</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 5.963x + -11261.543</t>
-        </is>
+      <c r="W13" t="n">
+        <v>5.962547138327809</v>
       </c>
       <c r="X13" t="n">
         <v>-11261.54318003224</v>
@@ -8788,7 +8516,7 @@
         <v>1.705364797175104e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>112.8399999999999</v>
+        <v>2304.474133319054</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000004977e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>80.08510871185089</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 5.721x + -10684.111</t>
-        </is>
+      <c r="W14" t="n">
+        <v>5.720962251384011</v>
       </c>
       <c r="X14" t="n">
         <v>-10684.11138840195</v>
@@ -8840,7 +8566,7 @@
         <v>1.029102557085396e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>119.0899999999999</v>
+        <v>2284.753928592743</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000340535e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>80.16381530960258</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 5.768x + -10690.681</t>
-        </is>
+      <c r="W15" t="n">
+        <v>5.767663021381217</v>
       </c>
       <c r="X15" t="n">
         <v>-10690.68072800848</v>
@@ -8892,7 +8616,7 @@
         <v>4.666552701910998e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>114.3799999999999</v>
+        <v>2265.661450334293</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000002183e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>79.82965826704286</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 5.574x + -10226.307</t>
-        </is>
+      <c r="W16" t="n">
+        <v>5.574320683196163</v>
       </c>
       <c r="X16" t="n">
         <v>-10226.30673371317</v>
@@ -8944,7 +8666,7 @@
         <v>4.761022622635242e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>112.29</v>
+        <v>2246.900968461987</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000041311e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>79.51745299937818</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 5.405x + -9811.821</t>
-        </is>
+      <c r="W17" t="n">
+        <v>5.404704640116488</v>
       </c>
       <c r="X17" t="n">
         <v>-9811.820734313953</v>
@@ -8996,7 +8716,7 @@
         <v>8.314017394173889e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>109.5599999999999</v>
+        <v>2227.580480675245</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>78.85770683064864</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 5.077x + -9094.208</t>
-        </is>
+      <c r="W18" t="n">
+        <v>5.077201933076315</v>
       </c>
       <c r="X18" t="n">
         <v>-9094.208120553181</v>
@@ -9048,7 +8766,7 @@
         <v>8.099807657802709e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>121.8299999999999</v>
+        <v>2207.892732821187</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002956e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>78.41101124211923</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 4.876x + -8631.513</t>
-        </is>
+      <c r="W19" t="n">
+        <v>4.876377777613471</v>
       </c>
       <c r="X19" t="n">
         <v>-8631.513384457108</v>
@@ -9100,7 +8816,7 @@
         <v>2.073916530529249e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>103.1299999999999</v>
+        <v>2188.466599121697</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>77.78010210306275</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 4.617x + -8066.440</t>
-        </is>
+      <c r="W20" t="n">
+        <v>4.617419161472648</v>
       </c>
       <c r="X20" t="n">
         <v>-8066.439876583923</v>
@@ -9152,7 +8866,7 @@
         <v>4.222547217124628e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>101.1600000000001</v>
+        <v>2169.165781966564</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000011e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>77.66151198302688</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 4.572x + -7918.459</t>
-        </is>
+      <c r="W21" t="n">
+        <v>4.571657614967597</v>
       </c>
       <c r="X21" t="n">
         <v>-7918.459157029197</v>
@@ -9204,7 +8916,7 @@
         <v>3.444047766692636e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>112.04</v>
+        <v>2150.050766356738</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000037755e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>77.64911761277996</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 4.567x + -7840.942</t>
-        </is>
+      <c r="W22" t="n">
+        <v>4.566924819591673</v>
       </c>
       <c r="X22" t="n">
         <v>-7840.941613102235</v>
@@ -9256,7 +8966,7 @@
         <v>1.738667450564676e-07</v>
       </c>
       <c r="Z22" t="n">
-        <v>109.8099999999999</v>
+        <v>2131.369482436101</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000109218e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>87.96484616691941</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 28.141x + -57740.795</t>
-        </is>
+      <c r="W2" t="n">
+        <v>28.14120497528986</v>
       </c>
       <c r="X2" t="n">
         <v>-57740.79517774256</v>
@@ -9454,7 +9162,7 @@
         <v>2.051247856185267e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>440.5800000000002</v>
+        <v>2294.017082802051</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000007539e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>-69.91631284645814</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = -2.735x + 6209.595</t>
-        </is>
+      <c r="W3" t="n">
+        <v>-2.735041045811539</v>
       </c>
       <c r="X3" t="n">
         <v>6209.594969437313</v>
@@ -9506,7 +9212,7 @@
         <v>1.712457392977619e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>128.6400000000001</v>
+        <v>2051.599275085305</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000011e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>80.92446931233515</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.260x + -10347.037</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.260327511175567</v>
       </c>
       <c r="X4" t="n">
         <v>-10347.03658303436</v>
@@ -9558,7 +9262,7 @@
         <v>1.080458273433676e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>119.6400000000001</v>
+        <v>1991.722397896727</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000001464e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>80.9611350739129</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.286x + -10223.294</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.286151177074117</v>
       </c>
       <c r="X5" t="n">
         <v>-10223.29399243064</v>
@@ -9610,7 +9312,7 @@
         <v>3.410662971559168e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>107.98</v>
+        <v>1957.402345524185</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002396e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>80.12736363966729</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 5.746x + -9147.922</t>
-        </is>
+      <c r="W6" t="n">
+        <v>5.745942673259194</v>
       </c>
       <c r="X6" t="n">
         <v>-9147.921927695401</v>
@@ -9662,7 +9362,7 @@
         <v>1.912706237936999e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>116.1899999999998</v>
+        <v>1927.861782576359</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>79.92610058583583</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.629x + -8826.233</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.628818597238174</v>
       </c>
       <c r="X7" t="n">
         <v>-8826.232647253944</v>
@@ -9714,7 +9412,7 @@
         <v>952.8512276116016</v>
       </c>
       <c r="Z7" t="n">
-        <v>114.1600000000001</v>
+        <v>1779851100.575519</v>
       </c>
       <c r="AA7" t="n">
         <v>4.231634030276023e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>80.06301893464592</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.708x + -8838.228</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.707986855774786</v>
       </c>
       <c r="X8" t="n">
         <v>-8838.227600150214</v>
@@ -9766,7 +9462,7 @@
         <v>910.5175082169267</v>
       </c>
       <c r="Z8" t="n">
-        <v>101.01</v>
+        <v>273617289.6517155</v>
       </c>
       <c r="AA8" t="n">
         <v>6.584274685941277e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>79.41383595310127</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 5.351x + -8135.038</t>
-        </is>
+      <c r="W9" t="n">
+        <v>5.350598385698979</v>
       </c>
       <c r="X9" t="n">
         <v>-8135.038187212838</v>
@@ -9818,7 +9512,7 @@
         <v>906.7673291276271</v>
       </c>
       <c r="Z9" t="n">
-        <v>104.28</v>
+        <v>232468487.862025</v>
       </c>
       <c r="AA9" t="n">
         <v>6.099039348884555e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>79.05683543241226</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.172x + -7742.104</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.171939534218198</v>
       </c>
       <c r="X10" t="n">
         <v>-7742.103527652958</v>
@@ -9870,7 +9562,7 @@
         <v>947.4125643243673</v>
       </c>
       <c r="Z10" t="n">
-        <v>97.11000000000013</v>
+        <v>702965445.5312467</v>
       </c>
       <c r="AA10" t="n">
         <v>3.240243778522406e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>78.98136727189252</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.136x + -7586.702</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.135636781980701</v>
       </c>
       <c r="X11" t="n">
         <v>-7586.701877014153</v>
@@ -9922,7 +9612,7 @@
         <v>943.3992148990433</v>
       </c>
       <c r="Z11" t="n">
-        <v>100.23</v>
+        <v>631947814.5222821</v>
       </c>
       <c r="AA11" t="n">
         <v>3.062665850609764e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>27.35999999999967</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>139.2000000000003</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>185.3499999999999</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>203.8699999999999</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>228.78</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>229.99</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>245.6600000000003</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>251.5600000000002</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>255.1100000000001</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>275.9199999999998</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-353.1399999999999</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-76.56999999999971</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>55.86999999999989</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>128.9199999999996</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>155.4600000000003</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>186.6400000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>199.97</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>217.49</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>222.6900000000001</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>240.27</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-468.4699999999998</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-118.96</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>41.80999999999995</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>103.98</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>152.8499999999999</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>185.6900000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>189.9199999999998</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>205.45</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>220.51</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>236.4200000000001</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-614.54</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-96.30000000000018</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>53.30999999999995</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>105.6900000000001</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>137.9000000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>165.1400000000001</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>178.5699999999999</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>188.5799999999999</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>206.3</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>211.2800000000002</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-440.5800000000002</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-34.09000000000015</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>49.31999999999994</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>89.18000000000006</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>92.34000000000015</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>102.73</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>117.74</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>121.54</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>131.1299999999999</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>130.04</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>27.35999999999967</v>
+        <v>1957.236</v>
       </c>
       <c r="D2" t="n">
         <v>9.684039999999999e-08</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>139.2000000000003</v>
+        <v>1817.878</v>
       </c>
       <c r="D3" t="n">
         <v>9.56945e-08</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>185.3499999999999</v>
+        <v>1774.953</v>
       </c>
       <c r="D4" t="n">
         <v>9.54046e-08</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>203.8699999999999</v>
+        <v>1735.142</v>
       </c>
       <c r="D5" t="n">
         <v>9.52796e-08</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>228.78</v>
+        <v>1714.096</v>
       </c>
       <c r="D6" t="n">
         <v>9.51974e-08</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>229.99</v>
+        <v>1679.517</v>
       </c>
       <c r="D7" t="n">
         <v>9.515719999999999e-08</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>245.6600000000003</v>
+        <v>1656.602</v>
       </c>
       <c r="D8" t="n">
         <v>9.51519e-08</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>251.5600000000002</v>
+        <v>1629.087</v>
       </c>
       <c r="D9" t="n">
         <v>9.51472e-08</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>255.1100000000001</v>
+        <v>1605.65</v>
       </c>
       <c r="D10" t="n">
         <v>9.517799999999999e-08</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>275.9199999999998</v>
+        <v>1591.787</v>
       </c>
       <c r="D11" t="n">
         <v>9.52153e-08</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>34.20000000000027</v>
+        <v>1836.084</v>
       </c>
       <c r="D2" t="n">
         <v>1.05005e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>72.45000000000027</v>
+        <v>1724.814</v>
       </c>
       <c r="D3" t="n">
         <v>1.05161e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>86.98000000000002</v>
+        <v>1680.562</v>
       </c>
       <c r="D4" t="n">
         <v>1.05226e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>97.51999999999998</v>
+        <v>1651.756</v>
       </c>
       <c r="D5" t="n">
         <v>1.05291e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>108.78</v>
+        <v>1629.905</v>
       </c>
       <c r="D6" t="n">
         <v>1.05335e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>110.6200000000001</v>
+        <v>1605.689</v>
       </c>
       <c r="D7" t="n">
         <v>1.05377e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>119.4199999999998</v>
+        <v>1585.731</v>
       </c>
       <c r="D8" t="n">
         <v>1.05451e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>128.26</v>
+        <v>1569.091</v>
       </c>
       <c r="D9" t="n">
         <v>1.05481e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>128.3099999999999</v>
+        <v>1549.136</v>
       </c>
       <c r="D10" t="n">
         <v>1.05533e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>131.3</v>
+        <v>1534.242</v>
       </c>
       <c r="D11" t="n">
         <v>1.0555e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>143.8800000000001</v>
+        <v>1526.608</v>
       </c>
       <c r="D12" t="n">
         <v>1.05571e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>142.9399999999998</v>
+        <v>1508.257</v>
       </c>
       <c r="D13" t="n">
         <v>1.05597e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>144.72</v>
+        <v>1492.967</v>
       </c>
       <c r="D14" t="n">
         <v>1.05623e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>158.98</v>
+        <v>1488.134</v>
       </c>
       <c r="D15" t="n">
         <v>1.0563e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>160.21</v>
+        <v>1473.284</v>
       </c>
       <c r="D16" t="n">
         <v>1.05636e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>167.8800000000001</v>
+        <v>1458.505</v>
       </c>
       <c r="D17" t="n">
         <v>1.05674e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>160.3800000000001</v>
+        <v>1438.01</v>
       </c>
       <c r="D18" t="n">
         <v>1.05681e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>166.0400000000002</v>
+        <v>1423.579</v>
       </c>
       <c r="D19" t="n">
         <v>1.05718e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>165.3100000000002</v>
+        <v>1399.36</v>
       </c>
       <c r="D20" t="n">
         <v>1.05747e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>185.77</v>
+        <v>1399.741</v>
       </c>
       <c r="D21" t="n">
         <v>1.05768e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>189.0699999999999</v>
+        <v>1386.226</v>
       </c>
       <c r="D22" t="n">
         <v>1.05792e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>97.19999999999982</v>
+        <v>1814.252</v>
       </c>
       <c r="D2" t="n">
         <v>9.624929999999999e-08</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>172.2999999999997</v>
+        <v>1717.973</v>
       </c>
       <c r="D3" t="n">
         <v>9.5979e-08</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>201.47</v>
+        <v>1680.069</v>
       </c>
       <c r="D4" t="n">
         <v>9.58995e-08</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>223.8900000000001</v>
+        <v>1658.341</v>
       </c>
       <c r="D5" t="n">
         <v>9.586429999999999e-08</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>237.5700000000002</v>
+        <v>1633.661</v>
       </c>
       <c r="D6" t="n">
         <v>9.58898e-08</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>243.9200000000001</v>
+        <v>1609.625</v>
       </c>
       <c r="D7" t="n">
         <v>9.59227e-08</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>248.9699999999998</v>
+        <v>1582.947</v>
       </c>
       <c r="D8" t="n">
         <v>9.594530000000001e-08</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>267.0999999999999</v>
+        <v>1567.266</v>
       </c>
       <c r="D9" t="n">
         <v>9.5998e-08</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>271.25</v>
+        <v>1539.483</v>
       </c>
       <c r="D10" t="n">
         <v>9.60494e-08</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>263.45</v>
+        <v>1507.92</v>
       </c>
       <c r="D11" t="n">
         <v>9.61057e-08</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>276.29</v>
+        <v>1494.158</v>
       </c>
       <c r="D12" t="n">
         <v>9.61588e-08</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>284.75</v>
+        <v>1476.015</v>
       </c>
       <c r="D13" t="n">
         <v>9.61873e-08</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>290.9300000000001</v>
+        <v>1459.38</v>
       </c>
       <c r="D14" t="n">
         <v>9.62606e-08</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>305.8699999999999</v>
+        <v>1451.144</v>
       </c>
       <c r="D15" t="n">
         <v>9.63104e-08</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>308.3600000000001</v>
+        <v>1433.17</v>
       </c>
       <c r="D16" t="n">
         <v>9.632859999999999e-08</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>301.1500000000001</v>
+        <v>1403.502</v>
       </c>
       <c r="D17" t="n">
         <v>9.638560000000001e-08</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>316.3700000000001</v>
+        <v>1399.118</v>
       </c>
       <c r="D18" t="n">
         <v>9.642870000000001e-08</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>319.3099999999999</v>
+        <v>1379.15</v>
       </c>
       <c r="D19" t="n">
         <v>9.645660000000001e-08</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>316.3399999999999</v>
+        <v>1359.163</v>
       </c>
       <c r="D20" t="n">
         <v>9.64629e-08</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>329.8100000000002</v>
+        <v>1348.709</v>
       </c>
       <c r="D21" t="n">
         <v>9.64984e-08</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>328.8</v>
+        <v>1332.375</v>
       </c>
       <c r="D22" t="n">
         <v>9.652589999999999e-08</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-353.1399999999999</v>
+        <v>2171.352</v>
       </c>
       <c r="D2" t="n">
         <v>9.80773e-08</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-76.56999999999971</v>
+        <v>1883.012</v>
       </c>
       <c r="D3" t="n">
         <v>9.83661e-08</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>55.86999999999989</v>
+        <v>1804.97</v>
       </c>
       <c r="D4" t="n">
         <v>9.789380000000001e-08</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>128.9199999999996</v>
+        <v>1770.276</v>
       </c>
       <c r="D5" t="n">
         <v>9.76139e-08</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>155.4600000000003</v>
+        <v>1725.149</v>
       </c>
       <c r="D6" t="n">
         <v>9.74876e-08</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>186.6400000000001</v>
+        <v>1694.95</v>
       </c>
       <c r="D7" t="n">
         <v>9.74243e-08</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>199.97</v>
+        <v>1658.698</v>
       </c>
       <c r="D8" t="n">
         <v>9.741360000000001e-08</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>217.49</v>
+        <v>1631.707</v>
       </c>
       <c r="D9" t="n">
         <v>9.74237e-08</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>222.6900000000001</v>
+        <v>1599.709</v>
       </c>
       <c r="D10" t="n">
         <v>9.74664e-08</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>240.27</v>
+        <v>1581.129</v>
       </c>
       <c r="D11" t="n">
         <v>9.751959999999999e-08</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.980000000000018</v>
+        <v>1854.921</v>
       </c>
       <c r="D2" t="n">
         <v>9.72135e-08</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>151.9499999999998</v>
+        <v>1716.726</v>
       </c>
       <c r="D3" t="n">
         <v>9.65722e-08</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>208.4600000000003</v>
+        <v>1681.905</v>
       </c>
       <c r="D4" t="n">
         <v>9.64161e-08</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>223.5399999999997</v>
+        <v>1646.014</v>
       </c>
       <c r="D5" t="n">
         <v>9.63627e-08</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>240.8899999999999</v>
+        <v>1627.187</v>
       </c>
       <c r="D6" t="n">
         <v>9.63395e-08</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>246.8699999999999</v>
+        <v>1606.584</v>
       </c>
       <c r="D7" t="n">
         <v>9.63448e-08</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>256.3499999999999</v>
+        <v>1589.029</v>
       </c>
       <c r="D8" t="n">
         <v>9.63549e-08</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>271.4799999999998</v>
+        <v>1585.458</v>
       </c>
       <c r="D9" t="n">
         <v>9.64281e-08</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>269.51</v>
+        <v>1564.309</v>
       </c>
       <c r="D10" t="n">
         <v>9.64436e-08</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>277.5599999999999</v>
+        <v>1555.784</v>
       </c>
       <c r="D11" t="n">
         <v>9.648890000000001e-08</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>280.8099999999999</v>
+        <v>1538.178</v>
       </c>
       <c r="D12" t="n">
         <v>9.65104e-08</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>285.03</v>
+        <v>1524.082</v>
       </c>
       <c r="D13" t="n">
         <v>9.65556e-08</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>294.9799999999998</v>
+        <v>1517.797</v>
       </c>
       <c r="D14" t="n">
         <v>9.65881e-08</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>285.04</v>
+        <v>1489.285</v>
       </c>
       <c r="D15" t="n">
         <v>9.65832e-08</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>305.77</v>
+        <v>1489.337</v>
       </c>
       <c r="D16" t="n">
         <v>9.66049e-08</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>311.3599999999999</v>
+        <v>1477.017</v>
       </c>
       <c r="D17" t="n">
         <v>9.663550000000001e-08</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>316.1500000000001</v>
+        <v>1459.828</v>
       </c>
       <c r="D18" t="n">
         <v>9.66478e-08</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>324.0700000000002</v>
+        <v>1448.405</v>
       </c>
       <c r="D19" t="n">
         <v>9.66655e-08</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>318.55</v>
+        <v>1423.77</v>
       </c>
       <c r="D20" t="n">
         <v>9.67068e-08</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>328.8099999999999</v>
+        <v>1417.283</v>
       </c>
       <c r="D21" t="n">
         <v>9.67213e-08</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>320.27</v>
+        <v>1385.385</v>
       </c>
       <c r="D22" t="n">
         <v>9.67732e-08</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-468.4699999999998</v>
+        <v>2100.214</v>
       </c>
       <c r="D2" t="n">
         <v>9.88663e-08</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-118.96</v>
+        <v>1853.215</v>
       </c>
       <c r="D3" t="n">
         <v>9.8513e-08</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>41.80999999999995</v>
+        <v>1789.613</v>
       </c>
       <c r="D4" t="n">
         <v>9.78979e-08</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>103.98</v>
+        <v>1742.008</v>
       </c>
       <c r="D5" t="n">
         <v>9.75794e-08</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>152.8499999999999</v>
+        <v>1716.142</v>
       </c>
       <c r="D6" t="n">
         <v>9.743639999999999e-08</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>185.6900000000001</v>
+        <v>1693.865</v>
       </c>
       <c r="D7" t="n">
         <v>9.736049999999999e-08</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>189.9199999999998</v>
+        <v>1649.548</v>
       </c>
       <c r="D8" t="n">
         <v>9.73717e-08</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>205.45</v>
+        <v>1619</v>
       </c>
       <c r="D9" t="n">
         <v>9.740380000000001e-08</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>220.51</v>
+        <v>1595.559</v>
       </c>
       <c r="D10" t="n">
         <v>9.74456e-08</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>236.4200000000001</v>
+        <v>1575.763</v>
       </c>
       <c r="D11" t="n">
         <v>9.74979e-08</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-129.3400000000001</v>
+        <v>1859.949</v>
       </c>
       <c r="D2" t="n">
         <v>9.90408e-08</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>116.5699999999999</v>
+        <v>1741.006</v>
       </c>
       <c r="D3" t="n">
         <v>9.80772e-08</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>166.8400000000001</v>
+        <v>1702.215</v>
       </c>
       <c r="D4" t="n">
         <v>9.79225e-08</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>182.5399999999997</v>
+        <v>1669.613</v>
       </c>
       <c r="D5" t="n">
         <v>9.79507e-08</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>196.7799999999997</v>
+        <v>1648.179</v>
       </c>
       <c r="D6" t="n">
         <v>9.80403e-08</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>198.5599999999999</v>
+        <v>1622.917</v>
       </c>
       <c r="D7" t="n">
         <v>9.81352e-08</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>214.6199999999999</v>
+        <v>1610.274</v>
       </c>
       <c r="D8" t="n">
         <v>9.821129999999999e-08</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>220.8</v>
+        <v>1591.012</v>
       </c>
       <c r="D9" t="n">
         <v>9.82893e-08</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>231.8</v>
+        <v>1573.55</v>
       </c>
       <c r="D10" t="n">
         <v>9.83558e-08</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>228.3</v>
+        <v>1546.478</v>
       </c>
       <c r="D11" t="n">
         <v>9.84276e-08</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>247.24</v>
+        <v>1547.203</v>
       </c>
       <c r="D12" t="n">
         <v>9.8483e-08</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>243.28</v>
+        <v>1515.979</v>
       </c>
       <c r="D13" t="n">
         <v>9.853999999999999e-08</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>256.0899999999999</v>
+        <v>1511.163</v>
       </c>
       <c r="D14" t="n">
         <v>9.85804e-08</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>261.1800000000001</v>
+        <v>1490.354</v>
       </c>
       <c r="D15" t="n">
         <v>9.861950000000001e-08</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>253.6800000000001</v>
+        <v>1468.902</v>
       </c>
       <c r="D16" t="n">
         <v>9.86953e-08</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>257.3700000000001</v>
+        <v>1450.005</v>
       </c>
       <c r="D17" t="n">
         <v>9.872379999999999e-08</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>267.5200000000002</v>
+        <v>1440.09</v>
       </c>
       <c r="D18" t="n">
         <v>9.87643e-08</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>279.8899999999999</v>
+        <v>1430.57</v>
       </c>
       <c r="D19" t="n">
         <v>9.8799e-08</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>282.75</v>
+        <v>1415.333</v>
       </c>
       <c r="D20" t="n">
         <v>9.88563e-08</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>283.6300000000001</v>
+        <v>1398.834</v>
       </c>
       <c r="D21" t="n">
         <v>9.8869e-08</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>274</v>
+        <v>1372.83</v>
       </c>
       <c r="D22" t="n">
         <v>9.88957e-08</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-614.54</v>
+        <v>1901.949</v>
       </c>
       <c r="D2" t="n">
         <v>1.02799e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-96.30000000000018</v>
+        <v>1746.613</v>
       </c>
       <c r="D3" t="n">
         <v>1.01085e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>53.30999999999995</v>
+        <v>1699.104</v>
       </c>
       <c r="D4" t="n">
         <v>1.00401e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>105.6900000000001</v>
+        <v>1658.84</v>
       </c>
       <c r="D5" t="n">
         <v>1.00171e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>137.9000000000001</v>
+        <v>1628.589</v>
       </c>
       <c r="D6" t="n">
         <v>1.00093e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>165.1400000000001</v>
+        <v>1596.459</v>
       </c>
       <c r="D7" t="n">
         <v>1.0013e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>178.5699999999999</v>
+        <v>1573.1</v>
       </c>
       <c r="D8" t="n">
         <v>1.00175e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>188.5799999999999</v>
+        <v>1546.414</v>
       </c>
       <c r="D9" t="n">
         <v>1.00236e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>206.3</v>
+        <v>1531.022</v>
       </c>
       <c r="D10" t="n">
         <v>1.00323e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>211.2800000000002</v>
+        <v>1503.517</v>
       </c>
       <c r="D11" t="n">
         <v>1.00425e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-412.6400000000003</v>
+        <v>1849.936</v>
       </c>
       <c r="D2" t="n">
         <v>1.04334e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>31.78999999999996</v>
+        <v>1737.542</v>
       </c>
       <c r="D3" t="n">
         <v>1.01775e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>96.92000000000007</v>
+        <v>1690.178</v>
       </c>
       <c r="D4" t="n">
         <v>1.01436e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>129.4199999999998</v>
+        <v>1674.687</v>
       </c>
       <c r="D5" t="n">
         <v>1.01433e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>149.9400000000001</v>
+        <v>1657.438</v>
       </c>
       <c r="D6" t="n">
         <v>1.01522e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>144.9000000000001</v>
+        <v>1620.582</v>
       </c>
       <c r="D7" t="n">
         <v>1.01607e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>165.1900000000001</v>
+        <v>1614.248</v>
       </c>
       <c r="D8" t="n">
         <v>1.01687e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>166.0799999999999</v>
+        <v>1589.135</v>
       </c>
       <c r="D9" t="n">
         <v>1.01774e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>173.8199999999999</v>
+        <v>1573.797</v>
       </c>
       <c r="D10" t="n">
         <v>1.01854e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>182.03</v>
+        <v>1557.214</v>
       </c>
       <c r="D11" t="n">
         <v>1.01902e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>177.8</v>
+        <v>1534.302</v>
       </c>
       <c r="D12" t="n">
         <v>1.01963e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>195.1200000000001</v>
+        <v>1527.01</v>
       </c>
       <c r="D13" t="n">
         <v>1.02014e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>190.49</v>
+        <v>1504.367</v>
       </c>
       <c r="D14" t="n">
         <v>1.02064e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>199.9000000000001</v>
+        <v>1493.931</v>
       </c>
       <c r="D15" t="n">
         <v>1.02105e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>206.48</v>
+        <v>1480.147</v>
       </c>
       <c r="D16" t="n">
         <v>1.02135e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>212.3400000000001</v>
+        <v>1466.799</v>
       </c>
       <c r="D17" t="n">
         <v>1.02168e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>200.28</v>
+        <v>1437.236</v>
       </c>
       <c r="D18" t="n">
         <v>1.02204e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>228.1200000000001</v>
+        <v>1441.264</v>
       </c>
       <c r="D19" t="n">
         <v>1.02245e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>230.55</v>
+        <v>1427.772</v>
       </c>
       <c r="D20" t="n">
         <v>1.02259e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>221.3199999999999</v>
+        <v>1398.795</v>
       </c>
       <c r="D21" t="n">
         <v>1.02283e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>227.03</v>
+        <v>1384.802</v>
       </c>
       <c r="D22" t="n">
         <v>1.02313e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-440.5800000000002</v>
+        <v>1559.477</v>
       </c>
       <c r="D2" t="n">
         <v>1.05842e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-34.09000000000015</v>
+        <v>1297.737</v>
       </c>
       <c r="D3" t="n">
         <v>1.05331e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>49.31999999999994</v>
+        <v>1239.304</v>
       </c>
       <c r="D4" t="n">
         <v>1.05269e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>89.18000000000006</v>
+        <v>1217.375</v>
       </c>
       <c r="D5" t="n">
         <v>1.05424e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>92.34000000000015</v>
+        <v>1181.601</v>
       </c>
       <c r="D6" t="n">
         <v>1.05608e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>102.73</v>
+        <v>1158.17</v>
       </c>
       <c r="D7" t="n">
         <v>1.05822e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>117.74</v>
+        <v>1145.558</v>
       </c>
       <c r="D8" t="n">
         <v>1.0607e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>121.54</v>
+        <v>1119.845</v>
       </c>
       <c r="D9" t="n">
         <v>1.0626e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>131.1299999999999</v>
+        <v>1104.321</v>
       </c>
       <c r="D10" t="n">
         <v>1.06462e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>130.04</v>
+        <v>1081.877</v>
       </c>
       <c r="D11" t="n">
         <v>1.06619e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1957.236</v>
       </c>
+      <c r="C2" t="n">
+        <v>2537.893314514995</v>
+      </c>
       <c r="D2" t="n">
         <v>9.684039999999999e-08</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1817.878</v>
       </c>
+      <c r="C3" t="n">
+        <v>2372.142000699871</v>
+      </c>
       <c r="D3" t="n">
         <v>9.56945e-08</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1774.953</v>
       </c>
+      <c r="C4" t="n">
+        <v>2322.200893762289</v>
+      </c>
       <c r="D4" t="n">
         <v>9.54046e-08</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1735.142</v>
       </c>
+      <c r="C5" t="n">
+        <v>2285.798376519984</v>
+      </c>
       <c r="D5" t="n">
         <v>9.52796e-08</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1714.096</v>
       </c>
+      <c r="C6" t="n">
+        <v>2263.415175637413</v>
+      </c>
       <c r="D6" t="n">
         <v>9.51974e-08</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1679.517</v>
       </c>
+      <c r="C7" t="n">
+        <v>2228.34206062287</v>
+      </c>
       <c r="D7" t="n">
         <v>9.515719999999999e-08</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1656.602</v>
       </c>
+      <c r="C8" t="n">
+        <v>2209.425598645605</v>
+      </c>
       <c r="D8" t="n">
         <v>9.51519e-08</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1629.087</v>
       </c>
+      <c r="C9" t="n">
+        <v>2181.033243968588</v>
+      </c>
       <c r="D9" t="n">
         <v>9.51472e-08</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1605.65</v>
       </c>
+      <c r="C10" t="n">
+        <v>2160.896095637971</v>
+      </c>
       <c r="D10" t="n">
         <v>9.517799999999999e-08</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1591.787</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2146.84285664637</v>
       </c>
       <c r="D11" t="n">
         <v>9.52153e-08</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1836.084</v>
       </c>
+      <c r="C2" t="n">
+        <v>2416.260362128484</v>
+      </c>
       <c r="D2" t="n">
         <v>1.05005e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1724.814</v>
       </c>
+      <c r="C3" t="n">
+        <v>2269.610409548753</v>
+      </c>
       <c r="D3" t="n">
         <v>1.05161e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1680.562</v>
       </c>
+      <c r="C4" t="n">
+        <v>2222.612909261894</v>
+      </c>
       <c r="D4" t="n">
         <v>1.05226e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1651.756</v>
       </c>
+      <c r="C5" t="n">
+        <v>2196.26454088843</v>
+      </c>
       <c r="D5" t="n">
         <v>1.05291e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1629.905</v>
       </c>
+      <c r="C6" t="n">
+        <v>2171.800367113566</v>
+      </c>
       <c r="D6" t="n">
         <v>1.05335e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1605.689</v>
       </c>
+      <c r="C7" t="n">
+        <v>2149.105702838181</v>
+      </c>
       <c r="D7" t="n">
         <v>1.05377e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1585.731</v>
       </c>
+      <c r="C8" t="n">
+        <v>2130.586573605911</v>
+      </c>
       <c r="D8" t="n">
         <v>1.05451e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1569.091</v>
       </c>
+      <c r="C9" t="n">
+        <v>2111.894531285834</v>
+      </c>
       <c r="D9" t="n">
         <v>1.05481e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1549.136</v>
       </c>
+      <c r="C10" t="n">
+        <v>2092.255251465298</v>
+      </c>
       <c r="D10" t="n">
         <v>1.05533e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1534.242</v>
       </c>
+      <c r="C11" t="n">
+        <v>2076.254876305061</v>
+      </c>
       <c r="D11" t="n">
         <v>1.0555e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1526.608</v>
       </c>
+      <c r="C12" t="n">
+        <v>2068.59747328301</v>
+      </c>
       <c r="D12" t="n">
         <v>1.05571e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1508.257</v>
       </c>
+      <c r="C13" t="n">
+        <v>2050.013494612379</v>
+      </c>
       <c r="D13" t="n">
         <v>1.05597e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1492.967</v>
       </c>
+      <c r="C14" t="n">
+        <v>2034.994025393448</v>
+      </c>
       <c r="D14" t="n">
         <v>1.05623e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1488.134</v>
       </c>
+      <c r="C15" t="n">
+        <v>2026.795789431821</v>
+      </c>
       <c r="D15" t="n">
         <v>1.0563e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1473.284</v>
       </c>
+      <c r="C16" t="n">
+        <v>2013.878990535072</v>
+      </c>
       <c r="D16" t="n">
         <v>1.05636e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1458.505</v>
       </c>
+      <c r="C17" t="n">
+        <v>1997.679037173893</v>
+      </c>
       <c r="D17" t="n">
         <v>1.05674e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1438.01</v>
       </c>
+      <c r="C18" t="n">
+        <v>1979.842400349142</v>
+      </c>
       <c r="D18" t="n">
         <v>1.05681e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1423.579</v>
       </c>
+      <c r="C19" t="n">
+        <v>1965.682709813468</v>
+      </c>
       <c r="D19" t="n">
         <v>1.05718e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1399.36</v>
       </c>
+      <c r="C20" t="n">
+        <v>1941.293621683161</v>
+      </c>
       <c r="D20" t="n">
         <v>1.05747e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1399.741</v>
       </c>
+      <c r="C21" t="n">
+        <v>1937.826387600744</v>
+      </c>
       <c r="D21" t="n">
         <v>1.05768e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1386.226</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1925.444384468529</v>
       </c>
       <c r="D22" t="n">
         <v>1.05792e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1814.252</v>
       </c>
+      <c r="C2" t="n">
+        <v>2394.164746115504</v>
+      </c>
       <c r="D2" t="n">
         <v>9.624929999999999e-08</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1717.973</v>
       </c>
+      <c r="C3" t="n">
+        <v>2267.445670920733</v>
+      </c>
       <c r="D3" t="n">
         <v>9.5979e-08</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1680.069</v>
       </c>
+      <c r="C4" t="n">
+        <v>2227.607729271344</v>
+      </c>
       <c r="D4" t="n">
         <v>9.58995e-08</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1658.341</v>
       </c>
+      <c r="C5" t="n">
+        <v>2203.028510789203</v>
+      </c>
       <c r="D5" t="n">
         <v>9.586429999999999e-08</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1633.661</v>
       </c>
+      <c r="C6" t="n">
+        <v>2181.157258826046</v>
+      </c>
       <c r="D6" t="n">
         <v>9.58898e-08</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1609.625</v>
       </c>
+      <c r="C7" t="n">
+        <v>2158.562258981773</v>
+      </c>
       <c r="D7" t="n">
         <v>9.59227e-08</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1582.947</v>
       </c>
+      <c r="C8" t="n">
+        <v>2132.386541429509</v>
+      </c>
       <c r="D8" t="n">
         <v>9.594530000000001e-08</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1567.266</v>
       </c>
+      <c r="C9" t="n">
+        <v>2116.939254523751</v>
+      </c>
       <c r="D9" t="n">
         <v>9.5998e-08</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1539.483</v>
       </c>
+      <c r="C10" t="n">
+        <v>2088.676622521903</v>
+      </c>
       <c r="D10" t="n">
         <v>9.60494e-08</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1507.92</v>
       </c>
+      <c r="C11" t="n">
+        <v>2061.476011915243</v>
+      </c>
       <c r="D11" t="n">
         <v>9.61057e-08</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1494.158</v>
       </c>
+      <c r="C12" t="n">
+        <v>2045.734835233415</v>
+      </c>
       <c r="D12" t="n">
         <v>9.61588e-08</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1476.015</v>
       </c>
+      <c r="C13" t="n">
+        <v>2026.680529995794</v>
+      </c>
       <c r="D13" t="n">
         <v>9.61873e-08</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1459.38</v>
       </c>
+      <c r="C14" t="n">
+        <v>2010.165022646152</v>
+      </c>
       <c r="D14" t="n">
         <v>9.62606e-08</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1451.144</v>
       </c>
+      <c r="C15" t="n">
+        <v>1999.675242782686</v>
+      </c>
       <c r="D15" t="n">
         <v>9.63104e-08</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1433.17</v>
       </c>
+      <c r="C16" t="n">
+        <v>1982.138742696403</v>
+      </c>
       <c r="D16" t="n">
         <v>9.632859999999999e-08</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1403.502</v>
       </c>
+      <c r="C17" t="n">
+        <v>1953.423809648053</v>
+      </c>
       <c r="D17" t="n">
         <v>9.638560000000001e-08</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1399.118</v>
       </c>
+      <c r="C18" t="n">
+        <v>1945.695730102676</v>
+      </c>
       <c r="D18" t="n">
         <v>9.642870000000001e-08</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1379.15</v>
       </c>
+      <c r="C19" t="n">
+        <v>1926.151346075597</v>
+      </c>
       <c r="D19" t="n">
         <v>9.645660000000001e-08</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1359.163</v>
       </c>
+      <c r="C20" t="n">
+        <v>1905.653165041942</v>
+      </c>
       <c r="D20" t="n">
         <v>9.64629e-08</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1348.709</v>
       </c>
+      <c r="C21" t="n">
+        <v>1894.475740269388</v>
+      </c>
       <c r="D21" t="n">
         <v>9.64984e-08</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1332.375</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1875.77742635839</v>
       </c>
       <c r="D22" t="n">
         <v>9.652589999999999e-08</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2171.352</v>
       </c>
+      <c r="C2" t="n">
+        <v>2825.950306961357</v>
+      </c>
       <c r="D2" t="n">
         <v>9.80773e-08</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1883.012</v>
       </c>
+      <c r="C3" t="n">
+        <v>2428.659283609369</v>
+      </c>
       <c r="D3" t="n">
         <v>9.83661e-08</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1804.97</v>
       </c>
+      <c r="C4" t="n">
+        <v>2341.314494364132</v>
+      </c>
       <c r="D4" t="n">
         <v>9.789380000000001e-08</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1770.276</v>
       </c>
+      <c r="C5" t="n">
+        <v>2307.655077018679</v>
+      </c>
       <c r="D5" t="n">
         <v>9.76139e-08</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1725.149</v>
       </c>
+      <c r="C6" t="n">
+        <v>2265.482235651575</v>
+      </c>
       <c r="D6" t="n">
         <v>9.74876e-08</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1694.95</v>
       </c>
+      <c r="C7" t="n">
+        <v>2236.852389713681</v>
+      </c>
       <c r="D7" t="n">
         <v>9.74243e-08</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1658.698</v>
       </c>
+      <c r="C8" t="n">
+        <v>2201.359077102462</v>
+      </c>
       <c r="D8" t="n">
         <v>9.741360000000001e-08</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1631.707</v>
       </c>
+      <c r="C9" t="n">
+        <v>2175.494354262195</v>
+      </c>
       <c r="D9" t="n">
         <v>9.74237e-08</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1599.709</v>
       </c>
+      <c r="C10" t="n">
+        <v>2145.337860559397</v>
+      </c>
       <c r="D10" t="n">
         <v>9.74664e-08</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1581.129</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2126.753607332737</v>
       </c>
       <c r="D11" t="n">
         <v>9.751959999999999e-08</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1854.921</v>
       </c>
+      <c r="C2" t="n">
+        <v>2451.84739346437</v>
+      </c>
       <c r="D2" t="n">
         <v>9.72135e-08</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1716.726</v>
       </c>
+      <c r="C3" t="n">
+        <v>2272.24661243234</v>
+      </c>
       <c r="D3" t="n">
         <v>9.65722e-08</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1681.905</v>
       </c>
+      <c r="C4" t="n">
+        <v>2233.096823700593</v>
+      </c>
       <c r="D4" t="n">
         <v>9.64161e-08</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1646.014</v>
       </c>
+      <c r="C5" t="n">
+        <v>2196.708333634479</v>
+      </c>
       <c r="D5" t="n">
         <v>9.63627e-08</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1627.187</v>
       </c>
+      <c r="C6" t="n">
+        <v>2177.647156022089</v>
+      </c>
       <c r="D6" t="n">
         <v>9.63395e-08</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1606.584</v>
       </c>
+      <c r="C7" t="n">
+        <v>2159.343010297847</v>
+      </c>
       <c r="D7" t="n">
         <v>9.63448e-08</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1589.029</v>
       </c>
+      <c r="C8" t="n">
+        <v>2138.555139486314</v>
+      </c>
       <c r="D8" t="n">
         <v>9.63549e-08</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1585.458</v>
       </c>
+      <c r="C9" t="n">
+        <v>2134.424257810192</v>
+      </c>
       <c r="D9" t="n">
         <v>9.64281e-08</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1564.309</v>
       </c>
+      <c r="C10" t="n">
+        <v>2113.973367760355</v>
+      </c>
       <c r="D10" t="n">
         <v>9.64436e-08</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1555.784</v>
       </c>
+      <c r="C11" t="n">
+        <v>2105.375018372568</v>
+      </c>
       <c r="D11" t="n">
         <v>9.648890000000001e-08</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1538.178</v>
       </c>
+      <c r="C12" t="n">
+        <v>2085.035612059058</v>
+      </c>
       <c r="D12" t="n">
         <v>9.65104e-08</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1524.082</v>
       </c>
+      <c r="C13" t="n">
+        <v>2071.310852097841</v>
+      </c>
       <c r="D13" t="n">
         <v>9.65556e-08</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1517.797</v>
       </c>
+      <c r="C14" t="n">
+        <v>2062.431573858107</v>
+      </c>
       <c r="D14" t="n">
         <v>9.65881e-08</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1489.285</v>
       </c>
+      <c r="C15" t="n">
+        <v>2035.369423316869</v>
+      </c>
       <c r="D15" t="n">
         <v>9.65832e-08</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1489.337</v>
       </c>
+      <c r="C16" t="n">
+        <v>2037.241983417567</v>
+      </c>
       <c r="D16" t="n">
         <v>9.66049e-08</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1477.017</v>
       </c>
+      <c r="C17" t="n">
+        <v>2021.334513825051</v>
+      </c>
       <c r="D17" t="n">
         <v>9.663550000000001e-08</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1459.828</v>
       </c>
+      <c r="C18" t="n">
+        <v>2005.858219299926</v>
+      </c>
       <c r="D18" t="n">
         <v>9.66478e-08</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1448.405</v>
       </c>
+      <c r="C19" t="n">
+        <v>1992.860517170389</v>
+      </c>
       <c r="D19" t="n">
         <v>9.66655e-08</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1423.77</v>
       </c>
+      <c r="C20" t="n">
+        <v>1967.034533600744</v>
+      </c>
       <c r="D20" t="n">
         <v>9.67068e-08</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1417.283</v>
       </c>
+      <c r="C21" t="n">
+        <v>1960.784483776245</v>
+      </c>
       <c r="D21" t="n">
         <v>9.67213e-08</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1385.385</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1929.794985102345</v>
       </c>
       <c r="D22" t="n">
         <v>9.67732e-08</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2100.214</v>
       </c>
+      <c r="C2" t="n">
+        <v>2723.098738722164</v>
+      </c>
       <c r="D2" t="n">
         <v>9.88663e-08</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1853.215</v>
       </c>
+      <c r="C3" t="n">
+        <v>2397.350677468669</v>
+      </c>
       <c r="D3" t="n">
         <v>9.8513e-08</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1789.613</v>
       </c>
+      <c r="C4" t="n">
+        <v>2324.20064477398</v>
+      </c>
       <c r="D4" t="n">
         <v>9.78979e-08</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1742.008</v>
       </c>
+      <c r="C5" t="n">
+        <v>2281.813705378237</v>
+      </c>
       <c r="D5" t="n">
         <v>9.75794e-08</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1716.142</v>
       </c>
+      <c r="C6" t="n">
+        <v>2252.136113383015</v>
+      </c>
       <c r="D6" t="n">
         <v>9.743639999999999e-08</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1693.865</v>
       </c>
+      <c r="C7" t="n">
+        <v>2231.458155510998</v>
+      </c>
       <c r="D7" t="n">
         <v>9.736049999999999e-08</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1649.548</v>
       </c>
+      <c r="C8" t="n">
+        <v>2190.47202695421</v>
+      </c>
       <c r="D8" t="n">
         <v>9.73717e-08</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1619</v>
       </c>
+      <c r="C9" t="n">
+        <v>2161.926391377645</v>
+      </c>
       <c r="D9" t="n">
         <v>9.740380000000001e-08</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1595.559</v>
       </c>
+      <c r="C10" t="n">
+        <v>2135.889147576366</v>
+      </c>
       <c r="D10" t="n">
         <v>9.74456e-08</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1575.763</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2115.850594550865</v>
       </c>
       <c r="D11" t="n">
         <v>9.74979e-08</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1859.949</v>
       </c>
+      <c r="C2" t="n">
+        <v>2443.111594873936</v>
+      </c>
       <c r="D2" t="n">
         <v>9.90408e-08</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1741.006</v>
       </c>
+      <c r="C3" t="n">
+        <v>2282.426798404507</v>
+      </c>
       <c r="D3" t="n">
         <v>9.80772e-08</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1702.215</v>
       </c>
+      <c r="C4" t="n">
+        <v>2238.240701795656</v>
+      </c>
       <c r="D4" t="n">
         <v>9.79225e-08</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1669.613</v>
       </c>
+      <c r="C5" t="n">
+        <v>2208.060119262033</v>
+      </c>
       <c r="D5" t="n">
         <v>9.79507e-08</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1648.179</v>
       </c>
+      <c r="C6" t="n">
+        <v>2189.236327510585</v>
+      </c>
       <c r="D6" t="n">
         <v>9.80403e-08</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1622.917</v>
       </c>
+      <c r="C7" t="n">
+        <v>2164.028629197055</v>
+      </c>
       <c r="D7" t="n">
         <v>9.81352e-08</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1610.274</v>
       </c>
+      <c r="C8" t="n">
+        <v>2151.048206745976</v>
+      </c>
       <c r="D8" t="n">
         <v>9.821129999999999e-08</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1591.012</v>
       </c>
+      <c r="C9" t="n">
+        <v>2130.526914208027</v>
+      </c>
       <c r="D9" t="n">
         <v>9.82893e-08</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1573.55</v>
       </c>
+      <c r="C10" t="n">
+        <v>2114.849026581153</v>
+      </c>
       <c r="D10" t="n">
         <v>9.83558e-08</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1546.478</v>
       </c>
+      <c r="C11" t="n">
+        <v>2088.135258999421</v>
+      </c>
       <c r="D11" t="n">
         <v>9.84276e-08</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1547.203</v>
       </c>
+      <c r="C12" t="n">
+        <v>2085.514726049872</v>
+      </c>
       <c r="D12" t="n">
         <v>9.8483e-08</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1515.979</v>
       </c>
+      <c r="C13" t="n">
+        <v>2054.257572987185</v>
+      </c>
       <c r="D13" t="n">
         <v>9.853999999999999e-08</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1511.163</v>
       </c>
+      <c r="C14" t="n">
+        <v>2049.962022481244</v>
+      </c>
       <c r="D14" t="n">
         <v>9.85804e-08</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1490.354</v>
       </c>
+      <c r="C15" t="n">
+        <v>2033.438023453771</v>
+      </c>
       <c r="D15" t="n">
         <v>9.861950000000001e-08</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1468.902</v>
       </c>
+      <c r="C16" t="n">
+        <v>2010.974585662378</v>
+      </c>
       <c r="D16" t="n">
         <v>9.86953e-08</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1450.005</v>
       </c>
+      <c r="C17" t="n">
+        <v>1988.782051381213</v>
+      </c>
       <c r="D17" t="n">
         <v>9.872379999999999e-08</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1440.09</v>
       </c>
+      <c r="C18" t="n">
+        <v>1979.304800250913</v>
+      </c>
       <c r="D18" t="n">
         <v>9.87643e-08</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1430.57</v>
       </c>
+      <c r="C19" t="n">
+        <v>1967.622275706751</v>
+      </c>
       <c r="D19" t="n">
         <v>9.8799e-08</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1415.333</v>
       </c>
+      <c r="C20" t="n">
+        <v>1953.002888861475</v>
+      </c>
       <c r="D20" t="n">
         <v>9.88563e-08</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1398.834</v>
       </c>
+      <c r="C21" t="n">
+        <v>1936.864508194354</v>
+      </c>
       <c r="D21" t="n">
         <v>9.8869e-08</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1372.83</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1911.036029610819</v>
       </c>
       <c r="D22" t="n">
         <v>9.88957e-08</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>1901.949</v>
       </c>
+      <c r="C2" t="n">
+        <v>2490.06709714313</v>
+      </c>
       <c r="D2" t="n">
         <v>1.02799e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1746.613</v>
       </c>
+      <c r="C3" t="n">
+        <v>2285.488776898233</v>
+      </c>
       <c r="D3" t="n">
         <v>1.01085e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1699.104</v>
       </c>
+      <c r="C4" t="n">
+        <v>2229.792932246197</v>
+      </c>
       <c r="D4" t="n">
         <v>1.00401e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1658.84</v>
       </c>
+      <c r="C5" t="n">
+        <v>2194.93890327516</v>
+      </c>
       <c r="D5" t="n">
         <v>1.00171e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1628.589</v>
       </c>
+      <c r="C6" t="n">
+        <v>2164.905344535497</v>
+      </c>
       <c r="D6" t="n">
         <v>1.00093e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1596.459</v>
       </c>
+      <c r="C7" t="n">
+        <v>2134.741542318</v>
+      </c>
       <c r="D7" t="n">
         <v>1.0013e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1573.1</v>
       </c>
+      <c r="C8" t="n">
+        <v>2112.018695471373</v>
+      </c>
       <c r="D8" t="n">
         <v>1.00175e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1546.414</v>
       </c>
+      <c r="C9" t="n">
+        <v>2083.8808935657</v>
+      </c>
       <c r="D9" t="n">
         <v>1.00236e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1531.022</v>
       </c>
+      <c r="C10" t="n">
+        <v>2065.927374453797</v>
+      </c>
       <c r="D10" t="n">
         <v>1.00323e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1503.517</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2043.732680664731</v>
       </c>
       <c r="D11" t="n">
         <v>1.00425e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1849.936</v>
       </c>
+      <c r="C2" t="n">
+        <v>2435.517943300861</v>
+      </c>
       <c r="D2" t="n">
         <v>1.04334e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1737.542</v>
       </c>
+      <c r="C3" t="n">
+        <v>2286.160727941884</v>
+      </c>
       <c r="D3" t="n">
         <v>1.01775e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1690.178</v>
       </c>
+      <c r="C4" t="n">
+        <v>2236.071836966913</v>
+      </c>
       <c r="D4" t="n">
         <v>1.01436e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1674.687</v>
       </c>
+      <c r="C5" t="n">
+        <v>2214.682100001874</v>
+      </c>
       <c r="D5" t="n">
         <v>1.01433e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1657.438</v>
       </c>
+      <c r="C6" t="n">
+        <v>2199.760361125655</v>
+      </c>
       <c r="D6" t="n">
         <v>1.01522e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1620.582</v>
       </c>
+      <c r="C7" t="n">
+        <v>2168.518987285596</v>
+      </c>
       <c r="D7" t="n">
         <v>1.01607e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1614.248</v>
       </c>
+      <c r="C8" t="n">
+        <v>2157.858902927871</v>
+      </c>
       <c r="D8" t="n">
         <v>1.01687e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1589.135</v>
       </c>
+      <c r="C9" t="n">
+        <v>2136.58030935374</v>
+      </c>
       <c r="D9" t="n">
         <v>1.01774e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1573.797</v>
       </c>
+      <c r="C10" t="n">
+        <v>2121.849966774515</v>
+      </c>
       <c r="D10" t="n">
         <v>1.01854e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1557.214</v>
       </c>
+      <c r="C11" t="n">
+        <v>2101.448854304762</v>
+      </c>
       <c r="D11" t="n">
         <v>1.01902e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1534.302</v>
       </c>
+      <c r="C12" t="n">
+        <v>2080.302694940596</v>
+      </c>
       <c r="D12" t="n">
         <v>1.01963e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1527.01</v>
       </c>
+      <c r="C13" t="n">
+        <v>2071.015174053372</v>
+      </c>
       <c r="D13" t="n">
         <v>1.02014e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1504.367</v>
       </c>
+      <c r="C14" t="n">
+        <v>2048.932304956159</v>
+      </c>
       <c r="D14" t="n">
         <v>1.02064e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1493.931</v>
       </c>
+      <c r="C15" t="n">
+        <v>2037.07354249604</v>
+      </c>
       <c r="D15" t="n">
         <v>1.02105e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1480.147</v>
       </c>
+      <c r="C16" t="n">
+        <v>2023.699190132939</v>
+      </c>
       <c r="D16" t="n">
         <v>1.02135e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1466.799</v>
       </c>
+      <c r="C17" t="n">
+        <v>2008.821568010644</v>
+      </c>
       <c r="D17" t="n">
         <v>1.02168e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1437.236</v>
       </c>
+      <c r="C18" t="n">
+        <v>1981.61313243641</v>
+      </c>
       <c r="D18" t="n">
         <v>1.02204e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1441.264</v>
       </c>
+      <c r="C19" t="n">
+        <v>1983.110090749402</v>
+      </c>
       <c r="D19" t="n">
         <v>1.02245e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1427.772</v>
       </c>
+      <c r="C20" t="n">
+        <v>1969.368119708464</v>
+      </c>
       <c r="D20" t="n">
         <v>1.02259e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1398.795</v>
       </c>
+      <c r="C21" t="n">
+        <v>1939.038454505945</v>
+      </c>
       <c r="D21" t="n">
         <v>1.02283e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1384.802</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1923.392788410255</v>
       </c>
       <c r="D22" t="n">
         <v>1.02313e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1559.477</v>
       </c>
+      <c r="C2" t="n">
+        <v>2312.574807807137</v>
+      </c>
       <c r="D2" t="n">
         <v>1.05842e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1297.737</v>
       </c>
+      <c r="C3" t="n">
+        <v>1902.136028898032</v>
+      </c>
       <c r="D3" t="n">
         <v>1.05331e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1239.304</v>
       </c>
+      <c r="C4" t="n">
+        <v>1827.987271113687</v>
+      </c>
       <c r="D4" t="n">
         <v>1.05269e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1217.375</v>
       </c>
+      <c r="C5" t="n">
+        <v>1804.914369665727</v>
+      </c>
       <c r="D5" t="n">
         <v>1.05424e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1181.601</v>
       </c>
+      <c r="C6" t="n">
+        <v>1769.41676104008</v>
+      </c>
       <c r="D6" t="n">
         <v>1.05608e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1158.17</v>
       </c>
+      <c r="C7" t="n">
+        <v>1747.117781222659</v>
+      </c>
       <c r="D7" t="n">
         <v>1.05822e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1145.558</v>
       </c>
+      <c r="C8" t="n">
+        <v>1738.395236141448</v>
+      </c>
       <c r="D8" t="n">
         <v>1.0607e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1119.845</v>
       </c>
+      <c r="C9" t="n">
+        <v>1711.423622922313</v>
+      </c>
       <c r="D9" t="n">
         <v>1.0626e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1104.321</v>
       </c>
+      <c r="C10" t="n">
+        <v>1696.310720595319</v>
+      </c>
       <c r="D10" t="n">
         <v>1.06462e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1081.877</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1673.314252988304</v>
       </c>
       <c r="D11" t="n">
         <v>1.06619e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -565,7 +565,7 @@
         <v>1957.236</v>
       </c>
       <c r="C2" t="n">
-        <v>2537.893314514995</v>
+        <v>873.3361019192233</v>
       </c>
       <c r="D2" t="n">
         <v>9.684039999999999e-08</v>
@@ -598,16 +598,13 @@
         <v>-15727.23503409055</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.080632580052182e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2802.239453311308</v>
+        <v>573.0817939208033</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000003123e-08</v>
+        <v>1.48199464244187e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8161890479173292</v>
+        <v>0.96848045589714</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>1817.878</v>
       </c>
       <c r="C3" t="n">
-        <v>2372.142000699871</v>
+        <v>6368.024383939443</v>
       </c>
       <c r="D3" t="n">
         <v>9.56945e-08</v>
@@ -651,10 +648,7 @@
         <v>-13996.82426852906</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.950350282412593e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2667.026421529901</v>
+        <v>-3901.929258916316</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001598e-08</v>
@@ -671,7 +665,7 @@
         <v>1774.953</v>
       </c>
       <c r="C4" t="n">
-        <v>2322.200893762289</v>
+        <v>7343.813689175114</v>
       </c>
       <c r="D4" t="n">
         <v>9.54046e-08</v>
@@ -704,10 +698,7 @@
         <v>-14736.30205345171</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.904923746523607e-07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2610.015283176012</v>
+        <v>-4960.575788765001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000101e-08</v>
@@ -724,7 +715,7 @@
         <v>1735.142</v>
       </c>
       <c r="C5" t="n">
-        <v>2285.798376519984</v>
+        <v>13034.93232822424</v>
       </c>
       <c r="D5" t="n">
         <v>9.52796e-08</v>
@@ -757,10 +748,7 @@
         <v>-13664.00322933267</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.851785725360481e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2570.230175119998</v>
+        <v>-10747.29459149242</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001147e-08</v>
@@ -777,7 +765,7 @@
         <v>1714.096</v>
       </c>
       <c r="C6" t="n">
-        <v>2263.415175637413</v>
+        <v>1958.104637714324</v>
       </c>
       <c r="D6" t="n">
         <v>9.51974e-08</v>
@@ -810,16 +798,13 @@
         <v>-14055.14574340741</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.394637800844841e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2536.645633999365</v>
+        <v>1.263577724684937</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>2.865725963952845e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8167631230097925</v>
+        <v>0.5454815836492499</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1679.517</v>
       </c>
       <c r="C7" t="n">
-        <v>2228.34206062287</v>
+        <v>1956.046389088657</v>
       </c>
       <c r="D7" t="n">
         <v>9.515719999999999e-08</v>
@@ -863,16 +848,13 @@
         <v>-12645.77171301273</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.537950428802318e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2504.78040946881</v>
+        <v>2.454732805781219</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>3.121125065595586e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.816862872176645</v>
+        <v>0.5402033045751623</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1656.602</v>
       </c>
       <c r="C8" t="n">
-        <v>2209.425598645605</v>
+        <v>8538.204169730918</v>
       </c>
       <c r="D8" t="n">
         <v>9.51519e-08</v>
@@ -916,10 +898,7 @@
         <v>-12428.94669676615</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.424484845822161e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2474.504905996447</v>
+        <v>1961.399133287689</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000022107e-08</v>
@@ -936,7 +915,7 @@
         <v>1629.087</v>
       </c>
       <c r="C9" t="n">
-        <v>2181.033243968588</v>
+        <v>4622.096776671618</v>
       </c>
       <c r="D9" t="n">
         <v>9.51472e-08</v>
@@ -969,10 +948,7 @@
         <v>-11963.91581649758</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.218083069425085e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2445.117948601374</v>
+        <v>1830.234860476461</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002113e-08</v>
@@ -989,7 +965,7 @@
         <v>1605.65</v>
       </c>
       <c r="C10" t="n">
-        <v>2160.896095637971</v>
+        <v>4652.02094654481</v>
       </c>
       <c r="D10" t="n">
         <v>9.517799999999999e-08</v>
@@ -1022,10 +998,7 @@
         <v>-11066.99855074649</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.743955955471329e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2416.910632523549</v>
+        <v>1805.871237339166</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000013692e-08</v>
@@ -1042,7 +1015,7 @@
         <v>1591.787</v>
       </c>
       <c r="C11" t="n">
-        <v>2146.84285664637</v>
+        <v>3575.004284858163</v>
       </c>
       <c r="D11" t="n">
         <v>9.52153e-08</v>
@@ -1075,10 +1048,7 @@
         <v>-11253.83144962725</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.620735479876497e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2389.6198397595</v>
+        <v>1699.9263664764</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000040143e-08</v>
@@ -1241,7 +1211,7 @@
         <v>1836.084</v>
       </c>
       <c r="C2" t="n">
-        <v>2416.260362128484</v>
+        <v>822.9783766741424</v>
       </c>
       <c r="D2" t="n">
         <v>1.05005e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-14531.52379694545</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.205509400413091e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2652.816355383428</v>
+        <v>608.1677228839006</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>1.883823431556822e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8164290424822086</v>
+        <v>0.9593916405620158</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1724.814</v>
       </c>
       <c r="C3" t="n">
-        <v>2269.610409548753</v>
+        <v>6506.415176081857</v>
       </c>
       <c r="D3" t="n">
         <v>1.05161e-07</v>
@@ -1327,10 +1294,7 @@
         <v>-15104.06592620119</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.926554895992382e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2535.796768424105</v>
+        <v>-4155.058684482121</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1347,7 +1311,7 @@
         <v>1680.562</v>
       </c>
       <c r="C4" t="n">
-        <v>2222.612909261894</v>
+        <v>6218.759317290942</v>
       </c>
       <c r="D4" t="n">
         <v>1.05226e-07</v>
@@ -1380,10 +1344,7 @@
         <v>-14320.8653249281</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.212245093627643e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2490.787529487453</v>
+        <v>-3908.524769206185</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -1400,7 +1361,7 @@
         <v>1651.756</v>
       </c>
       <c r="C5" t="n">
-        <v>2196.26454088843</v>
+        <v>6059.752794051262</v>
       </c>
       <c r="D5" t="n">
         <v>1.05291e-07</v>
@@ -1433,10 +1394,7 @@
         <v>-14041.20993973961</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.344720131362429e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2459.567312157532</v>
+        <v>-3776.918740621396</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000005e-08</v>
@@ -1453,7 +1411,7 @@
         <v>1629.905</v>
       </c>
       <c r="C6" t="n">
-        <v>2171.800367113566</v>
+        <v>5957.868253368471</v>
       </c>
       <c r="D6" t="n">
         <v>1.05335e-07</v>
@@ -1486,10 +1444,7 @@
         <v>-13919.00672417357</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.664310027760281e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2432.208839873017</v>
+        <v>-3699.526436087343</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000011593e-08</v>
@@ -1506,7 +1461,7 @@
         <v>1605.689</v>
       </c>
       <c r="C7" t="n">
-        <v>2149.105702838181</v>
+        <v>5958.660436796022</v>
       </c>
       <c r="D7" t="n">
         <v>1.05377e-07</v>
@@ -1539,10 +1494,7 @@
         <v>-13022.08877226029</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.900498580002884e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2407.354759170283</v>
+        <v>-3724.460929173092</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000071e-08</v>
@@ -1559,7 +1511,7 @@
         <v>1585.731</v>
       </c>
       <c r="C8" t="n">
-        <v>2130.586573605911</v>
+        <v>5969.08659032399</v>
       </c>
       <c r="D8" t="n">
         <v>1.05451e-07</v>
@@ -1592,10 +1544,7 @@
         <v>-12856.93658707621</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.052043104068951e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2384.044821637456</v>
+        <v>-3757.788185128586</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000201779e-08</v>
@@ -1612,7 +1561,7 @@
         <v>1569.091</v>
       </c>
       <c r="C9" t="n">
-        <v>2111.894531285834</v>
+        <v>6068.211285791519</v>
       </c>
       <c r="D9" t="n">
         <v>1.05481e-07</v>
@@ -1645,10 +1594,7 @@
         <v>-12830.07555650289</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.649142491406476e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2362.751824886014</v>
+        <v>-3880.054048539842</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000009025e-08</v>
@@ -1665,7 +1611,7 @@
         <v>1549.136</v>
       </c>
       <c r="C10" t="n">
-        <v>2092.255251465298</v>
+        <v>6119.391035529409</v>
       </c>
       <c r="D10" t="n">
         <v>1.05533e-07</v>
@@ -1698,10 +1644,7 @@
         <v>-12121.9023558993</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.908130286251949e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2343.211486301636</v>
+        <v>-3950.587296961548</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000067882e-08</v>
@@ -1718,7 +1661,7 @@
         <v>1534.242</v>
       </c>
       <c r="C11" t="n">
-        <v>2076.254876305061</v>
+        <v>6212.84552851977</v>
       </c>
       <c r="D11" t="n">
         <v>1.0555e-07</v>
@@ -1751,10 +1694,7 @@
         <v>-11836.7074318425</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.05937704701869e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2324.677621349778</v>
+        <v>-4063.772305777323</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000013e-08</v>
@@ -1771,7 +1711,7 @@
         <v>1526.608</v>
       </c>
       <c r="C12" t="n">
-        <v>2068.59747328301</v>
+        <v>6516.297097290804</v>
       </c>
       <c r="D12" t="n">
         <v>1.05571e-07</v>
@@ -1804,10 +1744,7 @@
         <v>-12418.7318184145</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.571729883172873e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2306.326090182869</v>
+        <v>-4390.580739820926</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000152832e-08</v>
@@ -1824,7 +1761,7 @@
         <v>1508.257</v>
       </c>
       <c r="C13" t="n">
-        <v>2050.013494612379</v>
+        <v>6556.400729526032</v>
       </c>
       <c r="D13" t="n">
         <v>1.05597e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-11455.12779674987</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.790366233193906e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2288.712336173526</v>
+        <v>-4447.812139353599</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000099389e-08</v>
@@ -1877,7 +1811,7 @@
         <v>1492.967</v>
       </c>
       <c r="C14" t="n">
-        <v>2034.994025393448</v>
+        <v>6801.650155604574</v>
       </c>
       <c r="D14" t="n">
         <v>1.05623e-07</v>
@@ -1910,10 +1844,7 @@
         <v>-11419.88564399849</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.849710405073938e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2271.346971401868</v>
+        <v>-4713.237935996391</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000002183e-08</v>
@@ -1930,7 +1861,7 @@
         <v>1488.134</v>
       </c>
       <c r="C15" t="n">
-        <v>2026.795789431821</v>
+        <v>7408.444302204326</v>
       </c>
       <c r="D15" t="n">
         <v>1.0563e-07</v>
@@ -1963,10 +1894,7 @@
         <v>-11759.36320920542</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.662643561047096e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2254.441781294051</v>
+        <v>-5347.026943917518</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000001e-08</v>
@@ -1983,7 +1911,7 @@
         <v>1473.284</v>
       </c>
       <c r="C16" t="n">
-        <v>2013.878990535072</v>
+        <v>7562.302568390683</v>
       </c>
       <c r="D16" t="n">
         <v>1.05636e-07</v>
@@ -2016,10 +1944,7 @@
         <v>-11207.44381029402</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.025842568782027e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2237.358463198035</v>
+        <v>-5518.429033757263</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000327e-08</v>
@@ -2036,7 +1961,7 @@
         <v>1458.505</v>
       </c>
       <c r="C17" t="n">
-        <v>1997.679037173893</v>
+        <v>7952.034434752853</v>
       </c>
       <c r="D17" t="n">
         <v>1.05674e-07</v>
@@ -2069,10 +1994,7 @@
         <v>-10969.49693665093</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.506004375871525e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2218.544026680097</v>
+        <v>-5930.144661375303</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2089,7 +2011,7 @@
         <v>1438.01</v>
       </c>
       <c r="C18" t="n">
-        <v>1979.842400349142</v>
+        <v>8549.92489353197</v>
       </c>
       <c r="D18" t="n">
         <v>1.05681e-07</v>
@@ -2122,10 +2044,7 @@
         <v>-10588.31972299025</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.106273292875994e-07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2199.208638576296</v>
+        <v>-6553.09814403996</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000030748e-08</v>
@@ -2142,7 +2061,7 @@
         <v>1423.579</v>
       </c>
       <c r="C19" t="n">
-        <v>1965.682709813468</v>
+        <v>9883.27452856542</v>
       </c>
       <c r="D19" t="n">
         <v>1.05718e-07</v>
@@ -2175,10 +2094,7 @@
         <v>-10171.74663262239</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.419850187548451e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2179.368621787795</v>
+        <v>-7917.241910459399</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2195,7 +2111,7 @@
         <v>1399.36</v>
       </c>
       <c r="C20" t="n">
-        <v>1941.293621683161</v>
+        <v>13655.39788781427</v>
       </c>
       <c r="D20" t="n">
         <v>1.05747e-07</v>
@@ -2228,10 +2144,7 @@
         <v>-9480.57087492682</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.047130096172059e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2160.272712394857</v>
+        <v>-11726.50097944143</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000263e-08</v>
@@ -2248,7 +2161,7 @@
         <v>1399.741</v>
       </c>
       <c r="C21" t="n">
-        <v>1937.826387600744</v>
+        <v>965.0319012187931</v>
       </c>
       <c r="D21" t="n">
         <v>1.05768e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-9881.312596649015</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.687192281668998e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2140.873516812504</v>
+        <v>260.898350067415</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000120302e-08</v>
+        <v>8.014300078516866e-10</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8206657821089919</v>
+        <v>0.9933412128357456</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1386.226</v>
       </c>
       <c r="C22" t="n">
-        <v>1925.444384468529</v>
+        <v>950.9780042256386</v>
       </c>
       <c r="D22" t="n">
         <v>1.05792e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-9141.055117616663</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.264954517345809e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2120.860802679746</v>
+        <v>252.7826834985036</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>6.945700894135587e-10</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.820957461140848</v>
+        <v>0.9982151301129225</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>1814.252</v>
       </c>
       <c r="C2" t="n">
-        <v>2394.164746115504</v>
+        <v>6571.759805655825</v>
       </c>
       <c r="D2" t="n">
         <v>9.624929999999999e-08</v>
@@ -2533,10 +2440,7 @@
         <v>-14030.21229415085</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.539789015139256e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2645.4919457626</v>
+        <v>-4102.967476299385</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -2553,7 +2457,7 @@
         <v>1717.973</v>
       </c>
       <c r="C3" t="n">
-        <v>2267.445670920733</v>
+        <v>7279.285415318862</v>
       </c>
       <c r="D3" t="n">
         <v>9.5979e-08</v>
@@ -2586,10 +2490,7 @@
         <v>-13842.95666542388</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.272677860425834e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2543.218713457283</v>
+        <v>-4950.258565347518</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000063277e-08</v>
@@ -2606,7 +2507,7 @@
         <v>1680.069</v>
       </c>
       <c r="C4" t="n">
-        <v>2227.607729271344</v>
+        <v>10998.54676827037</v>
       </c>
       <c r="D4" t="n">
         <v>9.58995e-08</v>
@@ -2639,10 +2540,7 @@
         <v>-13344.15301216381</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.053543146997756e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2501.368026914175</v>
+        <v>-8758.189080397236</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000022e-08</v>
@@ -2659,7 +2557,7 @@
         <v>1658.341</v>
       </c>
       <c r="C5" t="n">
-        <v>2203.028510789203</v>
+        <v>1934.036201932617</v>
       </c>
       <c r="D5" t="n">
         <v>9.586429999999999e-08</v>
@@ -2692,16 +2590,13 @@
         <v>-12883.50979965216</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.187792751825158e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2471.099133070812</v>
+        <v>1.490377772462623</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000182e-08</v>
+        <v>3.147650889853715e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8175913762229218</v>
+        <v>0.5402681389156279</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1633.661</v>
       </c>
       <c r="C6" t="n">
-        <v>2181.157258826046</v>
+        <v>9325.409167757225</v>
       </c>
       <c r="D6" t="n">
         <v>9.58898e-08</v>
@@ -2745,10 +2640,7 @@
         <v>-12517.65074811471</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.148872642765337e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2441.483833096495</v>
+        <v>1946.167785304166</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000021354e-08</v>
@@ -2765,7 +2657,7 @@
         <v>1609.625</v>
       </c>
       <c r="C7" t="n">
-        <v>2158.562258981773</v>
+        <v>9186.47600767758</v>
       </c>
       <c r="D7" t="n">
         <v>9.59227e-08</v>
@@ -2798,10 +2690,7 @@
         <v>-11979.17933148436</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.544833179621391e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2412.493819432607</v>
+        <v>1920.100832183371</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000011275e-08</v>
@@ -2818,7 +2707,7 @@
         <v>1582.947</v>
       </c>
       <c r="C8" t="n">
-        <v>2132.386541429509</v>
+        <v>5014.493112096318</v>
       </c>
       <c r="D8" t="n">
         <v>9.594530000000001e-08</v>
@@ -2851,10 +2740,7 @@
         <v>-11402.41242944528</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.479426259798415e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2383.802378626948</v>
+        <v>1801.446690782257</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000386943e-08</v>
@@ -2871,7 +2757,7 @@
         <v>1567.266</v>
       </c>
       <c r="C9" t="n">
-        <v>2116.939254523751</v>
+        <v>3735.700064635334</v>
       </c>
       <c r="D9" t="n">
         <v>9.5998e-08</v>
@@ -2904,10 +2790,7 @@
         <v>-11034.8764813468</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.567897819944889e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2355.290814508071</v>
+        <v>1695.04427501297</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000021e-08</v>
@@ -2924,7 +2807,7 @@
         <v>1539.483</v>
       </c>
       <c r="C10" t="n">
-        <v>2088.676622521903</v>
+        <v>3465.147106780258</v>
       </c>
       <c r="D10" t="n">
         <v>9.60494e-08</v>
@@ -2957,10 +2840,7 @@
         <v>-10435.68750078583</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.581782967803718e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2328.69973597662</v>
+        <v>1642.616133173698</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000162e-08</v>
@@ -2977,7 +2857,7 @@
         <v>1507.92</v>
       </c>
       <c r="C11" t="n">
-        <v>2061.476011915243</v>
+        <v>3242.422544139768</v>
       </c>
       <c r="D11" t="n">
         <v>9.61057e-08</v>
@@ -3010,10 +2890,7 @@
         <v>-9489.317125955242</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.878165230200405e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2303.031856226592</v>
+        <v>1591.769060015839</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000086677e-08</v>
@@ -3030,7 +2907,7 @@
         <v>1494.158</v>
       </c>
       <c r="C12" t="n">
-        <v>2045.734835233415</v>
+        <v>3092.370648776925</v>
       </c>
       <c r="D12" t="n">
         <v>9.61588e-08</v>
@@ -3063,10 +2940,7 @@
         <v>-9310.967628059669</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.898394540780897e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2277.953342403202</v>
+        <v>1546.64789296607</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000043942e-08</v>
@@ -3083,7 +2957,7 @@
         <v>1476.015</v>
       </c>
       <c r="C13" t="n">
-        <v>2026.680529995794</v>
+        <v>2955.404907479122</v>
       </c>
       <c r="D13" t="n">
         <v>9.61873e-08</v>
@@ -3116,10 +2990,7 @@
         <v>-8720.504584108672</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.073144087203971e-11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2254.016424429858</v>
+        <v>1502.631640701423</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -3136,7 +3007,7 @@
         <v>1459.38</v>
       </c>
       <c r="C14" t="n">
-        <v>2010.165022646152</v>
+        <v>2900.385018687055</v>
       </c>
       <c r="D14" t="n">
         <v>9.62606e-08</v>
@@ -3169,10 +3040,7 @@
         <v>-8058.743922769041</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.525846042948044e-07</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2231.339076593582</v>
+        <v>1469.885298794769</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000005142e-08</v>
@@ -3189,7 +3057,7 @@
         <v>1451.144</v>
       </c>
       <c r="C15" t="n">
-        <v>1999.675242782686</v>
+        <v>2832.976747008458</v>
       </c>
       <c r="D15" t="n">
         <v>9.63104e-08</v>
@@ -3222,10 +3090,7 @@
         <v>-6893.843963403062</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.496748599831116e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2208.739228182183</v>
+        <v>1436.069732060854</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3242,7 +3107,7 @@
         <v>1433.17</v>
       </c>
       <c r="C16" t="n">
-        <v>1982.138742696403</v>
+        <v>2784.447150729608</v>
       </c>
       <c r="D16" t="n">
         <v>9.632859999999999e-08</v>
@@ -3275,10 +3140,7 @@
         <v>-6260.118745598808</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.809198738748828e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2186.912322818807</v>
+        <v>1405.168195295373</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000023577e-08</v>
@@ -3295,7 +3157,7 @@
         <v>1403.502</v>
       </c>
       <c r="C17" t="n">
-        <v>1953.423809648053</v>
+        <v>2741.340999774729</v>
       </c>
       <c r="D17" t="n">
         <v>9.638560000000001e-08</v>
@@ -3328,10 +3190,7 @@
         <v>-6659.137677013047</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.056410063579411e-07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2165.798788532495</v>
+        <v>1376.024780792547</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000104934e-08</v>
@@ -3348,7 +3207,7 @@
         <v>1399.118</v>
       </c>
       <c r="C18" t="n">
-        <v>1945.695730102676</v>
+        <v>2737.441135006289</v>
       </c>
       <c r="D18" t="n">
         <v>9.642870000000001e-08</v>
@@ -3381,10 +3240,7 @@
         <v>-5059.27801755262</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.12674484447922e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2145.633565072945</v>
+        <v>1355.95695894625</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000056875e-08</v>
@@ -3401,7 +3257,7 @@
         <v>1379.15</v>
       </c>
       <c r="C19" t="n">
-        <v>1926.151346075597</v>
+        <v>2693.924769493029</v>
       </c>
       <c r="D19" t="n">
         <v>9.645660000000001e-08</v>
@@ -3434,10 +3290,7 @@
         <v>-5013.089439330403</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.406894532279455e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2125.834182320692</v>
+        <v>1325.766236935688</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000017028e-08</v>
@@ -3454,7 +3307,7 @@
         <v>1359.163</v>
       </c>
       <c r="C20" t="n">
-        <v>1905.653165041942</v>
+        <v>2678.042989504954</v>
       </c>
       <c r="D20" t="n">
         <v>9.64629e-08</v>
@@ -3487,10 +3340,7 @@
         <v>-4872.548960438281</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.05216978310343e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2106.696269590566</v>
+        <v>1304.27469237249</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000059e-08</v>
@@ -3507,7 +3357,7 @@
         <v>1348.709</v>
       </c>
       <c r="C21" t="n">
-        <v>1894.475740269388</v>
+        <v>2616.406567127424</v>
       </c>
       <c r="D21" t="n">
         <v>9.64984e-08</v>
@@ -3540,10 +3390,7 @@
         <v>-3613.793524151322</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.736925042440009e-07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2087.687086759841</v>
+        <v>1269.236091866318</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000390443e-08</v>
@@ -3560,7 +3407,7 @@
         <v>1332.375</v>
       </c>
       <c r="C22" t="n">
-        <v>1875.77742635839</v>
+        <v>2628.299288178809</v>
       </c>
       <c r="D22" t="n">
         <v>9.652589999999999e-08</v>
@@ -3593,10 +3440,7 @@
         <v>-3575.396579701583</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.881813102626941e-07</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2069.025207331233</v>
+        <v>1255.268733399051</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000004022e-08</v>
@@ -3759,7 +3603,7 @@
         <v>2171.352</v>
       </c>
       <c r="C2" t="n">
-        <v>2825.950306961357</v>
+        <v>998.8429964503713</v>
       </c>
       <c r="D2" t="n">
         <v>9.80773e-08</v>
@@ -3792,16 +3636,13 @@
         <v>-78760.15730880057</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.786831553088973e-07</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3011.390085308609</v>
+        <v>485.1751656763098</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000232958e-08</v>
+        <v>1.20825062506742e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8161385629375092</v>
+        <v>0.9671539807390376</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>1883.012</v>
       </c>
       <c r="C3" t="n">
-        <v>2428.659283609369</v>
+        <v>845.0865625131394</v>
       </c>
       <c r="D3" t="n">
         <v>9.83661e-08</v>
@@ -3845,16 +3686,13 @@
         <v>-21089.8647949108</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.233518091867686e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2717.953516990817</v>
+        <v>591.4873098658113</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000001024e-08</v>
+        <v>1.130867724204751e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8169989630959666</v>
+        <v>0.9879026157259312</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>1804.97</v>
       </c>
       <c r="C4" t="n">
-        <v>2341.314494364132</v>
+        <v>7910.921752555617</v>
       </c>
       <c r="D4" t="n">
         <v>9.789380000000001e-08</v>
@@ -3898,10 +3736,7 @@
         <v>-15220.71470400804</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.434306613700836e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2640.42276538133</v>
+        <v>-5490.566625461333</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000028616e-08</v>
@@ -3918,7 +3753,7 @@
         <v>1770.276</v>
       </c>
       <c r="C5" t="n">
-        <v>2307.655077018679</v>
+        <v>6665.573539337178</v>
       </c>
       <c r="D5" t="n">
         <v>9.76139e-08</v>
@@ -3951,10 +3786,7 @@
         <v>-15445.57309959872</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.711065944226108e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2592.826133116453</v>
+        <v>-4279.664681356302</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000041606e-08</v>
@@ -3971,7 +3803,7 @@
         <v>1725.149</v>
       </c>
       <c r="C6" t="n">
-        <v>2265.482235651575</v>
+        <v>7073.984828048609</v>
       </c>
       <c r="D6" t="n">
         <v>9.74876e-08</v>
@@ -4004,10 +3836,7 @@
         <v>-13852.93701736268</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.807054464653887e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2551.09613769508</v>
+        <v>-4740.173132103728</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000016451e-08</v>
@@ -4024,7 +3853,7 @@
         <v>1694.95</v>
       </c>
       <c r="C7" t="n">
-        <v>2236.852389713681</v>
+        <v>1466.055055681045</v>
       </c>
       <c r="D7" t="n">
         <v>9.74243e-08</v>
@@ -4057,16 +3886,13 @@
         <v>-13236.67640537149</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.612455610070082e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2512.0231756733</v>
+        <v>0.4519673825084409</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000107133e-08</v>
+        <v>2.766124725832324e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8175095380799655</v>
+        <v>0.8714284035861561</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1658.698</v>
       </c>
       <c r="C8" t="n">
-        <v>2201.359077102462</v>
+        <v>1924.997275128027</v>
       </c>
       <c r="D8" t="n">
         <v>9.741360000000001e-08</v>
@@ -4110,16 +3936,13 @@
         <v>-12411.65283345398</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.679975798242193e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2475.294392573575</v>
+        <v>0.8634623287131435</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000904e-08</v>
+        <v>3.010694017712615e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8176623878828427</v>
+        <v>0.5430379178518895</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1631.707</v>
       </c>
       <c r="C9" t="n">
-        <v>2175.494354262195</v>
+        <v>1920.683842357585</v>
       </c>
       <c r="D9" t="n">
         <v>9.74237e-08</v>
@@ -4163,16 +3986,13 @@
         <v>-11990.81323150786</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.294722738196046e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2440.997626481409</v>
+        <v>1.285048631474603</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000016248e-08</v>
+        <v>3.265256599008545e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8178330000012838</v>
+        <v>0.5380350968937849</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1599.709</v>
       </c>
       <c r="C10" t="n">
-        <v>2145.337860559397</v>
+        <v>9346.142210324762</v>
       </c>
       <c r="D10" t="n">
         <v>9.74664e-08</v>
@@ -4216,10 +4036,7 @@
         <v>-10973.14047150493</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.160217842635149e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2409.05635538728</v>
+        <v>1924.271056411402</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000025692e-08</v>
@@ -4236,7 +4053,7 @@
         <v>1581.129</v>
       </c>
       <c r="C11" t="n">
-        <v>2126.753607332737</v>
+        <v>5086.69847181857</v>
       </c>
       <c r="D11" t="n">
         <v>9.751959999999999e-08</v>
@@ -4269,10 +4086,7 @@
         <v>-11021.41217326432</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.799878448228988e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2379.12308594633</v>
+        <v>1810.019901973559</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000042e-08</v>
@@ -4435,7 +4249,7 @@
         <v>1854.921</v>
       </c>
       <c r="C2" t="n">
-        <v>2451.84739346437</v>
+        <v>828.177136304007</v>
       </c>
       <c r="D2" t="n">
         <v>9.72135e-08</v>
@@ -4468,16 +4282,13 @@
         <v>33683.17202914214</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.001697785037651e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2674.284493773773</v>
+        <v>558.5094203838427</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>9.599496558191981e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8165380297806613</v>
+        <v>0.9996760193013037</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1716.726</v>
       </c>
       <c r="C3" t="n">
-        <v>2272.24661243234</v>
+        <v>6800.926899628887</v>
       </c>
       <c r="D3" t="n">
         <v>9.65722e-08</v>
@@ -4521,10 +4332,7 @@
         <v>-13909.11086847288</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.527194843870823e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2543.438231911937</v>
+        <v>-4456.515723882958</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -4541,7 +4349,7 @@
         <v>1681.905</v>
       </c>
       <c r="C4" t="n">
-        <v>2233.096823700593</v>
+        <v>13142.17316970886</v>
       </c>
       <c r="D4" t="n">
         <v>9.64161e-08</v>
@@ -4574,10 +4382,7 @@
         <v>-14127.82846524425</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.73755727272483e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2498.320323195103</v>
+        <v>-10916.67346084535</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4594,7 +4399,7 @@
         <v>1646.014</v>
       </c>
       <c r="C5" t="n">
-        <v>2196.708333634479</v>
+        <v>1952.666332661396</v>
       </c>
       <c r="D5" t="n">
         <v>9.63627e-08</v>
@@ -4627,16 +4432,13 @@
         <v>-12395.1122341742</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.417716927405043e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2468.881075696555</v>
+        <v>3.269194991237041</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000226e-08</v>
+        <v>3.469523154793723e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.817003527336025</v>
+        <v>0.5335922407157588</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1627.187</v>
       </c>
       <c r="C6" t="n">
-        <v>2177.647156022089</v>
+        <v>6754.802890406514</v>
       </c>
       <c r="D6" t="n">
         <v>9.63395e-08</v>
@@ -4680,10 +4482,7 @@
         <v>-12233.19593743782</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.771905265476392e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2444.66050228381</v>
+        <v>1911.54878168612</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004754e-08</v>
@@ -4700,7 +4499,7 @@
         <v>1606.584</v>
       </c>
       <c r="C7" t="n">
-        <v>2159.343010297847</v>
+        <v>4243.287071666693</v>
       </c>
       <c r="D7" t="n">
         <v>9.63448e-08</v>
@@ -4733,10 +4532,7 @@
         <v>-11690.92654999617</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.054545805753066e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2422.261225547426</v>
+        <v>1796.513426510929</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018646e-08</v>
@@ -4753,7 +4549,7 @@
         <v>1589.029</v>
       </c>
       <c r="C8" t="n">
-        <v>2138.555139486314</v>
+        <v>3619.546432522609</v>
       </c>
       <c r="D8" t="n">
         <v>9.63549e-08</v>
@@ -4786,10 +4582,7 @@
         <v>-11359.06371320082</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.967864930265573e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2401.760521299128</v>
+        <v>1728.079556345813</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001124e-08</v>
@@ -4806,7 +4599,7 @@
         <v>1585.458</v>
       </c>
       <c r="C9" t="n">
-        <v>2134.424257810192</v>
+        <v>3476.459693438064</v>
       </c>
       <c r="D9" t="n">
         <v>9.64281e-08</v>
@@ -4839,10 +4632,7 @@
         <v>-11257.41373524666</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.151262931802478e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2382.859112404922</v>
+        <v>1696.680621646593</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000081e-08</v>
@@ -4859,7 +4649,7 @@
         <v>1564.309</v>
       </c>
       <c r="C10" t="n">
-        <v>2113.973367760355</v>
+        <v>3395.543805725841</v>
       </c>
       <c r="D10" t="n">
         <v>9.64436e-08</v>
@@ -4892,10 +4682,7 @@
         <v>-10869.38676452248</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.276352370959234e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2364.158321890183</v>
+        <v>1670.717363689663</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4912,7 +4699,7 @@
         <v>1555.784</v>
       </c>
       <c r="C11" t="n">
-        <v>2105.375018372568</v>
+        <v>3294.863051732693</v>
       </c>
       <c r="D11" t="n">
         <v>9.648890000000001e-08</v>
@@ -4945,10 +4732,7 @@
         <v>-10490.28538429595</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.213274958644838e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2346.350680881624</v>
+        <v>1642.387082497924</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000037979e-08</v>
@@ -4965,7 +4749,7 @@
         <v>1538.178</v>
       </c>
       <c r="C12" t="n">
-        <v>2085.035612059058</v>
+        <v>3056.896244911168</v>
       </c>
       <c r="D12" t="n">
         <v>9.65104e-08</v>
@@ -4998,10 +4782,7 @@
         <v>-9976.289598617124</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.285735264623511e-07</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2328.743438180887</v>
+        <v>1593.167865237745</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000062752e-08</v>
@@ -5018,7 +4799,7 @@
         <v>1524.082</v>
       </c>
       <c r="C13" t="n">
-        <v>2071.310852097841</v>
+        <v>2914.653205394185</v>
       </c>
       <c r="D13" t="n">
         <v>9.65556e-08</v>
@@ -5051,10 +4832,7 @@
         <v>-9821.918907996078</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.501943032585831e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2311.154004215749</v>
+        <v>1553.009446212786</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000003e-08</v>
@@ -5071,7 +4849,7 @@
         <v>1517.797</v>
       </c>
       <c r="C14" t="n">
-        <v>2062.431573858107</v>
+        <v>2873.448746245953</v>
       </c>
       <c r="D14" t="n">
         <v>9.65881e-08</v>
@@ -5104,10 +4882,7 @@
         <v>-9178.377094020414</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.082177876915714e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2294.221169055784</v>
+        <v>1528.497136104223</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000020636e-08</v>
@@ -5124,7 +4899,7 @@
         <v>1489.285</v>
       </c>
       <c r="C15" t="n">
-        <v>2035.369423316869</v>
+        <v>2865.415256947125</v>
       </c>
       <c r="D15" t="n">
         <v>9.65832e-08</v>
@@ -5157,10 +4932,7 @@
         <v>-8839.225052122372</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.708787579501874e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2276.695625055484</v>
+        <v>1510.891903283255</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000275e-08</v>
@@ -5177,7 +4949,7 @@
         <v>1489.337</v>
       </c>
       <c r="C16" t="n">
-        <v>2037.241983417567</v>
+        <v>2770.303731695532</v>
       </c>
       <c r="D16" t="n">
         <v>9.66049e-08</v>
@@ -5210,10 +4982,7 @@
         <v>-8187.16246258248</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.867870865145007e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2259.213562200337</v>
+        <v>1475.581757323268</v>
       </c>
       <c r="AA16" t="n">
         <v>1.00000000000057e-08</v>
@@ -5230,7 +4999,7 @@
         <v>1477.017</v>
       </c>
       <c r="C17" t="n">
-        <v>2021.334513825051</v>
+        <v>2714.308229446076</v>
       </c>
       <c r="D17" t="n">
         <v>9.663550000000001e-08</v>
@@ -5263,10 +5032,7 @@
         <v>-7598.949092311984</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.6082566251541e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2240.449683571833</v>
+        <v>1445.542092093258</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -5283,7 +5049,7 @@
         <v>1459.828</v>
       </c>
       <c r="C18" t="n">
-        <v>2005.858219299926</v>
+        <v>2700.814787465922</v>
       </c>
       <c r="D18" t="n">
         <v>9.66478e-08</v>
@@ -5316,10 +5082,7 @@
         <v>-7095.70000561196</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.582652997610923e-07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2221.403972757881</v>
+        <v>1425.096982171806</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000073e-08</v>
@@ -5336,7 +5099,7 @@
         <v>1448.405</v>
       </c>
       <c r="C19" t="n">
-        <v>1992.860517170389</v>
+        <v>2618.785221001118</v>
       </c>
       <c r="D19" t="n">
         <v>9.66655e-08</v>
@@ -5369,10 +5132,7 @@
         <v>-6174.36839395098</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.218837313543849e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2201.693149781671</v>
+        <v>1385.71725449831</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -5389,7 +5149,7 @@
         <v>1423.77</v>
       </c>
       <c r="C20" t="n">
-        <v>1967.034533600744</v>
+        <v>2626.586743284578</v>
       </c>
       <c r="D20" t="n">
         <v>9.67068e-08</v>
@@ -5422,10 +5182,7 @@
         <v>-6777.427021364794</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.369674985823065e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2182.224619966437</v>
+        <v>1369.885119493465</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -5442,7 +5199,7 @@
         <v>1417.283</v>
       </c>
       <c r="C21" t="n">
-        <v>1960.784483776245</v>
+        <v>2631.15116267477</v>
       </c>
       <c r="D21" t="n">
         <v>9.67213e-08</v>
@@ -5475,10 +5232,7 @@
         <v>-4924.697935117063</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.751548373145456e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2162.633245764146</v>
+        <v>1352.055661266358</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000292301e-08</v>
@@ -5495,7 +5249,7 @@
         <v>1385.385</v>
       </c>
       <c r="C22" t="n">
-        <v>1929.794985102345</v>
+        <v>2602.677741142464</v>
       </c>
       <c r="D22" t="n">
         <v>9.67732e-08</v>
@@ -5528,10 +5282,7 @@
         <v>-6064.797403531207</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.608922912703149e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2142.888228635001</v>
+        <v>1325.860797517912</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5694,7 +5445,7 @@
         <v>2100.214</v>
       </c>
       <c r="C2" t="n">
-        <v>2723.098738722164</v>
+        <v>1007.411605750975</v>
       </c>
       <c r="D2" t="n">
         <v>9.88663e-08</v>
@@ -5727,16 +5478,13 @@
         <v>-71616.06502077462</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.117751497835266e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2936.677572140641</v>
+        <v>453.381864523375</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000012968e-08</v>
+        <v>7.35411196190836e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8164851991062217</v>
+        <v>0.9972975256267533</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>1853.215</v>
       </c>
       <c r="C3" t="n">
-        <v>2397.350677468669</v>
+        <v>836.2835545857145</v>
       </c>
       <c r="D3" t="n">
         <v>9.8513e-08</v>
@@ -5780,16 +5528,13 @@
         <v>-45061.81952303981</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.958086466774596e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2692.242874545106</v>
+        <v>593.4942159030843</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000014577e-08</v>
+        <v>1.244541083635182e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8172474918555485</v>
+        <v>0.9865765071642146</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>1789.613</v>
       </c>
       <c r="C4" t="n">
-        <v>2324.20064477398</v>
+        <v>8618.533760567359</v>
       </c>
       <c r="D4" t="n">
         <v>9.78979e-08</v>
@@ -5833,10 +5578,7 @@
         <v>-15106.11296741202</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.247089447767962e-07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2618.150634152249</v>
+        <v>-6223.060529998322</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000153e-08</v>
@@ -5853,7 +5595,7 @@
         <v>1742.008</v>
       </c>
       <c r="C5" t="n">
-        <v>2281.813705378237</v>
+        <v>6724.85809708416</v>
       </c>
       <c r="D5" t="n">
         <v>9.75794e-08</v>
@@ -5886,10 +5628,7 @@
         <v>-13932.58900800227</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.635158269243158e-07</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2572.52477865014</v>
+        <v>-4352.4082861685</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000034e-08</v>
@@ -5906,7 +5645,7 @@
         <v>1716.142</v>
       </c>
       <c r="C6" t="n">
-        <v>2252.136113383015</v>
+        <v>6878.138745546041</v>
       </c>
       <c r="D6" t="n">
         <v>9.743639999999999e-08</v>
@@ -5939,10 +5678,7 @@
         <v>-13786.63331417237</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.416893742440481e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2533.289867695818</v>
+        <v>-4552.967864033299</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000174e-08</v>
@@ -5959,7 +5695,7 @@
         <v>1693.865</v>
       </c>
       <c r="C7" t="n">
-        <v>2231.458155510998</v>
+        <v>7634.030418760689</v>
       </c>
       <c r="D7" t="n">
         <v>9.736049999999999e-08</v>
@@ -5992,10 +5728,7 @@
         <v>-14050.34403228993</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.678018887649372e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2495.576749485846</v>
+        <v>-5360.154599094369</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001539e-08</v>
@@ -6012,7 +5745,7 @@
         <v>1649.548</v>
       </c>
       <c r="C8" t="n">
-        <v>2190.47202695421</v>
+        <v>9174.100943329515</v>
       </c>
       <c r="D8" t="n">
         <v>9.73717e-08</v>
@@ -6045,10 +5778,7 @@
         <v>-12026.51762871698</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.064094262318908e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2459.577970474297</v>
+        <v>-6955.344230671587</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -6065,7 +5795,7 @@
         <v>1619</v>
       </c>
       <c r="C9" t="n">
-        <v>2161.926391377645</v>
+        <v>1889.716263848224</v>
       </c>
       <c r="D9" t="n">
         <v>9.740380000000001e-08</v>
@@ -6098,16 +5828,13 @@
         <v>-11913.14283832148</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.39092983260449e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2424.696558775766</v>
+        <v>6.756225964112622</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000007224e-08</v>
+        <v>3.022948570516386e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8184047662893781</v>
+        <v>0.5441282366533133</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1595.559</v>
       </c>
       <c r="C10" t="n">
-        <v>2135.889147576366</v>
+        <v>1895.677754758598</v>
       </c>
       <c r="D10" t="n">
         <v>9.74456e-08</v>
@@ -6151,16 +5878,13 @@
         <v>-11610.49288341105</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.211950006983975e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2392.166845779026</v>
+        <v>0.8929656472217011</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.00000000000021e-08</v>
+        <v>3.389721456958847e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8186232526962256</v>
+        <v>0.536366446627497</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1575.763</v>
       </c>
       <c r="C11" t="n">
-        <v>2115.850594550865</v>
+        <v>7210.320592097051</v>
       </c>
       <c r="D11" t="n">
         <v>9.74979e-08</v>
@@ -6204,10 +5928,7 @@
         <v>-11537.81654469432</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.579255153750097e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2361.411093080482</v>
+        <v>1856.84278603587</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000105e-08</v>
@@ -6370,7 +6091,7 @@
         <v>1859.949</v>
       </c>
       <c r="C2" t="n">
-        <v>2443.111594873936</v>
+        <v>832.9400487974185</v>
       </c>
       <c r="D2" t="n">
         <v>9.90408e-08</v>
@@ -6403,16 +6124,13 @@
         <v>-44562.78278374775</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.402656826550151e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2685.379793263403</v>
+        <v>578.4866040672539</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000025999e-08</v>
+        <v>1.013554385548276e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8174613803224149</v>
+        <v>0.9985220376399511</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1741.006</v>
       </c>
       <c r="C3" t="n">
-        <v>2282.426798404507</v>
+        <v>6571.908440874538</v>
       </c>
       <c r="D3" t="n">
         <v>9.80772e-08</v>
@@ -6456,10 +6174,7 @@
         <v>-14698.11016432498</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.230863358269388e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2556.398313011775</v>
+        <v>-4205.820868764429</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000461458e-08</v>
@@ -6476,7 +6191,7 @@
         <v>1702.215</v>
       </c>
       <c r="C4" t="n">
-        <v>2238.240701795656</v>
+        <v>6987.530758369259</v>
       </c>
       <c r="D4" t="n">
         <v>9.79225e-08</v>
@@ -6509,10 +6224,7 @@
         <v>-14157.44454605444</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.793223466398135e-07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2512.416219146788</v>
+        <v>-4684.593719564311</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000101e-08</v>
@@ -6529,7 +6241,7 @@
         <v>1669.613</v>
       </c>
       <c r="C5" t="n">
-        <v>2208.060119262033</v>
+        <v>8887.715921545154</v>
       </c>
       <c r="D5" t="n">
         <v>9.79507e-08</v>
@@ -6562,10 +6274,7 @@
         <v>-13346.76369863253</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.160967592451774e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2482.432594083486</v>
+        <v>-6644.909236175208</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000055893e-08</v>
@@ -6582,7 +6291,7 @@
         <v>1648.179</v>
       </c>
       <c r="C6" t="n">
-        <v>2189.236327510585</v>
+        <v>13052.43678673408</v>
       </c>
       <c r="D6" t="n">
         <v>9.80403e-08</v>
@@ -6615,10 +6324,7 @@
         <v>-13058.46990651315</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.488412954610819e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2456.274889146551</v>
+        <v>-10865.16122138412</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -6635,7 +6341,7 @@
         <v>1622.917</v>
       </c>
       <c r="C7" t="n">
-        <v>2164.028629197055</v>
+        <v>14177.9691022125</v>
       </c>
       <c r="D7" t="n">
         <v>9.81352e-08</v>
@@ -6668,10 +6374,7 @@
         <v>-11989.41641045902</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.680785128129256e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2431.055510540169</v>
+        <v>-12018.93438246068</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000118768e-08</v>
@@ -6688,7 +6391,7 @@
         <v>1610.274</v>
       </c>
       <c r="C8" t="n">
-        <v>2151.048206745976</v>
+        <v>1907.537721174777</v>
       </c>
       <c r="D8" t="n">
         <v>9.821129999999999e-08</v>
@@ -6721,16 +6424,13 @@
         <v>-12487.46503069001</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.275129944872111e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2407.007506266758</v>
+        <v>1.387289495964014</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.0000000000002e-08</v>
+        <v>3.440581736719949e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8182995252561174</v>
+        <v>0.5351354206893225</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1591.012</v>
       </c>
       <c r="C9" t="n">
-        <v>2130.526914208027</v>
+        <v>829.6210769741105</v>
       </c>
       <c r="D9" t="n">
         <v>9.82893e-08</v>
@@ -6774,16 +6474,13 @@
         <v>-11839.36444176706</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.338815598007196e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2383.483686951633</v>
+        <v>538.2369830008016</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000079e-08</v>
+        <v>1.969551834559246e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.818506955335304</v>
+        <v>0.955978471178752</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1573.55</v>
       </c>
       <c r="C10" t="n">
-        <v>2114.849026581153</v>
+        <v>9240.710905903992</v>
       </c>
       <c r="D10" t="n">
         <v>9.83558e-08</v>
@@ -6827,10 +6524,7 @@
         <v>-11661.33753679387</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146485842324968e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2361.323694518063</v>
+        <v>1887.25233069701</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -6847,7 +6541,7 @@
         <v>1546.478</v>
       </c>
       <c r="C11" t="n">
-        <v>2088.135258999421</v>
+        <v>5878.395619144563</v>
       </c>
       <c r="D11" t="n">
         <v>9.84276e-08</v>
@@ -6880,10 +6574,7 @@
         <v>-10739.33531980895</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.095200877837401e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2339.502033475297</v>
+        <v>1809.977097913655</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000026e-08</v>
@@ -6900,7 +6591,7 @@
         <v>1547.203</v>
       </c>
       <c r="C12" t="n">
-        <v>2085.514726049872</v>
+        <v>5237.758490092477</v>
       </c>
       <c r="D12" t="n">
         <v>9.8483e-08</v>
@@ -6933,10 +6624,7 @@
         <v>-10669.77870015526</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.424735591807638e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2318.517083546198</v>
+        <v>1770.834178573738</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000043376e-08</v>
@@ -6953,7 +6641,7 @@
         <v>1515.979</v>
       </c>
       <c r="C13" t="n">
-        <v>2054.257572987185</v>
+        <v>4225.442020878478</v>
       </c>
       <c r="D13" t="n">
         <v>9.853999999999999e-08</v>
@@ -6986,10 +6674,7 @@
         <v>-10029.73288370191</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.804969955157933e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2297.534806654126</v>
+        <v>1702.868595432123</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000059e-08</v>
@@ -7006,7 +6691,7 @@
         <v>1511.163</v>
       </c>
       <c r="C14" t="n">
-        <v>2049.962022481244</v>
+        <v>3957.628373121199</v>
       </c>
       <c r="D14" t="n">
         <v>9.85804e-08</v>
@@ -7039,10 +6724,7 @@
         <v>-9788.442375689649</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.747167029613001e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2277.033258264069</v>
+        <v>1666.842974150308</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000099e-08</v>
@@ -7059,7 +6741,7 @@
         <v>1490.354</v>
       </c>
       <c r="C15" t="n">
-        <v>2033.438023453771</v>
+        <v>3458.878123854689</v>
       </c>
       <c r="D15" t="n">
         <v>9.861950000000001e-08</v>
@@ -7092,10 +6774,7 @@
         <v>-9265.580539951061</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.505443976199296e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2256.68389540495</v>
+        <v>1606.046789439469</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000001436e-08</v>
@@ -7112,7 +6791,7 @@
         <v>1468.902</v>
       </c>
       <c r="C16" t="n">
-        <v>2010.974585662378</v>
+        <v>3374.302111233723</v>
       </c>
       <c r="D16" t="n">
         <v>9.86953e-08</v>
@@ -7145,10 +6824,7 @@
         <v>-8755.207892042818</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.171452398963669e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2237.076718461622</v>
+        <v>1578.120100012105</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000634e-08</v>
@@ -7165,7 +6841,7 @@
         <v>1450.005</v>
       </c>
       <c r="C17" t="n">
-        <v>1988.782051381213</v>
+        <v>3171.155151616557</v>
       </c>
       <c r="D17" t="n">
         <v>9.872379999999999e-08</v>
@@ -7198,10 +6874,7 @@
         <v>-8527.547761122863</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.623683741287399e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2217.190969365798</v>
+        <v>1535.963566133959</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000005e-08</v>
@@ -7218,7 +6891,7 @@
         <v>1440.09</v>
       </c>
       <c r="C18" t="n">
-        <v>1979.304800250913</v>
+        <v>2982.915639572986</v>
       </c>
       <c r="D18" t="n">
         <v>9.87643e-08</v>
@@ -7251,10 +6924,7 @@
         <v>-8047.945031695579</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.027216755665779e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2197.636825311049</v>
+        <v>1490.412576969645</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000001e-08</v>
@@ -7271,7 +6941,7 @@
         <v>1430.57</v>
       </c>
       <c r="C19" t="n">
-        <v>1967.622275706751</v>
+        <v>2947.83967048288</v>
       </c>
       <c r="D19" t="n">
         <v>9.8799e-08</v>
@@ -7304,10 +6974,7 @@
         <v>-7235.633427636122</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.143263996301135e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2178.145451127642</v>
+        <v>1467.305033638073</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000001557e-08</v>
@@ -7324,7 +6991,7 @@
         <v>1415.333</v>
       </c>
       <c r="C20" t="n">
-        <v>1953.002888861475</v>
+        <v>2830.791118528962</v>
       </c>
       <c r="D20" t="n">
         <v>9.88563e-08</v>
@@ -7357,10 +7024,7 @@
         <v>-6817.736554585192</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.118932855856586e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2158.628595517052</v>
+        <v>1428.436576653497</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000026e-08</v>
@@ -7377,7 +7041,7 @@
         <v>1398.834</v>
       </c>
       <c r="C21" t="n">
-        <v>1936.864508194354</v>
+        <v>2761.524088305264</v>
       </c>
       <c r="D21" t="n">
         <v>9.8869e-08</v>
@@ -7410,10 +7074,7 @@
         <v>-6511.877174778572</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.233822405465896e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2139.201116971368</v>
+        <v>1397.139226344128</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -7430,7 +7091,7 @@
         <v>1372.83</v>
       </c>
       <c r="C22" t="n">
-        <v>1911.036029610819</v>
+        <v>2831.549512667058</v>
       </c>
       <c r="D22" t="n">
         <v>9.88957e-08</v>
@@ -7463,10 +7124,7 @@
         <v>-6573.57496791219</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.555134227633539e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2119.861688745518</v>
+        <v>1392.877694497951</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -7629,7 +7287,7 @@
         <v>1901.949</v>
       </c>
       <c r="C2" t="n">
-        <v>2490.06709714313</v>
+        <v>966.1825069971585</v>
       </c>
       <c r="D2" t="n">
         <v>1.02799e-07</v>
@@ -7662,16 +7320,13 @@
         <v>-53974.71950945709</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.251675918735745e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2722.482513789381</v>
+        <v>454.1776802018673</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000017296e-08</v>
+        <v>1.162443554109494e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8176698051296899</v>
+        <v>0.9717857923666984</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7337,7 @@
         <v>1746.613</v>
       </c>
       <c r="C3" t="n">
-        <v>2285.488776898233</v>
+        <v>792.8621358467395</v>
       </c>
       <c r="D3" t="n">
         <v>1.01085e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-37551.0497807443</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.754931479180862e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2559.186523764559</v>
+        <v>575.1996805404691</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000242e-08</v>
+        <v>1.256895376192363e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8181856435898024</v>
+        <v>0.988596472493019</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1699.104</v>
       </c>
       <c r="C4" t="n">
-        <v>2229.792932246197</v>
+        <v>1250.817977751288</v>
       </c>
       <c r="D4" t="n">
         <v>1.00401e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-14514.85180401859</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.105581795386281e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2502.965694501199</v>
+        <v>77.49142923309122</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000528e-08</v>
+        <v>6.709519406823859e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8183769204677546</v>
+        <v>0.9769362704839883</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1658.84</v>
       </c>
       <c r="C5" t="n">
-        <v>2194.93890327516</v>
+        <v>6700.561567845892</v>
       </c>
       <c r="D5" t="n">
         <v>1.00171e-07</v>
@@ -7821,10 +7470,7 @@
         <v>-13542.28276559242</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.840245649741695e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2463.981582635214</v>
+        <v>-4427.542332039991</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -7841,7 +7487,7 @@
         <v>1628.589</v>
       </c>
       <c r="C6" t="n">
-        <v>2164.905344535497</v>
+        <v>6866.086310282053</v>
       </c>
       <c r="D6" t="n">
         <v>1.00093e-07</v>
@@ -7874,10 +7520,7 @@
         <v>-12568.92099399804</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.387716667712425e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2429.137587880458</v>
+        <v>-4634.939928634873</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -7894,7 +7537,7 @@
         <v>1596.459</v>
       </c>
       <c r="C7" t="n">
-        <v>2134.741542318</v>
+        <v>7826.932527476951</v>
       </c>
       <c r="D7" t="n">
         <v>1.0013e-07</v>
@@ -7927,10 +7570,7 @@
         <v>-11845.22419483523</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.180917416166401e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2394.527931064527</v>
+        <v>-5647.700876166102</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000134e-08</v>
@@ -7947,7 +7587,7 @@
         <v>1573.1</v>
       </c>
       <c r="C8" t="n">
-        <v>2112.018695471373</v>
+        <v>9455.44066018255</v>
       </c>
       <c r="D8" t="n">
         <v>1.00175e-07</v>
@@ -7980,10 +7620,7 @@
         <v>-11434.39076983167</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.053913792970128e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2361.365768513816</v>
+        <v>-7326.981426943008</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000253e-08</v>
@@ -8000,7 +7637,7 @@
         <v>1546.414</v>
       </c>
       <c r="C9" t="n">
-        <v>2083.8808935657</v>
+        <v>14301.6487362597</v>
       </c>
       <c r="D9" t="n">
         <v>1.00236e-07</v>
@@ -8033,10 +7670,7 @@
         <v>-11204.7051286297</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.541374099500187e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2329.457937274167</v>
+        <v>-12230.94439205659</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000164e-08</v>
@@ -8053,7 +7687,7 @@
         <v>1531.022</v>
       </c>
       <c r="C10" t="n">
-        <v>2065.927374453797</v>
+        <v>825.4694729822822</v>
       </c>
       <c r="D10" t="n">
         <v>1.00323e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-11062.34664654996</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.912619760139729e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2298.439170782339</v>
+        <v>474.3725562342455</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000010019e-08</v>
+        <v>1.045327313733626e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8195950159865549</v>
+        <v>0.9977242512433813</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1503.517</v>
       </c>
       <c r="C11" t="n">
-        <v>2043.732680664731</v>
+        <v>827.9582385552712</v>
       </c>
       <c r="D11" t="n">
         <v>1.00425e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-10468.77814691912</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.186783077225627e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2269.055220485489</v>
+        <v>486.4918885495715</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000006196e-08</v>
+        <v>1.729671086565759e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.81985115140063</v>
+        <v>0.9630146185421552</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>1849.936</v>
       </c>
       <c r="C2" t="n">
-        <v>2435.517943300861</v>
+        <v>889.9878956246775</v>
       </c>
       <c r="D2" t="n">
         <v>1.04334e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-67463.80481688313</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.183145902954188e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2686.390486970981</v>
+        <v>522.2046088747577</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000018286e-08</v>
+        <v>9.064677854600656e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8165520185062216</v>
+        <v>0.9989828102150307</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1737.542</v>
       </c>
       <c r="C3" t="n">
-        <v>2286.160727941884</v>
+        <v>1429.72638630008</v>
       </c>
       <c r="D3" t="n">
         <v>1.01775e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-14814.85070680051</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.111474521042406e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2560.684989515539</v>
+        <v>3.770685120007879</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000013943e-08</v>
+        <v>1.720985391445261e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8168337792095237</v>
+        <v>0.9024080132848591</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1690.178</v>
       </c>
       <c r="C4" t="n">
-        <v>2236.071836966913</v>
+        <v>6480.35273421254</v>
       </c>
       <c r="D4" t="n">
         <v>1.01436e-07</v>
@@ -8444,10 +8066,7 @@
         <v>-13853.59290068857</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71941888220926e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2516.113398311693</v>
+        <v>-4158.035911157398</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001757e-08</v>
@@ -8464,7 +8083,7 @@
         <v>1674.687</v>
       </c>
       <c r="C5" t="n">
-        <v>2214.682100001874</v>
+        <v>6377.843624704918</v>
       </c>
       <c r="D5" t="n">
         <v>1.01433e-07</v>
@@ -8497,10 +8116,7 @@
         <v>-14143.72172759192</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.457389973645242e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2487.330254789892</v>
+        <v>-4084.67620361874</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000577437e-08</v>
@@ -8517,7 +8133,7 @@
         <v>1657.438</v>
       </c>
       <c r="C6" t="n">
-        <v>2199.760361125655</v>
+        <v>6554.408897681636</v>
       </c>
       <c r="D6" t="n">
         <v>1.01522e-07</v>
@@ -8550,10 +8166,7 @@
         <v>-14321.88272867534</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.031497483976484e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2461.543711295295</v>
+        <v>-4291.486608244251</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000019187e-08</v>
@@ -8570,7 +8183,7 @@
         <v>1620.582</v>
       </c>
       <c r="C7" t="n">
-        <v>2168.518987285596</v>
+        <v>6927.364743322851</v>
       </c>
       <c r="D7" t="n">
         <v>1.01607e-07</v>
@@ -8603,10 +8216,7 @@
         <v>-12160.6112450819</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.727864788294048e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2436.832044872622</v>
+        <v>-4696.697563433869</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003428e-08</v>
@@ -8623,7 +8233,7 @@
         <v>1614.248</v>
       </c>
       <c r="C8" t="n">
-        <v>2157.858902927871</v>
+        <v>7509.766178729214</v>
       </c>
       <c r="D8" t="n">
         <v>1.01687e-07</v>
@@ -8656,10 +8266,7 @@
         <v>-13435.87290284801</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.367192601541056e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2412.822244999396</v>
+        <v>-5311.884878220888</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000013e-08</v>
@@ -8676,7 +8283,7 @@
         <v>1589.135</v>
       </c>
       <c r="C9" t="n">
-        <v>2136.58030935374</v>
+        <v>7689.879297023005</v>
       </c>
       <c r="D9" t="n">
         <v>1.01774e-07</v>
@@ -8709,10 +8316,7 @@
         <v>-12348.74472933945</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.054996948110553e-07</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2389.72479508471</v>
+        <v>-5514.914883208974</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000046243e-08</v>
@@ -8729,7 +8333,7 @@
         <v>1573.797</v>
       </c>
       <c r="C10" t="n">
-        <v>2121.849966774515</v>
+        <v>8525.542762206354</v>
       </c>
       <c r="D10" t="n">
         <v>1.01854e-07</v>
@@ -8762,10 +8366,7 @@
         <v>-12155.25681238084</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.024568131383995e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2367.4116501242</v>
+        <v>-6383.100584319337</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000006e-08</v>
@@ -8782,7 +8383,7 @@
         <v>1557.214</v>
       </c>
       <c r="C11" t="n">
-        <v>2101.448854304762</v>
+        <v>12039.09084932399</v>
       </c>
       <c r="D11" t="n">
         <v>1.01902e-07</v>
@@ -8815,10 +8416,7 @@
         <v>-11858.280242979</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.314009031061219e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2345.958731469249</v>
+        <v>-9945.237415699938</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000032e-08</v>
@@ -8835,7 +8433,7 @@
         <v>1534.302</v>
       </c>
       <c r="C12" t="n">
-        <v>2080.302694940596</v>
+        <v>11480.02996073723</v>
       </c>
       <c r="D12" t="n">
         <v>1.01963e-07</v>
@@ -8868,10 +8466,7 @@
         <v>-11095.67692918065</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.97857171440006e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2325.072926922543</v>
+        <v>-9401.506203558014</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000060638e-08</v>
@@ -8888,7 +8483,7 @@
         <v>1527.01</v>
       </c>
       <c r="C13" t="n">
-        <v>2071.015174053372</v>
+        <v>16452.75729209457</v>
       </c>
       <c r="D13" t="n">
         <v>1.02014e-07</v>
@@ -8921,10 +8516,7 @@
         <v>-11261.54318003224</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.705364797175104e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2304.474133319054</v>
+        <v>-14411.54745749171</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000004977e-08</v>
@@ -8941,7 +8533,7 @@
         <v>1504.367</v>
       </c>
       <c r="C14" t="n">
-        <v>2048.932304956159</v>
+        <v>853.8513011589231</v>
       </c>
       <c r="D14" t="n">
         <v>1.02064e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-10684.11138840195</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.029102557085396e-07</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2284.753928592743</v>
+        <v>446.0936346207775</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000340535e-08</v>
+        <v>9.942339535432457e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8187178637891661</v>
+        <v>0.9964705040936501</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1493.931</v>
       </c>
       <c r="C15" t="n">
-        <v>2037.07354249604</v>
+        <v>854.7012617507893</v>
       </c>
       <c r="D15" t="n">
         <v>1.02105e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-10690.68072800848</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.666552701910998e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2265.661450334293</v>
+        <v>462.1703521802559</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000002183e-08</v>
+        <v>1.612101442933645e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8189684566732628</v>
+        <v>0.9620783546213757</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1480.147</v>
       </c>
       <c r="C16" t="n">
-        <v>2023.699190132939</v>
+        <v>1061.503358094628</v>
       </c>
       <c r="D16" t="n">
         <v>1.02135e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-10226.30673371317</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.761022622635242e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2246.900968461987</v>
+        <v>216.3519586801979</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000041311e-08</v>
+        <v>1.073669498462169e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8192341039442174</v>
+        <v>0.9633621810676111</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1466.799</v>
       </c>
       <c r="C17" t="n">
-        <v>2008.821568010644</v>
+        <v>1037.159826287174</v>
       </c>
       <c r="D17" t="n">
         <v>1.02168e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-9811.820734313953</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.314017394173889e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2227.580480675245</v>
+        <v>195.7815197033495</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>6.438036395858392e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8195014124726352</v>
+        <v>0.9991157359905396</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1437.236</v>
       </c>
       <c r="C18" t="n">
-        <v>1981.61313243641</v>
+        <v>13522.65579783177</v>
       </c>
       <c r="D18" t="n">
         <v>1.02204e-07</v>
@@ -9186,10 +8766,7 @@
         <v>-9094.208120553181</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.099807657802709e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2207.892732821187</v>
+        <v>1796.930099437322</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002956e-08</v>
@@ -9206,7 +8783,7 @@
         <v>1441.264</v>
       </c>
       <c r="C19" t="n">
-        <v>1983.110090749402</v>
+        <v>7854.40835194289</v>
       </c>
       <c r="D19" t="n">
         <v>1.02245e-07</v>
@@ -9239,10 +8816,7 @@
         <v>-8631.513384457108</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.073916530529249e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2188.466599121697</v>
+        <v>1736.564982669792</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9259,7 +8833,7 @@
         <v>1427.772</v>
       </c>
       <c r="C20" t="n">
-        <v>1969.368119708464</v>
+        <v>6861.054028545216</v>
       </c>
       <c r="D20" t="n">
         <v>1.02259e-07</v>
@@ -9292,10 +8866,7 @@
         <v>-8066.439876583923</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.222547217124628e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2169.165781966564</v>
+        <v>1703.619620102908</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000011e-08</v>
@@ -9312,7 +8883,7 @@
         <v>1398.795</v>
       </c>
       <c r="C21" t="n">
-        <v>1939.038454505945</v>
+        <v>6065.743454479982</v>
       </c>
       <c r="D21" t="n">
         <v>1.02283e-07</v>
@@ -9345,10 +8916,7 @@
         <v>-7918.459157029197</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.444047766692636e-07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2150.050766356738</v>
+        <v>1668.933553572794</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000037755e-08</v>
@@ -9365,7 +8933,7 @@
         <v>1384.802</v>
       </c>
       <c r="C22" t="n">
-        <v>1923.392788410255</v>
+        <v>13786.53371571041</v>
       </c>
       <c r="D22" t="n">
         <v>1.02313e-07</v>
@@ -9398,10 +8966,7 @@
         <v>-7840.941613102235</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.738667450564676e-07</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2131.369482436101</v>
+        <v>-11858.11335172926</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000109218e-08</v>
@@ -9564,7 +9129,7 @@
         <v>1559.477</v>
       </c>
       <c r="C2" t="n">
-        <v>2312.574807807137</v>
+        <v>739.9778774549121</v>
       </c>
       <c r="D2" t="n">
         <v>1.05842e-07</v>
@@ -9597,16 +9162,13 @@
         <v>-57740.79517774256</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.051247856185267e-07</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2294.017082802051</v>
+        <v>565.9060003362407</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000007539e-08</v>
+        <v>1.219292409558566e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8181831631597025</v>
+        <v>0.9895302778656663</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1297.737</v>
       </c>
       <c r="C3" t="n">
-        <v>1902.136028898032</v>
+        <v>9954.90957184425</v>
       </c>
       <c r="D3" t="n">
         <v>1.05331e-07</v>
@@ -9650,10 +9212,7 @@
         <v>6209.594969437313</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.712457392977619e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2051.599275085305</v>
+        <v>-8073.54890815898</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000011e-08</v>
@@ -9670,7 +9229,7 @@
         <v>1239.304</v>
       </c>
       <c r="C4" t="n">
-        <v>1827.987271113687</v>
+        <v>667.5402744499386</v>
       </c>
       <c r="D4" t="n">
         <v>1.05269e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-10347.03658303436</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.080458273433676e-07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1991.722397896727</v>
+        <v>563.33023858396</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000001464e-08</v>
+        <v>1.430016374758582e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.819023732765717</v>
+        <v>0.9971778754723727</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1217.375</v>
       </c>
       <c r="C5" t="n">
-        <v>1804.914369665727</v>
+        <v>7150.098061523608</v>
       </c>
       <c r="D5" t="n">
         <v>1.05424e-07</v>
@@ -9756,10 +9312,7 @@
         <v>-10223.29399243064</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.410662971559168e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1957.402345524185</v>
+        <v>-5308.811591595847</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002396e-08</v>
@@ -9776,7 +9329,7 @@
         <v>1181.601</v>
       </c>
       <c r="C6" t="n">
-        <v>1769.41676104008</v>
+        <v>7066.749771265028</v>
       </c>
       <c r="D6" t="n">
         <v>1.05608e-07</v>
@@ -9809,10 +9362,7 @@
         <v>-9147.921927695401</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.912706237936999e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1927.861782576359</v>
+        <v>-5253.503104669156</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9829,7 +9379,7 @@
         <v>1158.17</v>
       </c>
       <c r="C7" t="n">
-        <v>1747.117781222659</v>
+        <v>7134.881887331253</v>
       </c>
       <c r="D7" t="n">
         <v>1.05822e-07</v>
@@ -9862,10 +9412,7 @@
         <v>-8826.232647253944</v>
       </c>
       <c r="Y7" t="n">
-        <v>952.8512276116016</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1779851100.575519</v>
+        <v>-5350.953070930087</v>
       </c>
       <c r="AA7" t="n">
         <v>4.231634030276023e-07</v>
@@ -9882,7 +9429,7 @@
         <v>1145.558</v>
       </c>
       <c r="C8" t="n">
-        <v>1738.395236141448</v>
+        <v>7306.732942283248</v>
       </c>
       <c r="D8" t="n">
         <v>1.0607e-07</v>
@@ -9915,10 +9462,7 @@
         <v>-8838.227600150214</v>
       </c>
       <c r="Y8" t="n">
-        <v>910.5175082169267</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>273617289.6517155</v>
+        <v>-5550.757624240421</v>
       </c>
       <c r="AA8" t="n">
         <v>6.584274685941277e-07</v>
@@ -9935,7 +9479,7 @@
         <v>1119.845</v>
       </c>
       <c r="C9" t="n">
-        <v>1711.423622922313</v>
+        <v>7481.653514682367</v>
       </c>
       <c r="D9" t="n">
         <v>1.0626e-07</v>
@@ -9968,10 +9512,7 @@
         <v>-8135.038187212838</v>
       </c>
       <c r="Y9" t="n">
-        <v>906.7673291276271</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>232468487.862025</v>
+        <v>-5753.831672624248</v>
       </c>
       <c r="AA9" t="n">
         <v>6.099039348884555e-07</v>
@@ -9988,7 +9529,7 @@
         <v>1104.321</v>
       </c>
       <c r="C10" t="n">
-        <v>1696.310720595319</v>
+        <v>7901.130646926235</v>
       </c>
       <c r="D10" t="n">
         <v>1.06462e-07</v>
@@ -10021,10 +9562,7 @@
         <v>-7742.103527652958</v>
       </c>
       <c r="Y10" t="n">
-        <v>947.4125643243673</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>702965445.5312467</v>
+        <v>-6203.229366675925</v>
       </c>
       <c r="AA10" t="n">
         <v>3.240243778522406e-07</v>
@@ -10041,7 +9579,7 @@
         <v>1081.877</v>
       </c>
       <c r="C11" t="n">
-        <v>1673.314252988304</v>
+        <v>8073.130012013689</v>
       </c>
       <c r="D11" t="n">
         <v>1.06619e-07</v>
@@ -10074,10 +9612,7 @@
         <v>-7586.701877014153</v>
       </c>
       <c r="Y11" t="n">
-        <v>943.3992148990433</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>631947814.5222821</v>
+        <v>-6398.335062319954</v>
       </c>
       <c r="AA11" t="n">
         <v>3.062665850609764e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3365,6 +3365,566 @@
       </c>
       <c r="AD51" t="n">
         <v>0.9535623148081498</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1957.236</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2490.695431616286</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.684039999999999e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-81.73999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2464082806988297</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.065456564382695</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.808311007737921</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.00874385993695</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>81.60782704804083</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>6.778394084486807</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-15727.23503409055</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-24.16691658448508</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000003123e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8161890479173292</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1817.878</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.928798571046108</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2316.118145251856</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9299082159350404</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.56945e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-82.723</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.209911878579621</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5326187816257929</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.74938596575435</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.901539909549118</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.711666836141368</v>
+      </c>
+      <c r="M53" t="n">
+        <v>81.14125697098204</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>6.416089444416845</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-13996.82426852906</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-2.083799004395814</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000001598e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8165654469945532</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1774.953</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.906867133038632</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2255.801759480275</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9056915313071492</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.54046e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-83.047</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.2981711704284343</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.160196326418705</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.140866704231422</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.990574883511687</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>81.73160861482086</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>6.881324863281834</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-14736.30205345171</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.574251919631479</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8166515681835362</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1735.142</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8865267142030906</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2216.966631785988</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8900994491917193</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9.52796e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-83.255</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.08881987577638284</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.6166760145653803</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.81146618259224</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.043709091954853</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>81.25908569877066</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>6.503963809243431</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-13664.00322933267</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.411316126798056</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000001147e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.816683488194488</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1714.096</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8757737952909103</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2192.589427632244</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8803121408583494</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.51974e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-83.414</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.07380040201350339</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9824895076588682</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.094930141534711</v>
+      </c>
+      <c r="K56" t="n">
+        <v>148.6024802247455</v>
+      </c>
+      <c r="L56" t="n">
+        <v>16.40948733475846</v>
+      </c>
+      <c r="M56" t="n">
+        <v>81.58407020134409</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6.75898291607694</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-14055.14574340741</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.018123012928072</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8167631230097925</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1679.517</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8581065339080213</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2158.314695794248</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8665510316504871</v>
+      </c>
+      <c r="F57" t="n">
+        <v>9.515719999999999e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-83.535</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.08900785847456036</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6206488008115633</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.423896995470146</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.76433878048367</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>80.82287179736515</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6.189841522509957</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-12645.77171301273</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>6.121793081247915</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.816862872176645</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1656.602</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.846398696937927</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2136.754677437255</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8578948073352555</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.51519e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1719250643571295</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.172215164609002</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.944370792145309</v>
+      </c>
+      <c r="K58" t="n">
+        <v>99.71930588253194</v>
+      </c>
+      <c r="L58" t="n">
+        <v>13.78948298022853</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80.77470821132474</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.156964600332436</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-12428.94669676615</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4.703535327434793</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000022107e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8170062526080324</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1629.087</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.8323406068557907</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2110.104873404312</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8471950631213876</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9.51472e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-83.78</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3290674210841114</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.4609210184406642</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.659266979585766</v>
+      </c>
+      <c r="K59" t="n">
+        <v>123.3816088222879</v>
+      </c>
+      <c r="L59" t="n">
+        <v>12.9237346579996</v>
+      </c>
+      <c r="M59" t="n">
+        <v>80.54680279413365</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6.005898305563314</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11963.91581649758</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>5.61721806092828</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000002113e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8171981026411727</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1605.65</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.8203660672499383</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2087.19090480466</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8379952355114811</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9.517799999999999e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-83.869</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1872782362963178</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7056324719965327</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.598024832937826</v>
+      </c>
+      <c r="K60" t="n">
+        <v>163.1705869132753</v>
+      </c>
+      <c r="L60" t="n">
+        <v>13.20297201633247</v>
+      </c>
+      <c r="M60" t="n">
+        <v>79.9499842672588</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.642474761899186</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11066.99855074649</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>5.368146752630309</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000013692e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8173849821701255</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1591.787</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.8132831196646699</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2063.430118184225</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8284554152994947</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.52153e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6237956901773648</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.781425406388826</v>
+      </c>
+      <c r="J61" t="n">
+        <v>178.1658589114167</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.72517974260488</v>
+      </c>
+      <c r="L61" t="n">
+        <v>17.75493996409865</v>
+      </c>
+      <c r="M61" t="n">
+        <v>80.19763229919931</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5.787956472433362</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11253.83144962725</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>6.08401335663325</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000040143e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8175983326854956</v>
       </c>
     </row>
   </sheetData>
@@ -3378,7 +3938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AD127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9401,6 +9961,1182 @@
       </c>
       <c r="AD106" t="n">
         <v>0.8209574610682182</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1836.084</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2355.337816415195</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.05005e-07</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-81.492</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.2294850460880035</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.9117348194682676</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.382022521022515</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.96481337859651</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2.51316755848042</v>
+      </c>
+      <c r="M107" t="n">
+        <v>81.34705985591967</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>6.571121395343384</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-14531.52379694545</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-20.04196432912704</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.8164290424822086</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1724.814</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9393981974680897</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2205.304247198202</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9363006154907566</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.05161e-07</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-82.054</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.3846586601078535</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.2503263427891</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.384893305564139</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4.141879435883444</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>82.06379504898048</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>7.173313701032324</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-15104.06592620119</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-1.484694170833109</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.8167890851169918</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1680.562</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9152969036275028</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2158.596185671065</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9164698883646467</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.05226e-07</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-82.274</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.2397672969372497</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.009010407698981</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.002422501929528</v>
+      </c>
+      <c r="K109" t="n">
+        <v>4.112992077985594</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>81.80798960018973</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>6.946380567912005</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-14320.8653249281</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>1.33407103181753</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.8169176540291773</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1651.756</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.8996080789332078</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2132.103063131309</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.905221768305131</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.05291e-07</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-82.414</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.3501464651645957</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.9717721362737951</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.069455352377541</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.996827109048287</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>81.7535500828057</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6.89989047036303</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-14041.20993973961</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>1.382733742713981</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.8170249113027882</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1629.905</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.8877072072955268</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2105.285071239517</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.893835719261598</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.05335e-07</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-82.535</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.3686085134892848</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.89116369914952</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.926453288571458</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.93998286664764</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>81.77058638393777</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>6.914373410095767</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>-13919.00672417357</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>3.312782034281554</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.000000000011593e-08</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.8171670241063483</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1605.689</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8745182682273795</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2085.193743832154</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8853055936603618</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.05377e-07</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-82.631</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.1487730363654174</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.8383467530932587</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.626298478154131</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3.106449255987164</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>81.32543878358123</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>6.554491053336548</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-13022.08877226029</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>2.846915867641201</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.8173498152651262</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>10</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1585.731</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.8636483951714627</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2064.499055398605</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8765193005480444</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.05451e-07</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.2299338700590891</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.7143512204342742</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.070379490846969</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3.080394153878762</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>81.29900621639202</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>6.53427126770334</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-12856.93658707621</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>3.134258695881044</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.000000000201779e-08</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.8175382246741291</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1569.091</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.8545856289799376</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2048.447451013779</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.8697043102426384</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.05481e-07</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-82.83199999999999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.2545023264494192</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.177978654821514</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.731666160886648</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3.350571170729051</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>81.35220862018741</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>6.575093850844786</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-12830.07555650289</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>2.547092353861217</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.000000000009025e-08</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.8177361393076815</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1549.136</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.8437173898361948</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2031.575004608324</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8625408170537355</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.05533e-07</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-82.90900000000001</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.1920988709124505</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.7597588092186146</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.05545177468824</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2.638453666211698</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>80.95650726652701</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>6.282880365670981</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>-12121.9023558993</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>2.854886772038981</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.00000000067882e-08</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.8179322349113838</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1534.242</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.8356055605299103</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2012.18561384871</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8543087109734604</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.0555e-07</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-82.98099999999999</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.4984085124369117</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.607854202421477</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1.825480393688617</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2.556753500969978</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>80.82040280242383</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>6.188147845855583</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>-11836.7074318425</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>4.924105260245028</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.818146980576532</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1526.608</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8314477986845917</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1999.865001124833</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.849077778646891</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.05571e-07</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-83.057</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7324841365319408</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.405327996482811</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2.328669498677294</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4.232004389831275</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>81.28144585114816</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>6.520905598763334</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-12418.7318184145</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>3.309023266251529</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.000000000152832e-08</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.8183527964476967</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1508.257</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8214531579165223</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1986.576224743123</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8434357954506396</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.05597e-07</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-83.125</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.04733327142602921</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.920580467823689</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.844943631070001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2.672277950581289</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>80.66582593562056</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>6.083880243086495</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-11455.12779674987</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>2.761381188583414</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.000000000099389e-08</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8185770352402901</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1492.967</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.8131256522032762</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1972.641293634008</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8375194759265369</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.05623e-07</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-83.193</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.2782604091437579</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4801439799008048</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.52453563469924</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2.418167897778835</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>80.70512503046389</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>6.110062979920581</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-11419.88564399849</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3.071132511613655</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.8188130232065193</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>20</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1488.134</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8104934196910381</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1953.602790422775</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8294363453120888</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.0563e-07</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-83.26900000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.2696173664028442</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.085184214499734</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.159718663370333</v>
+      </c>
+      <c r="K120" t="n">
+        <v>161.5361781834394</v>
+      </c>
+      <c r="L120" t="n">
+        <v>13.23225507074418</v>
+      </c>
+      <c r="M120" t="n">
+        <v>81.01223314878425</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>6.322487996767297</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>-11759.36320920542</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>5.165050186870303</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.8190634983198728</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1473.284</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.8024055544299715</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1941.953242224178</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.824490325205161</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.05636e-07</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-83.32899999999999</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.5187671132853936</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1.347753456221208</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1.810854263797419</v>
+      </c>
+      <c r="K121" t="n">
+        <v>95.02163482108934</v>
+      </c>
+      <c r="L121" t="n">
+        <v>12.80203987389221</v>
+      </c>
+      <c r="M121" t="n">
+        <v>80.66484607984803</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>6.083230213197538</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-11207.44381029402</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>4.491451482685534</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.000000000000327e-08</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.8193162547204189</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1458.505</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7943563584236887</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1929.984235238838</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8194086732646523</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.05674e-07</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2997701145575761</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.9605998038662696</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2.018198539370903</v>
+      </c>
+      <c r="K122" t="n">
+        <v>117.7590066559949</v>
+      </c>
+      <c r="L122" t="n">
+        <v>12.01550196845362</v>
+      </c>
+      <c r="M122" t="n">
+        <v>80.5500727252478</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>6.008014701821815</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-10969.49693665093</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>2.610018537470978</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.8195739759225688</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1438.01</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7831940150886343</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1909.863433033482</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.8108660336207224</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.05681e-07</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-83.46899999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.1870019213098451</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.9469573745814291</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1.649445068294622</v>
+      </c>
+      <c r="K123" t="n">
+        <v>130.2858933423074</v>
+      </c>
+      <c r="L123" t="n">
+        <v>11.9785488939127</v>
+      </c>
+      <c r="M123" t="n">
+        <v>80.31281421458912</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>5.858129429053886</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-10588.31972299025</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>4.863599169619647</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.000000000030748e-08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.8198329197472933</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1423.579</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.7753343528945299</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1893.570978638052</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.8039487862170241</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.05718e-07</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-83.55</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.1217157933677126</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.06403055153623</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1.554126858888137</v>
+      </c>
+      <c r="K124" t="n">
+        <v>156.0368456143822</v>
+      </c>
+      <c r="L124" t="n">
+        <v>11.69193191600545</v>
+      </c>
+      <c r="M124" t="n">
+        <v>80.02813702653556</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>5.687613330801211</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-10171.74663262239</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>4.788368428660192</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8201046979891833</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1399.36</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7621437799142088</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1879.502418246399</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.797975732036174</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.05747e-07</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-83.636</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.03794074822452956</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5625863827636554</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2.304550078785692</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>16.54069689900615</v>
+      </c>
+      <c r="M125" t="n">
+        <v>79.44889331479698</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>5.368786864273599</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-9480.57087492682</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>4.242984877307549</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.00000000000263e-08</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.8203777163172912</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1399.741</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7623512867603007</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1865.403126760146</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7919896304298608</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.05768e-07</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.8069869720462988</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.9343169398906577</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2.561089956336871</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>14.4017455706923</v>
+      </c>
+      <c r="M126" t="n">
+        <v>79.91750698976013</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>5.623920632195568</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-9881.312596649015</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>3.627285961003167</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.000000000120302e-08</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.8206657821089919</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1386.226</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7549905124166433</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1845.577632265529</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7835723688564061</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.05792e-07</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-83.782</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.6534863945577725</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.9784512371289356</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2.79013894862836</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>14.93830358927775</v>
+      </c>
+      <c r="M127" t="n">
+        <v>79.26125899409929</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>5.272805740264764</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-9141.055117616663</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>4.727277035371003</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.820957461140848</v>
       </c>
     </row>
   </sheetData>
@@ -9414,7 +11150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AD127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15437,6 +17173,1182 @@
       </c>
       <c r="AD106" t="n">
         <v>0.8217586907038337</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1814.252</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2339.057964890725</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.624929999999999e-08</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-82.541</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.2199663514713317</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.5430347125919821</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.559088863125198</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2.859277521977673</v>
+      </c>
+      <c r="L107" t="n">
+        <v>6.371781080523672</v>
+      </c>
+      <c r="M107" t="n">
+        <v>81.16861795734711</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>6.436287350390533</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-14030.21229415085</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-16.08687997773086</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.8172228647327775</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1717.973</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.946931848497342</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2206.173324548646</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9431888211678897</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9.5979e-08</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.2190206085376029</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.8063177372918047</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1.442064191158716</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3.442142867555391</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>81.43477619218186</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>6.639445107112255</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-13842.95666542388</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>1.165618327657057</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1.000000000063277e-08</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.8174399678725334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1680.069</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9260394917574847</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2162.218222677857</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9243970244144294</v>
+      </c>
+      <c r="F109" t="n">
+        <v>9.58995e-08</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-83.39700000000001</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.1882749671647599</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.6417509285887323</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.011960917883008</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3.202052621258274</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>81.27911746970352</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>6.519137415136154</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-13344.15301216381</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>4.347303168778353</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.8175077489775567</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1658.341</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.9140632062139108</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2138.435894189785</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9142295429560625</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9.586429999999999e-08</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-83.54900000000001</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.3725479276760159</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.5033974455550557</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.133273462211748</v>
+      </c>
+      <c r="K110" t="n">
+        <v>106.2929094236003</v>
+      </c>
+      <c r="L110" t="n">
+        <v>14.70292033046309</v>
+      </c>
+      <c r="M110" t="n">
+        <v>81.08890683592003</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6.377787459526253</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-12883.50979965216</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>4.018949842580923</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.8175913762229218</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1633.661</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.9004598038199766</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2109.269229088876</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.901760136238187</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9.58898e-08</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-83.67700000000001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.5255914365273067</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.8388112922987668</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2.471447849005576</v>
+      </c>
+      <c r="K111" t="n">
+        <v>117.3699782833126</v>
+      </c>
+      <c r="L111" t="n">
+        <v>14.33176626959156</v>
+      </c>
+      <c r="M111" t="n">
+        <v>80.94242132094284</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>6.272945191355327</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>-12517.65074811471</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>5.580486405689498</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.000000000021354e-08</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.8177127484635036</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1609.625</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8872113686522048</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2083.455068001962</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8907240005483559</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.59227e-08</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.5263957367283191</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.6994297570443527</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2.374158659249447</v>
+      </c>
+      <c r="K112" t="n">
+        <v>38.83990851865718</v>
+      </c>
+      <c r="L112" t="n">
+        <v>15.04528357771289</v>
+      </c>
+      <c r="M112" t="n">
+        <v>80.66544031910878</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>6.083624411482382</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-11979.17933148436</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>6.492867149185258</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.000000000011275e-08</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.8178621643413874</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>10</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1582.947</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.8725066859510144</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2062.046726737374</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8815714521353077</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.594530000000001e-08</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-83.88800000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.1159678631247716</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.268364515548442</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1.672799835271107</v>
+      </c>
+      <c r="K113" t="n">
+        <v>187.9770402029174</v>
+      </c>
+      <c r="L113" t="n">
+        <v>12.66675223498165</v>
+      </c>
+      <c r="M113" t="n">
+        <v>80.33828804435977</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>5.873872752663535</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-11402.41242944528</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>5.306753407002134</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.000000000386943e-08</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.8180559343544889</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1567.266</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.8638634544704925</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2031.945921635717</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.868702679512538</v>
+      </c>
+      <c r="F114" t="n">
+        <v>9.5998e-08</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-83.999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.5637077412034458</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.194641851154163</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2.142102675327511</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>16.26723134778424</v>
+      </c>
+      <c r="M114" t="n">
+        <v>80.14307853878834</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>5.755287158325647</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-11034.8764813468</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>7.819278448108321</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.8182605588147898</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1539.483</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.8485497053331071</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2013.479934137071</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8608080536521189</v>
+      </c>
+      <c r="F115" t="n">
+        <v>9.60494e-08</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-84.10599999999999</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.2047974902549611</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.8174481656248804</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.023114955504484</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>13.87641558853618</v>
+      </c>
+      <c r="M115" t="n">
+        <v>79.73537743298156</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>5.522023777319139</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>-10435.68750078583</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>6.731098916767451</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.000000000000162e-08</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.818483972974807</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1507.92</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.8311524529117235</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1993.667597190265</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8523378330572517</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9.61057e-08</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-84.18600000000001</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.07314627817032779</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.8182027167092857</v>
+      </c>
+      <c r="J116" t="n">
+        <v>108.4230324087155</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3.117450240086721</v>
+      </c>
+      <c r="L116" t="n">
+        <v>17.66604575329081</v>
+      </c>
+      <c r="M116" t="n">
+        <v>78.91863691543492</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>5.105833053084565</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>-9489.317125955242</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>5.876635771557858</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.000000000086677e-08</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.8187105035549397</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1494.158</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8235669576222046</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1969.499310342414</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8420053457009667</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9.61588e-08</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-84.274</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.09275825574913091</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.229632643733593</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.67232430408463</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4.760114879320008</v>
+      </c>
+      <c r="L117" t="n">
+        <v>14.77705265714258</v>
+      </c>
+      <c r="M117" t="n">
+        <v>78.83031336632652</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>5.064430218133074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-9310.967628059669</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>7.446115734600539</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.000000000043942e-08</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.8189553136926873</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1476.015</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.813566693050359</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1954.801351333283</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8357216369473799</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.61873e-08</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-84.36499999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.2962648364452972</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.9005835056790648</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4.355019783095714</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3.607634364717111</v>
+      </c>
+      <c r="M118" t="n">
+        <v>78.25862137758851</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>4.811316464110353</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-8720.504584108672</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>5.216171439508798</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8192201606935929</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1459.38</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.8043976250267327</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1931.770085281579</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8258752516087506</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9.62606e-08</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-84.444</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.06492433219232048</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.014310593005116</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>5.239716276678986</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.01935456888561009</v>
+      </c>
+      <c r="M119" t="n">
+        <v>77.51182730448956</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>4.515119068603103</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-8058.743922769041</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>7.174486143270542</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.000000000005142e-08</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.8194724802478264</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>20</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1451.144</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.7998580131095349</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1917.336597696724</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8197046103499608</v>
+      </c>
+      <c r="F120" t="n">
+        <v>9.63104e-08</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-84.52200000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.0570368241408</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.227897346711024</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3.285076205876169</v>
+      </c>
+      <c r="L120" t="n">
+        <v>14.80312841820791</v>
+      </c>
+      <c r="M120" t="n">
+        <v>75.80413585887663</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>3.95316142324273</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>-6893.843963403062</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>5.352696183400781</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.8197406873615102</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1433.17</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7899508998749899</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1895.487282166043</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8103635354990426</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9.632859999999999e-08</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.8189765562806439</v>
+      </c>
+      <c r="I121" t="n">
+        <v>218.4355551746952</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2.482146482319791</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3.169630458842067</v>
+      </c>
+      <c r="L121" t="n">
+        <v>13.91899362428572</v>
+      </c>
+      <c r="M121" t="n">
+        <v>74.70374740596479</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>3.656323908945197</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-6260.118745598808</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>7.087704999945458</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.000000000023577e-08</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.8200099863063431</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1403.502</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7735981550523301</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1879.40781480687</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8034892007880067</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.638560000000001e-08</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-84.67</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2092596657023919</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.893030789528475</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.750432008183268</v>
+      </c>
+      <c r="L122" t="n">
+        <v>9.902189719805582</v>
+      </c>
+      <c r="M122" t="n">
+        <v>75.59641130130557</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>3.89373036157181</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-6659.137677013047</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>6.462492215129032</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.000000000104934e-08</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.8202854958693423</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1399.118</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7711817321959683</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1866.691116433037</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.7980525256116277</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.642870000000001e-08</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-84.73999999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.4349214832108929</v>
+      </c>
+      <c r="I123" t="n">
+        <v>200.7162704063553</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2.310032999613516</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.163314272649033</v>
+      </c>
+      <c r="L123" t="n">
+        <v>12.80518441346568</v>
+      </c>
+      <c r="M123" t="n">
+        <v>71.97983678564529</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>3.074002227919823</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-5059.27801755262</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>4.80060642110891</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.000000000056875e-08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.8205908934782528</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1379.15</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.760175543419547</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1845.120781179249</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7888307211170156</v>
+      </c>
+      <c r="F124" t="n">
+        <v>9.645660000000001e-08</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-84.81999999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.3701394717652773</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.335929102145418</v>
+      </c>
+      <c r="K124" t="n">
+        <v>5.004489859244035</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>71.96496809531085</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>3.071292667337166</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-5013.089439330403</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>7.159032068649481</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1.000000000017028e-08</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8208824224879117</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1359.163</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7491588820075712</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1835.515012871585</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.7847240386611521</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.64629e-08</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-84.883</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3223559499627363</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1.898546098295892</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4.56112116579276</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>71.66015199783415</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>3.016681303761611</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-4872.548960438281</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>4.557608400150116</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.8211788291260644</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1348.709</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7433967276872232</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1811.353803448595</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7743945770635136</v>
+      </c>
+      <c r="F126" t="n">
+        <v>9.64984e-08</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="H126" t="n">
+        <v>121.3816997576813</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.7126119870318681</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2.64866864389906</v>
+      </c>
+      <c r="K126" t="n">
+        <v>39.14406202042679</v>
+      </c>
+      <c r="L126" t="n">
+        <v>21.41592926820701</v>
+      </c>
+      <c r="M126" t="n">
+        <v>66.96628715035813</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>2.352003655164078</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-3613.793524151322</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>8.327452122856243</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.000000000390443e-08</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.82146872071185</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1332.375</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7343935682584338</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1798.703986672823</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7689864952777493</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9.652589999999999e-08</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-85.023</v>
+      </c>
+      <c r="H127" t="n">
+        <v>171.0113492104345</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.7416526651963362</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.823918039892177</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.660707813994264</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>66.90489445212472</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>2.345022262484005</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-3575.396579701583</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>7.20621665343856</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.000000000004022e-08</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.821758690607435</v>
       </c>
     </row>
   </sheetData>
@@ -15450,7 +18362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18393,6 +21305,566 @@
       </c>
       <c r="AD51" t="n">
         <v>0.991701241764596</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2171.352</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3085.291125010337</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.80773e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-79.444</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1445789469345338</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7604756728346141</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.853294080221938</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.669289995406845</v>
+      </c>
+      <c r="L52" t="n">
+        <v>89.76950346118916</v>
+      </c>
+      <c r="M52" t="n">
+        <v>88.09430783337544</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>30.05451289616062</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-78760.15730880057</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-190.9244325294928</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000232958e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8161385629375092</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1883.012</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8672071594103583</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2436.193174009384</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7896153313574976</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.83661e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-81.511</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3818162323081923</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.147766437032013</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.425940734313148</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>10.26766489092141</v>
+      </c>
+      <c r="M53" t="n">
+        <v>84.09575976678013</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>9.669801019728071</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-21089.8647949108</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-35.32588200447844</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000001024e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8169989630959666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1804.97</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8312654972570085</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2290.591876072059</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.74242325383942</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.789380000000001e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-82.307</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.2553528543394512</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.148965500645029</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.178143219805741</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.621626337690618</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>81.88686765536133</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7.014839894666415</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-15220.71470400804</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-0.2526180468184975</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000028616e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8171656507180421</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1770.276</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8152874338200347</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2245.974991376862</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7279620951067745</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9.76139e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-82.712</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4826688389467782</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.474534677935025</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.551418930969855</v>
+      </c>
+      <c r="K55" t="n">
+        <v>94.2665018684901</v>
+      </c>
+      <c r="L55" t="n">
+        <v>18.41846900261313</v>
+      </c>
+      <c r="M55" t="n">
+        <v>82.12892926366001</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7.233436821182334</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-15445.57309959872</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.547942045868012</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000041606e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8172691439735189</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1725.149</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7945045298965807</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2208.057951621056</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7156724802148643</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.74876e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-82.973</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.009891440307489442</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.6965849257542726</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.756289284891249</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.200001266309295</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>81.41976774629789</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6.62765646336601</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-13852.93701736268</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.962476556874208</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000016451e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8173830739668587</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1694.95</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7805966052487114</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2173.878184337614</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.704594184553761</v>
+      </c>
+      <c r="F57" t="n">
+        <v>9.74243e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-83.19</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3278303911701608</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9353620008008451</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.971391505277188</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.061888657648388</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>81.17035524019785</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6.437574006989479</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-13236.67640537149</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3.433354351091111</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000107133e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8175095380799655</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1658.698</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7639010165095296</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2138.115766978489</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6930029226889654</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.741360000000001e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-83.364</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.05366468757043546</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7020164046096002</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.152978730997928</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.82604458027804</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80.75572285552995</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.144098341469087</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-12411.65283345398</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>5.936963132610117</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000000904e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8176623878828427</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1631.707</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7514705123812261</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2111.21212628579</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.6842829544258053</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9.74237e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-83.518</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3516471436276056</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6421215460414904</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.976196603117052</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.761157167783962</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>80.57165800571153</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6.022021829632053</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11990.81323150786</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4.89914605947456</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000016248e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8178330000012838</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1599.709</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7367340716751591</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2082.350874416249</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6749284881209621</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9.74664e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-83.64400000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.061919367068565</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.175823067208262</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.517860839839246</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>24.400999184891</v>
+      </c>
+      <c r="M60" t="n">
+        <v>79.89208914264633</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.609481839932464</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-10973.14047150493</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>5.930691616077183</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000025692e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8180311021553025</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1581.129</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7281771909851558</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2057.531095024056</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6668839379029954</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.751959999999999e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-83.765</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1398900408625366</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9920217197286048</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.595946545525786</v>
+      </c>
+      <c r="K61" t="n">
+        <v>218.4362878340127</v>
+      </c>
+      <c r="L61" t="n">
+        <v>12.90198656556534</v>
+      </c>
+      <c r="M61" t="n">
+        <v>80.04006496451282</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5.694564204306438</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11021.41217326432</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>5.625273935444056</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8182581466551765</v>
       </c>
     </row>
   </sheetData>
@@ -18406,7 +21878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AD127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24429,6 +27901,1182 @@
       </c>
       <c r="AD106" t="n">
         <v>0.9655460990838817</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1854.921</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2388.984962295792</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.72135e-08</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-81.926</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1656.568567225756</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1.028857051805552</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.016396611544593</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.71801986465499</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.742967931525837</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-85.82040409444005</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>-13.68412499268006</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>33683.17202914214</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-27.53562436280663</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.8165380297806613</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1716.726</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9254981748548861</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2211.408221159387</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9256685395935875</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9.65722e-08</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-83.03700000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.2529629039766714</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.355951619639265</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1.944795797822973</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3.729611011067499</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>81.46238613246548</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>6.661239260371824</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-13909.11086847288</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-1.880157488272289</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.816893901879613</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1681.905</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9067259468192987</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2160.349836133622</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.904296121670664</v>
+      </c>
+      <c r="F109" t="n">
+        <v>9.64161e-08</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-83.36199999999999</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.2382581298525882</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.258968562129347</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.306272676671824</v>
+      </c>
+      <c r="K109" t="n">
+        <v>113.2765236757852</v>
+      </c>
+      <c r="L109" t="n">
+        <v>16.10855099166881</v>
+      </c>
+      <c r="M109" t="n">
+        <v>81.73056589589275</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>6.8804450097968</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-14127.82846524425</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>2.932454824206843</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.816966791088103</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1646.014</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.8873768748103018</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2129.411283386107</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8913456204177036</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9.63627e-08</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-83.54000000000001</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.1760504078327485</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.5045293470557471</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.391650945373703</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2.573435797253967</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>80.77018552246251</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6.153894840862897</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-12395.1122341742</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>5.702421716281606</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.000000000000226e-08</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.817003527336025</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1627.187</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.8772271164108876</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2108.262040931066</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8824928051891319</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9.63395e-08</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-83.667</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.223086058834283</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.273925209285006</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.820325334899557</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2.958181476390237</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>80.73905095853198</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>6.132843024214359</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>-12233.19593743782</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>6.019765793581655</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.000000000004754e-08</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.8170836664869446</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1606.584</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8661199048369176</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2089.619768976085</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8746893772692401</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.63448e-08</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0741945992124429</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.6978039638298839</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.960425074315506</v>
+      </c>
+      <c r="K112" t="n">
+        <v>156.9225691472907</v>
+      </c>
+      <c r="L112" t="n">
+        <v>11.97479660027733</v>
+      </c>
+      <c r="M112" t="n">
+        <v>80.42384485326912</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>5.927355759885804</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-11690.92654999617</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>5.881280818775167</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.000000000018646e-08</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.8172060814185189</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>10</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1589.029</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.8566558899273878</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2071.751066326546</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8672097560361421</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.63549e-08</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-83.85299999999999</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.001248707332933483</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.7666237820916938</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.312164149141327</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>25.25669326091678</v>
+      </c>
+      <c r="M113" t="n">
+        <v>80.24359187525593</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>5.815759951450092</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-11359.06371320082</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>6.319563617524409</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.000000000001124e-08</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.8173700029627323</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1585.458</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.8547307405544495</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2053.938575453076</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.8597536643676738</v>
+      </c>
+      <c r="F114" t="n">
+        <v>9.64281e-08</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-83.91800000000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.3805797275400432</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.103456164048328</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.500830451179291</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>15.15069688435534</v>
+      </c>
+      <c r="M114" t="n">
+        <v>80.22458941476644</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>5.804232923996405</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-11257.41373524666</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>7.085494468465868</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.8175663715730012</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1564.309</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.8433291768220857</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2042.082571884564</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8547908857166442</v>
+      </c>
+      <c r="F115" t="n">
+        <v>9.64436e-08</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.3606018139721277</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.932489075902218</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.416635528966547</v>
+      </c>
+      <c r="K115" t="n">
+        <v>92.1903162381076</v>
+      </c>
+      <c r="L115" t="n">
+        <v>13.10461781313708</v>
+      </c>
+      <c r="M115" t="n">
+        <v>79.97780457130467</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>5.658463019198656</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>-10869.38676452248</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>5.639931485149646</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.8177835016258257</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1555.784</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.8387332937629151</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2026.092551225812</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8480976578767396</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9.648890000000001e-08</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.5511483594942026</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.948567449698868</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.168022407329723</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>14.88958405013333</v>
+      </c>
+      <c r="M116" t="n">
+        <v>79.71579786482299</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>5.511282095653958</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>-10490.28538429595</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>6.224691934585167</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.000000000037979e-08</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.8180193315197199</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1538.178</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8292417844210077</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2010.723251914548</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8416642564305896</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9.65104e-08</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-84.111</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3340320331106048</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.721110757677336</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1.77561061095463</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>13.14867659308288</v>
+      </c>
+      <c r="M117" t="n">
+        <v>79.30153815519702</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>5.293129337561722</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-9976.289598617124</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>6.900272159726342</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.000000000062752e-08</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.81826740690988</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1524.082</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8216425389544894</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1996.812005139222</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8358411780123992</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.65556e-08</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-84.176</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.3471056561107775</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.13709222758171</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.653177338914261</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>13.38858150051373</v>
+      </c>
+      <c r="M118" t="n">
+        <v>79.22364525887699</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>5.253962609440527</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-9821.918907996078</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>6.643089299408757</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8185265014020772</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1517.797</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.8182542544938572</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1985.199198156014</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8309801984890925</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9.65881e-08</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-84.235</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.2706076348460714</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.670943180479548</v>
+      </c>
+      <c r="J119" t="n">
+        <v>227.3232916582942</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3.506617038875208</v>
+      </c>
+      <c r="L119" t="n">
+        <v>15.61731569043798</v>
+      </c>
+      <c r="M119" t="n">
+        <v>78.61445943814785</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>4.965915012758859</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-9178.377094020414</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>5.950556861386303</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.000000000020636e-08</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.818778926608831</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>20</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1489.285</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8028832494753145</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1965.088938694983</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8225622888837907</v>
+      </c>
+      <c r="F120" t="n">
+        <v>9.65832e-08</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-84.30200000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.6445833554132325</v>
+      </c>
+      <c r="J120" t="n">
+        <v>82.05334716232932</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3.813064629317002</v>
+      </c>
+      <c r="L120" t="n">
+        <v>17.6199836138575</v>
+      </c>
+      <c r="M120" t="n">
+        <v>78.30266259639752</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>4.829947665105149</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>-8839.225052122372</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>8.497923526999102</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.000000000000275e-08</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.8190324203767602</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1489.337</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.8029112830142093</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1954.351781387989</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.818067845646829</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9.66049e-08</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-84.374</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.4883549082127023</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1.095797266738241</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2.891766816469899</v>
+      </c>
+      <c r="L121" t="n">
+        <v>14.94533875307528</v>
+      </c>
+      <c r="M121" t="n">
+        <v>77.5568465763868</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>4.531982853826364</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-8187.16246258248</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>6.926860876018736</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.00000000000057e-08</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.8193055149624258</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1477.017</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7962694907222465</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1938.076110545078</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8112550481199367</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.663550000000001e-08</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-84.44199999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.7034386978764323</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.348296817527572</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2.868179526312546</v>
+      </c>
+      <c r="L122" t="n">
+        <v>15.32296882602677</v>
+      </c>
+      <c r="M122" t="n">
+        <v>76.80255617255989</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>4.264377502545075</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-7598.949092311984</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>7.57491666089652</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.8195705992598853</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1459.828</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7870027887980136</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1920.017897098878</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.8036960999761839</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.66478e-08</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-84.518</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3641921920536133</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1.188582495060085</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.504481906177751</v>
+      </c>
+      <c r="L123" t="n">
+        <v>14.74180737221922</v>
+      </c>
+      <c r="M123" t="n">
+        <v>76.08746304544461</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>4.037024273282904</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-7095.70000561196</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>8.875728333353891</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.000000000000073e-08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.819850926027284</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1448.405</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.7808445750519835</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1908.781221096853</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7989925642991625</v>
+      </c>
+      <c r="F124" t="n">
+        <v>9.66655e-08</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-84.58799999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.780083888284994</v>
+      </c>
+      <c r="I124" t="n">
+        <v>265.9202271174925</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.285032003146982</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3.418456234320121</v>
+      </c>
+      <c r="L124" t="n">
+        <v>14.97462815327426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>74.42830302001586</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>3.588440331864283</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-6174.36839395098</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>6.403335234270799</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8201283384230544</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1423.77</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7675636860006437</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1893.084783767881</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.7924222268643518</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.67068e-08</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-84.654</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.08991647443220739</v>
+      </c>
+      <c r="I125" t="n">
+        <v>129.7756561245102</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2.325242113593637</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4.857065206495601</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>75.7245552548771</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>3.93019288369934</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-6777.427021364794</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>6.602450655352072</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.8204074573804105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1417.283</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7640665020235363</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1873.043834194451</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7840333295335916</v>
+      </c>
+      <c r="F126" t="n">
+        <v>9.67213e-08</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-84.714</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.8293180911928117</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.856753153755542</v>
+      </c>
+      <c r="K126" t="n">
+        <v>3.671136805359361</v>
+      </c>
+      <c r="L126" t="n">
+        <v>12.79659607309218</v>
+      </c>
+      <c r="M126" t="n">
+        <v>71.47192935793714</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>2.983826024096705</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-4924.697935117063</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>8.311090644652722</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.000000000292301e-08</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.8207055371406068</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1385.385</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7468700823377384</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1859.480337086301</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7783558148894155</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9.67732e-08</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-84.795</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.1133243076337183</v>
+      </c>
+      <c r="I127" t="n">
+        <v>138.6391193276019</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.728790196691539</v>
+      </c>
+      <c r="K127" t="n">
+        <v>3.280980592147037</v>
+      </c>
+      <c r="L127" t="n">
+        <v>12.80737643806228</v>
+      </c>
+      <c r="M127" t="n">
+        <v>74.51123344201001</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>3.608630768459387</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-6064.797403531207</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>7.19707130089671</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.8209818814846213</v>
       </c>
     </row>
   </sheetData>
@@ -24442,7 +29090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27385,6 +32033,566 @@
       </c>
       <c r="AD51" t="n">
         <v>0.9997428963779533</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2100.214</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2965.393644485681</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.88663e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-79.185</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2057593420806764</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.105907683838851</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.36970407044839</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.641220531884353</v>
+      </c>
+      <c r="L52" t="n">
+        <v>49.39408555463013</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.96324123033871</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>28.11901144093827</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-71616.06502077462</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-171.1334095612729</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000012968e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8164851991062217</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1853.215</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8823934132426505</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2442.017152254233</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8235052222477457</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.8513e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-81.44799999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1203477286669403</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.898654026974901</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.635442683566334</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.719989318811659</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.13931916918921</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>20.01207591544794</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-45061.81952303981</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-47.37994801868535</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000014577e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8172474918555485</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1789.613</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8521098326170572</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2272.03449412809</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7661830996208776</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.78979e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-82.315</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.02481220319470143</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6964719331509209</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.671513471678277</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.473927917717882</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>81.88833678925752</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7.016127520282379</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-15106.11296741202</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-0.07081724266117817</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.00000000153e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8174387567703176</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1742.008</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8294430948465252</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2229.105464475118</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7517064281230476</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9.75794e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2879055827993872</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.506813794196044</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.773380966419395</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.314709404821689</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>81.39979066064795</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>6.612028470594559</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-13932.58900800227</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.914762832142969</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8175968994201085</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1716.142</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8171272070369971</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2194.252609082881</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7399532312221749</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.743639999999999e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-83.005</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1683943636202961</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.781194210531596</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.80280347844018</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.475649650161801</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>81.43435707413214</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6.639115347060015</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-13786.63331417237</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.047053294870238</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000000174e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8177714730722562</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1693.865</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8065201927041721</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2158.654143258376</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.727948597068223</v>
+      </c>
+      <c r="F57" t="n">
+        <v>9.736049999999999e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-83.205</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.417429452196065</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.425321431417159</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.030845255892864</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>19.55664655669159</v>
+      </c>
+      <c r="M57" t="n">
+        <v>81.6869081072623</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6.843802973259718</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-14050.34403228993</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4.857417691670889</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000001539e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8179664656866953</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1649.548</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7854190096818704</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2130.134998287589</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7183312752587493</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.73717e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1286106502330682</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7330588641550995</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.361303792710249</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.748321941369903</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80.52929401056504</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>5.99459073920224</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-12026.51762871698</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4.109680187245885</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8181836745645537</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7708738252387614</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2098.78111570525</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7077580137153304</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9.740380000000001e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-83.53</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.04474668343653658</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.109429628303797</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.617469705417038</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.205082936199291</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>80.56663963579884</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6.018759639972834</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11913.14283832148</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>5.174037301547969</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000007224e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8184047662893781</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1595.559</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7597125816702489</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2069.876093420263</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6980105650625225</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9.74456e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.06423757596991378</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7650552631925904</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.509966839088409</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.834348293579376</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>80.45632785736454</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.947910219392215</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11610.49288341105</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>6.050638274220091</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.00000000000021e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8186232526962256</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1575.763</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7502868755279224</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2043.988599371136</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6892806974116403</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.74979e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-83.785</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5501458033630298</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.509719737848023</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.000623241495188</v>
+      </c>
+      <c r="K61" t="n">
+        <v>21.14189972878443</v>
+      </c>
+      <c r="L61" t="n">
+        <v>14.38673845139171</v>
+      </c>
+      <c r="M61" t="n">
+        <v>80.50804722548756</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5.980924602514635</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11537.81654469432</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>6.257350190236139</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.818853211455457</v>
       </c>
     </row>
   </sheetData>
@@ -27398,7 +32606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AD127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33421,6 +38629,1182 @@
       </c>
       <c r="AD106" t="n">
         <v>0.9625230340636656</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1859.949</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2578.362696465633</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.90408e-08</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-81.328</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.07862985149743296</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.6713827541761467</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.845018331475061</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.435321416442945</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>87.09007767888573</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>19.67286475166236</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-44562.78278374775</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-107.3027325998783</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1.000000000025999e-08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.8174613803224149</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1741.006</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9360503970807801</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2221.548510273373</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8616121049682525</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9.80772e-08</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5110277694281686</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.9770484696433644</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.319816735474548</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4.397622809040036</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>81.84538930699718</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>6.978676287053522</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-14698.11016432498</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-0.5398390673656195</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1.000000000461458e-08</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.8177850475871441</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1702.215</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.91519444888005</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2173.844179846736</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.8431103129232351</v>
+      </c>
+      <c r="F109" t="n">
+        <v>9.79225e-08</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-83.06399999999999</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.7152535867745332</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.091341211769979</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.27294244963675</v>
+      </c>
+      <c r="K109" t="n">
+        <v>109.831049622968</v>
+      </c>
+      <c r="L109" t="n">
+        <v>15.22961902674731</v>
+      </c>
+      <c r="M109" t="n">
+        <v>81.69939753094116</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>6.854246276422602</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-14157.44454605444</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>3.704015162272071</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.8178456379488879</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1669.613</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.897666011272352</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2145.310615980667</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8320437690637609</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9.79507e-08</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-83.23099999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.2019764229100033</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.9836200509265005</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.081804188927177</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.879212420928498</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>81.33003173151414</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6.558016938701641</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-13346.76369863253</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>4.9463256623294</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.000000000055893e-08</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.8178922151452737</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1648.179</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.886142039378499</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2125.057825833924</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8241888655722912</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9.80403e-08</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-83.349</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.2610037691569966</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.6546857917244217</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2.179115876654897</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.684186082680875</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>81.23911844931203</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>6.488907595617004</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>-13058.46990651315</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>4.25519419952434</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.8179899605417242</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1622.917</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8725599465361684</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2107.056987480151</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8172073658870653</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.81352e-08</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-83.44</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.1527783114673207</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.8530274045713003</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.598212038295621</v>
+      </c>
+      <c r="K112" t="n">
+        <v>2.990977435564807</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>80.60546996201529</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>6.044091305916541</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-11989.41641045902</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>2.973737185888695</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.000000000118768e-08</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.8181237090838903</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>10</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1610.274</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.8657624483251959</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2083.86710811746</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8082133328154268</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.821129999999999e-08</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-83.53400000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.05929077803703878</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.238433217245756</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.560716357865072</v>
+      </c>
+      <c r="K113" t="n">
+        <v>142.9954905608733</v>
+      </c>
+      <c r="L113" t="n">
+        <v>14.09846820616437</v>
+      </c>
+      <c r="M113" t="n">
+        <v>81.02813574746196</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>6.333880392911789</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-12487.46503069001</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>4.174617211114537</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.0000000000002e-08</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.8182995252561174</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1591.012</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.8554062503864353</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2061.283376789911</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.7994543900342167</v>
+      </c>
+      <c r="F114" t="n">
+        <v>9.82893e-08</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-83.621</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.5671932623847262</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.8438618306635417</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.998470242387886</v>
+      </c>
+      <c r="K114" t="n">
+        <v>63.14283551123326</v>
+      </c>
+      <c r="L114" t="n">
+        <v>14.3343036825985</v>
+      </c>
+      <c r="M114" t="n">
+        <v>80.65532393194952</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>6.076920319123904</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-11839.36444176706</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>5.733898027167243</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.818506955335304</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1573.55</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.8460178209187456</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2041.689827867813</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.7918551686566516</v>
+      </c>
+      <c r="F115" t="n">
+        <v>9.83558e-08</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-83.718</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.2629833315448777</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.418673959908506</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.145778115761439</v>
+      </c>
+      <c r="K115" t="n">
+        <v>40.7591205789175</v>
+      </c>
+      <c r="L115" t="n">
+        <v>14.50598228471504</v>
+      </c>
+      <c r="M115" t="n">
+        <v>80.60168176755981</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>6.041610877417288</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>-11661.33753679387</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>6.109641813789722</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.8187235001853064</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1546.478</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.831462583113838</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2027.15954356042</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7862196991676964</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9.84276e-08</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-83.794</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1551171840530976</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.050480866123949</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.290924625546688</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>22.44773017891563</v>
+      </c>
+      <c r="M116" t="n">
+        <v>79.95085488340752</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>5.642973774707093</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>-10739.33531980895</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>4.599528198652933</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.8189363941046487</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1547.203</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8318523787480194</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2008.313198503226</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7789102756009388</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9.8483e-08</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-83.861</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.8945027922325282</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.366291899499271</v>
+      </c>
+      <c r="J117" t="n">
+        <v>175.4470384430855</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4.11893742600376</v>
+      </c>
+      <c r="L117" t="n">
+        <v>18.35831355793997</v>
+      </c>
+      <c r="M117" t="n">
+        <v>79.96308992866611</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>5.649995623016379</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-10669.77870015526</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>5.246987271302487</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.000000000043376e-08</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.8191824354446653</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1515.979</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8150648216698414</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1987.004161158352</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7706457139959779</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.853999999999999e-08</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-83.95699999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.1127619683915746</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.7495989397176721</v>
+      </c>
+      <c r="J118" t="n">
+        <v>92.74001119599137</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4.295206003041953</v>
+      </c>
+      <c r="L118" t="n">
+        <v>19.53239605355517</v>
+      </c>
+      <c r="M118" t="n">
+        <v>79.46950916523271</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>5.379538695557694</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-10029.73288370191</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>7.340377265121901</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8194237523939037</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1511.163</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.8124755033605759</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1975.898398618931</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7663384214049686</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9.85804e-08</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-84.018</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.8559532461375106</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.328389985989696</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.333184107710662</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>14.66175364629218</v>
+      </c>
+      <c r="M119" t="n">
+        <v>79.31465910136225</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>5.29978245289024</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-9788.442375689649</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>4.346408811813035</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.000000000000099e-08</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.8196299009321035</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>20</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1490.354</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8012875621858448</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1948.404744053622</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7556751991193698</v>
+      </c>
+      <c r="F120" t="n">
+        <v>9.861950000000001e-08</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-84.107</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.2356607234229905</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.213634806891813</v>
+      </c>
+      <c r="J120" t="n">
+        <v>137.9658200224859</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.99416386679548</v>
+      </c>
+      <c r="L120" t="n">
+        <v>14.57072050935274</v>
+      </c>
+      <c r="M120" t="n">
+        <v>78.85400274089908</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>5.075471343248195</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>-9265.580539951061</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>9.142040037818106</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.000000000001436e-08</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.8199098661430432</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1468.902</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7897539126072811</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1942.473133893661</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.7533746654636152</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9.86953e-08</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-84.157</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.1185021279577231</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.9864508394808011</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>4.304114361557826</v>
+      </c>
+      <c r="L121" t="n">
+        <v>15.3647802535071</v>
+      </c>
+      <c r="M121" t="n">
+        <v>78.36099238823104</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>4.854837506900851</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-8755.207892042818</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>4.50147063119914</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.000000000000634e-08</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.8201691887276035</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1450.005</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7795939566084877</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1921.799240122437</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7453564398665867</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.872379999999999e-08</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-84.23699999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.05380113572511737</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.090143531918051</v>
+      </c>
+      <c r="J122" t="n">
+        <v>63.35111615984849</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.626598489664141</v>
+      </c>
+      <c r="L122" t="n">
+        <v>17.43238285260841</v>
+      </c>
+      <c r="M122" t="n">
+        <v>78.17445881809338</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>4.776092922867646</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-8527.547761122863</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>6.712865146004788</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.8204288800316157</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1440.09</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7742631652803383</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1907.307614901686</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.739735964034922</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.87643e-08</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-84.31</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.07207044813801851</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1.232324247895761</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4.523189088942083</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6.914344935431254</v>
+      </c>
+      <c r="M123" t="n">
+        <v>77.64146237975108</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>4.564006334416027</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-8047.945031695579</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>5.881987166349518</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.8206916463326047</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1430.57</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.769144745366674</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1892.251133305422</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7338964125952028</v>
+      </c>
+      <c r="F124" t="n">
+        <v>9.8799e-08</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6213181397165357</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.247902344606112</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2.80461654878724</v>
+      </c>
+      <c r="L124" t="n">
+        <v>14.49138730460957</v>
+      </c>
+      <c r="M124" t="n">
+        <v>76.52796988685211</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>4.174275743988929</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-7235.633427636122</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>5.538980953159012</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1.000000000001557e-08</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8209766645390726</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1415.333</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7609525852590581</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1873.511165162557</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.7266282465731948</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.88563e-08</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-84.453</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.188211527472301</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.019736079446583</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2.326592394364633</v>
+      </c>
+      <c r="L125" t="n">
+        <v>13.10354341677175</v>
+      </c>
+      <c r="M125" t="n">
+        <v>75.90669352731483</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>3.983136241071378</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-6817.736554585192</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>6.643188404103512</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.00000000000026e-08</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.8212503947327692</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1398.834</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7520819119233915</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1859.866517525914</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7213362650938834</v>
+      </c>
+      <c r="F126" t="n">
+        <v>9.8869e-08</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6035058288152853</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.8463011961467574</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2.844202944668714</v>
+      </c>
+      <c r="L126" t="n">
+        <v>13.05602717923162</v>
+      </c>
+      <c r="M126" t="n">
+        <v>75.45103271350774</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>3.85312522429649</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-6511.877174778572</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>5.910673956230767</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.8215162161485162</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1372.83</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7381008834113193</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1847.235037239816</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7164372335094549</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9.88957e-08</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-84.575</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.8605719348080185</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>3.362185293685391</v>
+      </c>
+      <c r="L127" t="n">
+        <v>13.26643862178885</v>
+      </c>
+      <c r="M127" t="n">
+        <v>75.66571386144132</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>3.913370700239529</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-6573.57496791219</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>4.339350397981889</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.8218041925291998</v>
       </c>
     </row>
   </sheetData>
@@ -33434,7 +39818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36377,6 +42761,566 @@
       </c>
       <c r="AD51" t="n">
         <v>0.8198511514445603</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1901.949</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2749.353534071263</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.02799e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-78.922</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3346450058000554</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.890959066615111</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.277958507874815</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.042836670231522</v>
+      </c>
+      <c r="L52" t="n">
+        <v>30.03495252401388</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.51033630518397</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>22.99897536986291</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-53974.71950945709</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-165.1646215448336</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000017296e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8176698051296899</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1746.613</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.9183279888156832</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2271.667056857229</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8262549827461905</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.01085e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-81.69499999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1610724394091827</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8934902534604947</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.973319903309193</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.59014275151022</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.74904427002542</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>17.60537047733306</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-37551.0497807443</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-21.35167127158547</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000000242e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8181856435898024</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1699.104</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8933488752852995</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2173.660616752567</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7906078973895345</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.00401e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-82.489</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.388816161843519</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9792127061044772</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.860796190842195</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.954153685741215</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>81.9062215115754</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7.031839855797516</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-14514.85180401859</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.828953980688311</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000000528e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8183769204677546</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1658.84</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8721790121606836</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2137.17521112342</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7773373575418927</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.00171e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-82.84</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1415250389016196</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.246585801163391</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.645144929512142</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.36699026060447</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>81.49194910206108</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>6.68473070198293</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-13542.28276559242</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.451056985458763</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8185163722777227</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1628.589</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.856273748665185</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2110.418671138663</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7676054188686092</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.00093e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-83.071</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1598942784002132</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5099825813020249</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.42525797530225</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.904213287956088</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>80.99987116188733</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6.313659628394239</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-12568.92099399804</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.516923114106476</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8186844962466338</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1596.459</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8393805512135184</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2077.370447218381</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.755585057168765</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.0013e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-83.282</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1630186829299076</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.5731723277345485</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.428068579194771</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.652329495690666</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>80.60684936062036</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6.044994998973135</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-11845.22419483523</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4.818297810895956</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000000134e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8188554601852759</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1573.1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8270989390356943</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2050.186584860075</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.745697692004034</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.00175e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-83.41200000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1244895923720541</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7789443752369859</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.618069492605652</v>
+      </c>
+      <c r="K58" t="n">
+        <v>109.7542742221394</v>
+      </c>
+      <c r="L58" t="n">
+        <v>11.95330561959743</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80.41532819728054</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>5.921989464303661</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-11434.39076983167</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4.543562923048512</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000000253e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8190826759879687</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1546.414</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.8130680685970023</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2020.812272300039</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7350136122027221</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.00236e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-83.541</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.02914394035866134</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8408035347977428</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.612262370933581</v>
+      </c>
+      <c r="K59" t="n">
+        <v>144.2822449300018</v>
+      </c>
+      <c r="L59" t="n">
+        <v>12.21083507529948</v>
+      </c>
+      <c r="M59" t="n">
+        <v>80.35126635696295</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>5.881925263315612</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11204.7051286297</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>6.326656702948981</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000000164e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.819332156295854</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1531.022</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.8049753174243893</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1998.854409759556</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7270270574478058</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.00323e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5189174118278151</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.214168915191787</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.172152328658639</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>14.28678920538973</v>
+      </c>
+      <c r="M60" t="n">
+        <v>80.34649884336676</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.878964724563564</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11062.34664654996</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.317954996042431</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000010019e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8195950159865549</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1503.517</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7905138360702627</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1974.457857720213</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7181534979957349</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.00425e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-83.768</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.4415845295430562</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.893304348388936</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.129368859957696</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>14.91811428563402</v>
+      </c>
+      <c r="M61" t="n">
+        <v>79.96284655099919</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5.649855780309382</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-10468.77814691912</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>4.237117696082237</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000006196e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.81985115140063</v>
       </c>
     </row>
   </sheetData>
@@ -36390,7 +43334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AD127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42413,6 +49357,1182 @@
       </c>
       <c r="AD106" t="n">
         <v>0.9896137907607819</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1849.936</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2715.263723024029</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.04334e-07</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-79.729</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.07221102643770386</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.8153864675599375</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.523630945438303</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.21598841060984</v>
+      </c>
+      <c r="L107" t="n">
+        <v>51.98606918974787</v>
+      </c>
+      <c r="M107" t="n">
+        <v>88.03838653368703</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>29.19708312213158</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-67463.80481688313</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-170.2408674524675</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1.000000000018286e-08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.8165520185062216</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1737.542</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9392443846706048</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2228.786138463523</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8208359724193905</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.01775e-07</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-82.123</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.04802972034645723</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.162847846074162</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.071463983561139</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3.750417880057738</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>81.87646600769138</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>7.005736580532762</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-14814.85070680051</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-3.248842204567154</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1.000000000013943e-08</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.8168337792095237</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1690.178</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9136413367813806</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2180.894508495188</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.8031980429754699</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.01436e-07</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-82.565</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.1571034666902901</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.6680626160459657</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1.910836983482066</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3.196214401413367</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>81.50581769194375</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>6.695806946384173</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-13853.59290068857</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0.708461525831126</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1.000000000001757e-08</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.816915519181752</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1674.687</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.90526753357954</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2150.891078453141</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.7921481291908036</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.01433e-07</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.358482999663529</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.9627377802583735</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.958623020502255</v>
+      </c>
+      <c r="K110" t="n">
+        <v>4.857751477583812</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>81.75069506449455</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6.897469167641519</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-14143.72172759192</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>3.536353899453388</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.000000000577437e-08</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.8169795429763897</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1657.438</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.8959434272320773</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2130.880636421414</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.7847785164853972</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.01522e-07</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-82.869</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.497352742750175</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.349833159084221</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2.519932584590876</v>
+      </c>
+      <c r="K111" t="n">
+        <v>33.2319258141921</v>
+      </c>
+      <c r="L111" t="n">
+        <v>20.30903338794726</v>
+      </c>
+      <c r="M111" t="n">
+        <v>81.92128411004097</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>7.045126467469285</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>-14321.88272867534</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>2.924935331708184</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.000000000019187e-08</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.8170717724703349</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1620.582</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8760205758469481</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2109.960749891053</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.7770739659649557</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.01607e-07</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.1072742295219764</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.4619959198776698</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.993346798279628</v>
+      </c>
+      <c r="K112" t="n">
+        <v>2.6840425335955</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>80.68534012519825</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>6.096854058715722</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-12160.6112450819</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>2.807780879382562</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.000000000003428e-08</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.8171979482723294</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>10</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1614.248</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.8725966736146549</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2090.654714323986</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.7699637779550907</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.01687e-07</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-83.075</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.4043530171562512</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.512388706013889</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.37238199963529</v>
+      </c>
+      <c r="K113" t="n">
+        <v>115.1112371819762</v>
+      </c>
+      <c r="L113" t="n">
+        <v>16.45125575877624</v>
+      </c>
+      <c r="M113" t="n">
+        <v>81.57974651930112</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>6.755461832548046</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-13435.87290284801</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>2.575547353859292</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.8173656663243782</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1589.135</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.859021609396217</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2072.693197316159</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.7633487604687512</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.01774e-07</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.3009057455802208</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.9824012355063746</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.834218651502062</v>
+      </c>
+      <c r="K114" t="n">
+        <v>98.11477485825704</v>
+      </c>
+      <c r="L114" t="n">
+        <v>13.55663055230919</v>
+      </c>
+      <c r="M114" t="n">
+        <v>80.97047297236134</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>6.292761078618605</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-12348.74472933945</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>1.671060994940717</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.000000000046243e-08</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.8175583319736806</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1573.797</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.8507305117582447</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2051.656558471574</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.755601211430989</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.01854e-07</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-83.241</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.2269290068811579</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.101760772814085</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.673655151434051</v>
+      </c>
+      <c r="K115" t="n">
+        <v>117.1986098632979</v>
+      </c>
+      <c r="L115" t="n">
+        <v>13.99043955274803</v>
+      </c>
+      <c r="M115" t="n">
+        <v>80.91333530017002</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>6.252526741927878</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>-12155.25681238084</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>3.172168830990813</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.8177651938916631</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1557.214</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.8417664178652667</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2034.194394765822</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.749170099949006</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.01902e-07</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-83.33499999999999</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.4727134313213929</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.203178740075887</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1.972665473997059</v>
+      </c>
+      <c r="K116" t="n">
+        <v>197.3629486900238</v>
+      </c>
+      <c r="L116" t="n">
+        <v>14.42424309320021</v>
+      </c>
+      <c r="M116" t="n">
+        <v>80.78016904878108</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>6.160675103707614</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>-11858.280242979</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>3.04614329024821</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.8179934978746392</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1534.302</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8293811245362003</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2016.451158592099</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7426354727511876</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01963e-07</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-83.401</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0547763765681951</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7475629351901885</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1.738895974210846</v>
+      </c>
+      <c r="K117" t="n">
+        <v>134.7982161970187</v>
+      </c>
+      <c r="L117" t="n">
+        <v>12.36322587635323</v>
+      </c>
+      <c r="M117" t="n">
+        <v>80.2745815969581</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>5.834654230646167</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-11095.67692918065</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>3.159168614843452</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.000000000060638e-08</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.8182255311758677</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1527.01</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8254393665510591</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1998.896250023604</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7361702044166099</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.02014e-07</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-83.48699999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5453071387991288</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.007795929683587</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2.543924050633056</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>14.62491971941346</v>
+      </c>
+      <c r="M118" t="n">
+        <v>80.47932636684661</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>5.962547138327809</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-11261.54318003224</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>3.142808010174122</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.000000000004977e-08</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8184733066684976</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1504.367</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.813199483657813</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1980.300041171025</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7293214373171591</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.02064e-07</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-83.55500000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.3444030504286444</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.5264318081434376</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.574755172271788</v>
+      </c>
+      <c r="K119" t="n">
+        <v>160.0837812543127</v>
+      </c>
+      <c r="L119" t="n">
+        <v>12.51476857572979</v>
+      </c>
+      <c r="M119" t="n">
+        <v>80.08510871185089</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>5.720962251384011</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-10684.11138840195</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>4.604141973889227</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.000000000340535e-08</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.8187178637891661</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>20</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1493.931</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8075582074190675</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1963.498654280912</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7231336822392097</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.02105e-07</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-83.63</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.245714806729214</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.071463879186556</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.510289885984</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>14.561066897228</v>
+      </c>
+      <c r="M120" t="n">
+        <v>80.16381530960258</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>5.767663021381217</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>-10690.68072800848</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>5.122786650373769</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.8189684566732628</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1480.147</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.8001071388415599</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1946.148260189231</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.7167437342041227</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.02135e-07</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-83.70399999999999</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3904550772244574</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.8634324040443383</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2.240531366720148</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>15.01970933529592</v>
+      </c>
+      <c r="M121" t="n">
+        <v>79.82965826704286</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>5.574320683196163</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-10226.30673371317</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>6.147883797360578</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.000000000041311e-08</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.8192341039442174</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1466.799</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7928917540931146</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1934.641942708281</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7125060915090938</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.02168e-07</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-83.77500000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2638232518632726</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.8594018518498668</v>
+      </c>
+      <c r="J122" t="n">
+        <v>149.6584194857321</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.359417809749259</v>
+      </c>
+      <c r="L122" t="n">
+        <v>14.83379814423165</v>
+      </c>
+      <c r="M122" t="n">
+        <v>79.51745299937818</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>5.404704640116488</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-9811.820734313953</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>4.368828999999664</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.8195014124726352</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1437.236</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7769112012523678</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1915.88602134111</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.7055985041509558</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.02204e-07</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-83.842</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.01007423593638938</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.8054758056909639</v>
+      </c>
+      <c r="J123" t="n">
+        <v>105.9799522777741</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.564154106978066</v>
+      </c>
+      <c r="L123" t="n">
+        <v>17.08648223889134</v>
+      </c>
+      <c r="M123" t="n">
+        <v>78.85770683064864</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>5.077201933076315</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-9094.208120553181</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>5.334055379330152</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.000000000002956e-08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.8197814386767727</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1441.264</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.7790885738749882</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1901.160074436681</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.700175109443635</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.02245e-07</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-83.932</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.7220517471916093</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.335564449736083</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>4.212643479132743</v>
+      </c>
+      <c r="L124" t="n">
+        <v>16.47982504918808</v>
+      </c>
+      <c r="M124" t="n">
+        <v>78.41101124211923</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>4.876377777613471</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-8631.513384457108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>4.883444725780237</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8200545176185636</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1427.772</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7717953485958433</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1882.099733560388</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6931554079263675</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.02259e-07</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-83.994</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.9302917877483331</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.381184476831069</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4.260408880643395</v>
+      </c>
+      <c r="L125" t="n">
+        <v>18.1641522587751</v>
+      </c>
+      <c r="M125" t="n">
+        <v>77.78010210306275</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>4.617419161472648</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-8066.439876583923</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>6.066403621508698</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.8203296737622451</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1398.795</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7561315634703037</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1867.991966839171</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.6879596817795514</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.02283e-07</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-84.06399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.01274439153736469</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.084235647129528</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4.536558949837817</v>
+      </c>
+      <c r="L126" t="n">
+        <v>8.44330511315562</v>
+      </c>
+      <c r="M126" t="n">
+        <v>77.66151198302688</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>4.571657614967597</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-7918.459157029197</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>5.755217785123591</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.000000000037755e-08</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.8206258426420179</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1384.802</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7485675180114341</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1858.134241596125</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.6843291964018483</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.02313e-07</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-84.14</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3239519518475613</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.322944238129567</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.8118744503229</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3.48187088756099</v>
+      </c>
+      <c r="M127" t="n">
+        <v>77.64911761277996</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>4.566924819591673</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-7840.941613102235</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>3.473669291390024</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.000000000109218e-08</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.8209298020088069</v>
       </c>
     </row>
   </sheetData>
@@ -42426,7 +50546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45371,6 +53491,566 @@
         <v>0.9944531998390341</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1559.477</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2813.986455296634</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.05842e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-80.506</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3528159199901776</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.6669320117494155</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.529651980191906</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.103139989096558</v>
+      </c>
+      <c r="L52" t="n">
+        <v>44.89756659844245</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.96484616691941</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>28.14120497528986</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-57740.79517774256</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-380.3783518806579</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000007539e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8181831631597025</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1297.737</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8321616798452302</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1826.828247836768</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6491958212514546</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.05331e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-83.16800000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.04660029998507831</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.327850653843779</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.463901758323729</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-69.91631284645814</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-2.735041045811539</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>6209.594969437313</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-14.41823400068881</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.818895471137981</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1239.304</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7946920666351603</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1750.669803530729</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6221315672062051</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.05269e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3107858070265758</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9096776634867305</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.980938647482868</v>
+      </c>
+      <c r="K54" t="n">
+        <v>61.49764626791477</v>
+      </c>
+      <c r="L54" t="n">
+        <v>15.4660026766381</v>
+      </c>
+      <c r="M54" t="n">
+        <v>80.92446931233515</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>6.260327511175567</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-10347.03658303436</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-3.649310196047281</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.00000000001464e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.819023732765717</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1217.375</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7806303010560592</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1714.693787254134</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.6093468516974013</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.05424e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-83.935</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.474339229962512</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.351401500302413</v>
+      </c>
+      <c r="J55" t="n">
+        <v>100.7697835095543</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.936543064069988</v>
+      </c>
+      <c r="L55" t="n">
+        <v>22.04559694701835</v>
+      </c>
+      <c r="M55" t="n">
+        <v>80.9611350739129</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>6.286151177074117</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-10223.29399243064</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-0.1141265549177888</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000002396e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8191151929529787</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1181.601</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7576905590784604</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1693.244625444675</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6017245115937073</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.05608e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.06999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1597118555682698</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8167215999862497</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.84388588911887</v>
+      </c>
+      <c r="K56" t="n">
+        <v>23.56478560098161</v>
+      </c>
+      <c r="L56" t="n">
+        <v>14.11058442340532</v>
+      </c>
+      <c r="M56" t="n">
+        <v>80.12736363966729</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>5.745942673259194</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-9147.921927695401</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-1.75005011937651</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8192422096301489</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1158.17</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7426656500865355</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1668.877806469671</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5930653302642664</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.05822e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.01618100064961282</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.070121003233528</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.70369905569678</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>13.85428694202342</v>
+      </c>
+      <c r="M57" t="n">
+        <v>79.92610058583583</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>5.628818597238174</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8826.232647253944</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-1.488093375455492</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.231634030276023e-07</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.7868628787226625</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1145.558</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7345783233737978</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1646.719188679884</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5851908723939814</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.0607e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.7233808433196347</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.725761784498405</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25.67739654717785</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.696672284942948</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.543562575648232</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80.06301893464592</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>5.707986855774786</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-8838.227600150214</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-1.671341015480721</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>6.584274685941277e-07</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.7233923153944689</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1119.845</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.718090103284627</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1623.178401216876</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5768252360140697</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.0626e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-84.379</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4088697727430021</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8715005190239302</v>
+      </c>
+      <c r="J59" t="n">
+        <v>116.0786115068044</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.637143637841801</v>
+      </c>
+      <c r="L59" t="n">
+        <v>14.98323341364893</v>
+      </c>
+      <c r="M59" t="n">
+        <v>79.41383595310127</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>5.350598385698979</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8135.038187212838</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-1.365157902565329</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>6.099039348884555e-07</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.734891437666408</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1104.321</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7081354838833789</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1602.18810069103</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.569365960406564</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.06462e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-84.465</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7204716997980477</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.839993321069983</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.223868249991634</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9.708328117735769</v>
+      </c>
+      <c r="M60" t="n">
+        <v>79.05683543241226</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.171939534218198</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-7742.103527652958</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-1.33328542519871</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.240243778522406e-07</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8278783438886272</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1081.877</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6937434793844347</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1583.370574256017</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5626788186118357</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.06619e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-84.54300000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7672461269706286</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.073688639716408</v>
+      </c>
+      <c r="J61" t="n">
+        <v>46.56680091890948</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.671151584716592</v>
+      </c>
+      <c r="L61" t="n">
+        <v>13.67848923597194</v>
+      </c>
+      <c r="M61" t="n">
+        <v>78.98136727189252</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5.135636781980701</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-7586.701877014153</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-1.84882022897591</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.062665850609764e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8366385479089919</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 46.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3924,6 +3924,566 @@
         <v>1.000000000040143e-08</v>
       </c>
       <c r="AD61" t="n">
+        <v>0.8175983326854956</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1957.236</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2490.695431616286</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.684039999999999e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-81.73999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2464082806988297</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.065456564382695</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.808311007737921</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.00874385993695</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>81.60782704804083</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>6.778394084486807</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-15727.23503409055</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-24.16691658448508</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000003123e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8161890479173292</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1817.878</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.928798571046108</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2316.118145251856</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9299082159350404</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.56945e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-82.723</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.209911878579621</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5326187816257929</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.74938596575435</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.901539909549118</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.711666836141368</v>
+      </c>
+      <c r="M63" t="n">
+        <v>81.14125697098204</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>6.416089444416845</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-13996.82426852906</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-2.083799004395814</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000001598e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8165654469945532</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1774.953</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.906867133038632</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2255.801759480275</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9056915313071492</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.54046e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-83.047</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2981711704284343</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.160196326418705</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.140866704231422</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.990574883511687</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>81.73160861482086</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>6.881324863281834</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-14736.30205345171</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.574251919631479</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.8166515681835362</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1735.142</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.8865267142030906</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2216.966631785988</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8900994491917193</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.52796e-08</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-83.255</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.08881987577638284</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.6166760145653803</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.81146618259224</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.043709091954853</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>81.25908569877066</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>6.503963809243431</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-13664.00322933267</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.411316126798056</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.000000000001147e-08</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.816683488194488</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1714.096</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.8757737952909103</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2192.589427632244</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8803121408583494</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.51974e-08</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-83.414</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.07380040201350339</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.9824895076588682</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.094930141534711</v>
+      </c>
+      <c r="K66" t="n">
+        <v>148.6024802247455</v>
+      </c>
+      <c r="L66" t="n">
+        <v>16.40948733475846</v>
+      </c>
+      <c r="M66" t="n">
+        <v>81.58407020134409</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>6.75898291607694</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-14055.14574340741</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.018123012928072</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8167631230097925</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1679.517</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.8581065339080213</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2158.314695794248</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8665510316504871</v>
+      </c>
+      <c r="F67" t="n">
+        <v>9.515719999999999e-08</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-83.535</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.08900785847456036</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.6206488008115633</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.423896995470146</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2.76433878048367</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>80.82287179736515</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>6.189841522509957</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-12645.77171301273</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>6.121793081247915</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.816862872176645</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1656.602</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.846398696937927</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2136.754677437255</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8578948073352555</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9.51519e-08</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1719250643571295</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.172215164609002</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.944370792145309</v>
+      </c>
+      <c r="K68" t="n">
+        <v>99.71930588253194</v>
+      </c>
+      <c r="L68" t="n">
+        <v>13.78948298022853</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80.77470821132474</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>6.156964600332436</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-12428.94669676615</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4.703535327434793</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.000000000022107e-08</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.8170062526080324</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1629.087</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.8323406068557907</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2110.104873404312</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8471950631213876</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.51472e-08</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-83.78</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3290674210841114</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.4609210184406642</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.659266979585766</v>
+      </c>
+      <c r="K69" t="n">
+        <v>123.3816088222879</v>
+      </c>
+      <c r="L69" t="n">
+        <v>12.9237346579996</v>
+      </c>
+      <c r="M69" t="n">
+        <v>80.54680279413365</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>6.005898305563314</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-11963.91581649758</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>5.61721806092828</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.000000000002113e-08</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.8171981026411727</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1605.65</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.8203660672499383</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2087.19090480466</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8379952355114811</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.517799999999999e-08</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-83.869</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1872782362963178</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7056324719965327</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1.598024832937826</v>
+      </c>
+      <c r="K70" t="n">
+        <v>163.1705869132753</v>
+      </c>
+      <c r="L70" t="n">
+        <v>13.20297201633247</v>
+      </c>
+      <c r="M70" t="n">
+        <v>79.9499842672588</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.642474761899186</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-11066.99855074649</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>5.368146752630309</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.000000000013692e-08</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.8173849821701255</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1591.787</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.8132831196646699</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2063.430118184225</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8284554152994947</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9.52153e-08</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6237956901773648</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.781425406388826</v>
+      </c>
+      <c r="J71" t="n">
+        <v>178.1658589114167</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3.72517974260488</v>
+      </c>
+      <c r="L71" t="n">
+        <v>17.75493996409865</v>
+      </c>
+      <c r="M71" t="n">
+        <v>80.19763229919931</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5.787956472433362</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-11253.83144962725</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>6.08401335663325</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.000000000040143e-08</v>
+      </c>
+      <c r="AD71" t="n">
         <v>0.8175983326854956</v>
       </c>
     </row>
@@ -3938,7 +4498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD127"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11136,6 +11696,1182 @@
         <v>1.000000000000001e-08</v>
       </c>
       <c r="AD127" t="n">
+        <v>0.820957461140848</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1836.084</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2355.337816415195</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.05005e-07</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-81.492</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2294850460880035</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.9117348194682676</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.382022521022515</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.96481337859651</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2.51316755848042</v>
+      </c>
+      <c r="M128" t="n">
+        <v>81.34705985591967</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>6.571121395343384</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>-14531.52379694545</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-20.04196432912704</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.8164290424822086</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1724.814</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.9393981974680897</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2205.304247198202</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.9363006154907566</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.05161e-07</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-82.054</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3846586601078535</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.2503263427891</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.384893305564139</v>
+      </c>
+      <c r="K129" t="n">
+        <v>4.141879435883444</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>82.06379504898048</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>7.173313701032324</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-15104.06592620119</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-1.484694170833109</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.8167890851169918</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1680.562</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9152969036275028</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2158.596185671065</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9164698883646467</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.05226e-07</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-82.274</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2397672969372497</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1.009010407698981</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.002422501929528</v>
+      </c>
+      <c r="K130" t="n">
+        <v>4.112992077985594</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>81.80798960018973</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>6.946380567912005</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-14320.8653249281</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>1.33407103181753</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.8169176540291773</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1651.756</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.8996080789332078</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2132.103063131309</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.905221768305131</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.05291e-07</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-82.414</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501464651645957</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.9717721362737951</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.069455352377541</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3.996827109048287</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>81.7535500828057</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>6.89989047036303</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-14041.20993973961</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>1.382733742713981</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.8170249113027882</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1629.905</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.8877072072955268</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2105.285071239517</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.893835719261598</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.05335e-07</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-82.535</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3686085134892848</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.89116369914952</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1.926453288571458</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3.93998286664764</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>81.77058638393777</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>6.914373410095767</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-13919.00672417357</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>3.312782034281554</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.000000000011593e-08</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.8171670241063483</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1605.689</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.8745182682273795</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2085.193743832154</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8853055936603618</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.05377e-07</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-82.631</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.1487730363654174</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.8383467530932587</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.626298478154131</v>
+      </c>
+      <c r="K133" t="n">
+        <v>3.106449255987164</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>81.32543878358123</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>6.554491053336548</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-13022.08877226029</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>2.846915867641201</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.8173498152651262</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1585.731</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8636483951714627</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2064.499055398605</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.8765193005480444</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.05451e-07</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.2299338700590891</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.7143512204342742</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.070379490846969</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3.080394153878762</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>81.29900621639202</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>6.53427126770334</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-12856.93658707621</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3.134258695881044</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.000000000201779e-08</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.8175382246741291</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1569.091</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.8545856289799376</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2048.447451013779</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8697043102426384</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.05481e-07</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-82.83199999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2545023264494192</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.177978654821514</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.731666160886648</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3.350571170729051</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>81.35220862018741</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>6.575093850844786</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-12830.07555650289</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>2.547092353861217</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.000000000009025e-08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.8177361393076815</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1549.136</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8437173898361948</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2031.575004608324</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.8625408170537355</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.05533e-07</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-82.90900000000001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.1920988709124505</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.7597588092186146</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.05545177468824</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2.638453666211698</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>80.95650726652701</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>6.282880365670981</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-12121.9023558993</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>2.854886772038981</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.00000000067882e-08</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.8179322349113838</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1534.242</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8356055605299103</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2012.18561384871</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8543087109734604</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.0555e-07</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-82.98099999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4984085124369117</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.607854202421477</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.825480393688617</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2.556753500969978</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>80.82040280242383</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>6.188147845855583</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-11836.7074318425</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>4.924105260245028</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.818146980576532</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1526.608</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.8314477986845917</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1999.865001124833</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.849077778646891</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.05571e-07</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-83.057</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.7324841365319408</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.405327996482811</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2.328669498677294</v>
+      </c>
+      <c r="K138" t="n">
+        <v>4.232004389831275</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>81.28144585114816</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>6.520905598763334</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-12418.7318184145</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.309023266251529</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.000000000152832e-08</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.8183527964476967</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1508.257</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8214531579165223</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1986.576224743123</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8434357954506396</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.05597e-07</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-83.125</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.04733327142602921</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.920580467823689</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1.844943631070001</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2.672277950581289</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>80.66582593562056</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>6.083880243086495</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-11455.12779674987</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>2.761381188583414</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.000000000099389e-08</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.8185770352402901</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1492.967</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8131256522032762</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1972.641293634008</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.8375194759265369</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.05623e-07</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-83.193</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.2782604091437579</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.4801439799008048</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.52453563469924</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2.418167897778835</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>80.70512503046389</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>6.110062979920581</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-11419.88564399849</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3.071132511613655</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8188130232065193</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1488.134</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.8104934196910381</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1953.602790422775</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.8294363453120888</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.0563e-07</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-83.26900000000001</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.2696173664028442</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1.085184214499734</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2.159718663370333</v>
+      </c>
+      <c r="K141" t="n">
+        <v>161.5361781834394</v>
+      </c>
+      <c r="L141" t="n">
+        <v>13.23225507074418</v>
+      </c>
+      <c r="M141" t="n">
+        <v>81.01223314878425</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>6.322487996767297</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-11759.36320920542</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>5.165050186870303</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8190634983198728</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1473.284</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8024055544299715</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1941.953242224178</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.824490325205161</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.05636e-07</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-83.32899999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.5187671132853936</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.347753456221208</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1.810854263797419</v>
+      </c>
+      <c r="K142" t="n">
+        <v>95.02163482108934</v>
+      </c>
+      <c r="L142" t="n">
+        <v>12.80203987389221</v>
+      </c>
+      <c r="M142" t="n">
+        <v>80.66484607984803</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>6.083230213197538</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-11207.44381029402</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>4.491451482685534</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.000000000000327e-08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8193162547204189</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1458.505</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7943563584236887</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1929.984235238838</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8194086732646523</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.05674e-07</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.2997701145575761</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.9605998038662696</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2.018198539370903</v>
+      </c>
+      <c r="K143" t="n">
+        <v>117.7590066559949</v>
+      </c>
+      <c r="L143" t="n">
+        <v>12.01550196845362</v>
+      </c>
+      <c r="M143" t="n">
+        <v>80.5500727252478</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>6.008014701821815</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-10969.49693665093</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>2.610018537470978</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8195739759225688</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1438.01</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7831940150886343</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1909.863433033482</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.8108660336207224</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.05681e-07</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-83.46899999999999</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.1870019213098451</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.9469573745814291</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1.649445068294622</v>
+      </c>
+      <c r="K144" t="n">
+        <v>130.2858933423074</v>
+      </c>
+      <c r="L144" t="n">
+        <v>11.9785488939127</v>
+      </c>
+      <c r="M144" t="n">
+        <v>80.31281421458912</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>5.858129429053886</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-10588.31972299025</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>4.863599169619647</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.000000000030748e-08</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.8198329197472933</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1423.579</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.7753343528945299</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1893.570978638052</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.8039487862170241</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.05718e-07</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-83.55</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.1217157933677126</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1.06403055153623</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1.554126858888137</v>
+      </c>
+      <c r="K145" t="n">
+        <v>156.0368456143822</v>
+      </c>
+      <c r="L145" t="n">
+        <v>11.69193191600545</v>
+      </c>
+      <c r="M145" t="n">
+        <v>80.02813702653556</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>5.687613330801211</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-10171.74663262239</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>4.788368428660192</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.8201046979891833</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1399.36</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.7621437799142088</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1879.502418246399</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.797975732036174</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.05747e-07</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-83.636</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.03794074822452956</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.5625863827636554</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2.304550078785692</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>16.54069689900615</v>
+      </c>
+      <c r="M146" t="n">
+        <v>79.44889331479698</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>5.368786864273599</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-9480.57087492682</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>4.242984877307549</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.00000000000263e-08</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.8203777163172912</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1399.741</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7623512867603007</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1865.403126760146</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7919896304298608</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.05768e-07</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.8069869720462988</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.9343169398906577</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2.561089956336871</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>14.4017455706923</v>
+      </c>
+      <c r="M147" t="n">
+        <v>79.91750698976013</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>5.623920632195568</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-9881.312596649015</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.627285961003167</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.000000000120302e-08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.8206657821089919</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1386.226</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7549905124166433</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1845.577632265529</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7835723688564061</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.05792e-07</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-83.782</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.6534863945577725</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.9784512371289356</v>
+      </c>
+      <c r="J148" t="n">
+        <v>2.79013894862836</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>14.93830358927775</v>
+      </c>
+      <c r="M148" t="n">
+        <v>79.26125899409929</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>5.272805740264764</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>-9141.055117616663</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>4.727277035371003</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD148" t="n">
         <v>0.820957461140848</v>
       </c>
     </row>
@@ -11150,7 +12886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD127"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18348,6 +20084,1182 @@
         <v>1.000000000004022e-08</v>
       </c>
       <c r="AD127" t="n">
+        <v>0.821758690607435</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1814.252</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2339.057964890725</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.624929999999999e-08</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-82.541</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2199663514713317</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.5430347125919821</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1.559088863125198</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2.859277521977673</v>
+      </c>
+      <c r="L128" t="n">
+        <v>6.371781080523672</v>
+      </c>
+      <c r="M128" t="n">
+        <v>81.16861795734711</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>6.436287350390533</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>-14030.21229415085</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-16.08687997773086</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.8172228647327775</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1717.973</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.946931848497342</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2206.173324548646</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.9431888211678897</v>
+      </c>
+      <c r="F129" t="n">
+        <v>9.5979e-08</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.2190206085376029</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.8063177372918047</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.442064191158716</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.442142867555391</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>81.43477619218186</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>6.639445107112255</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-13842.95666542388</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1.165618327657057</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.000000000063277e-08</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.8174399678725334</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1680.069</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9260394917574847</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2162.218222677857</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9243970244144294</v>
+      </c>
+      <c r="F130" t="n">
+        <v>9.58995e-08</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-83.39700000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.1882749671647599</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.6417509285887323</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.011960917883008</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.202052621258274</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>81.27911746970352</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>6.519137415136154</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-13344.15301216381</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>4.347303168778353</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.8175077489775567</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1658.341</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.9140632062139108</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2138.435894189785</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.9142295429560625</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9.586429999999999e-08</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-83.54900000000001</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3725479276760159</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.5033974455550557</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.133273462211748</v>
+      </c>
+      <c r="K131" t="n">
+        <v>106.2929094236003</v>
+      </c>
+      <c r="L131" t="n">
+        <v>14.70292033046309</v>
+      </c>
+      <c r="M131" t="n">
+        <v>81.08890683592003</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>6.377787459526253</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-12883.50979965216</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>4.018949842580923</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.8175913762229218</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1633.661</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.9004598038199766</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2109.269229088876</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.901760136238187</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9.58898e-08</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-83.67700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5255914365273067</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.8388112922987668</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.471447849005576</v>
+      </c>
+      <c r="K132" t="n">
+        <v>117.3699782833126</v>
+      </c>
+      <c r="L132" t="n">
+        <v>14.33176626959156</v>
+      </c>
+      <c r="M132" t="n">
+        <v>80.94242132094284</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>6.272945191355327</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-12517.65074811471</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>5.580486405689498</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.000000000021354e-08</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.8177127484635036</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1609.625</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.8872113686522048</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2083.455068001962</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8907240005483559</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.59227e-08</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.5263957367283191</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.6994297570443527</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2.374158659249447</v>
+      </c>
+      <c r="K133" t="n">
+        <v>38.83990851865718</v>
+      </c>
+      <c r="L133" t="n">
+        <v>15.04528357771289</v>
+      </c>
+      <c r="M133" t="n">
+        <v>80.66544031910878</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>6.083624411482382</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-11979.17933148436</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>6.492867149185258</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.000000000011275e-08</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.8178621643413874</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1582.947</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8725066859510144</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2062.046726737374</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.8815714521353077</v>
+      </c>
+      <c r="F134" t="n">
+        <v>9.594530000000001e-08</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-83.88800000000001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.1159678631247716</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.268364515548442</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1.672799835271107</v>
+      </c>
+      <c r="K134" t="n">
+        <v>187.9770402029174</v>
+      </c>
+      <c r="L134" t="n">
+        <v>12.66675223498165</v>
+      </c>
+      <c r="M134" t="n">
+        <v>80.33828804435977</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>5.873872752663535</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-11402.41242944528</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>5.306753407002134</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.000000000386943e-08</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.8180559343544889</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1567.266</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.8638634544704925</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2031.945921635717</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.868702679512538</v>
+      </c>
+      <c r="F135" t="n">
+        <v>9.5998e-08</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-83.999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.5637077412034458</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.194641851154163</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2.142102675327511</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>16.26723134778424</v>
+      </c>
+      <c r="M135" t="n">
+        <v>80.14307853878834</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>5.755287158325647</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-11034.8764813468</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>7.819278448108321</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.8182605588147898</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1539.483</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8485497053331071</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2013.479934137071</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.8608080536521189</v>
+      </c>
+      <c r="F136" t="n">
+        <v>9.60494e-08</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-84.10599999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.2047974902549611</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.8174481656248804</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.023114955504484</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>13.87641558853618</v>
+      </c>
+      <c r="M136" t="n">
+        <v>79.73537743298156</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>5.522023777319139</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-10435.68750078583</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>6.731098916767451</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.000000000000162e-08</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.818483972974807</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1507.92</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8311524529117235</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1993.667597190265</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8523378330572517</v>
+      </c>
+      <c r="F137" t="n">
+        <v>9.61057e-08</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-84.18600000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.07314627817032779</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.8182027167092857</v>
+      </c>
+      <c r="J137" t="n">
+        <v>108.4230324087155</v>
+      </c>
+      <c r="K137" t="n">
+        <v>3.117450240086721</v>
+      </c>
+      <c r="L137" t="n">
+        <v>17.66604575329081</v>
+      </c>
+      <c r="M137" t="n">
+        <v>78.91863691543492</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>5.105833053084565</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-9489.317125955242</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>5.876635771557858</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.000000000086677e-08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.8187105035549397</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1494.158</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.8235669576222046</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1969.499310342414</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8420053457009667</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9.61588e-08</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-84.274</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.09275825574913091</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.229632643733593</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.67232430408463</v>
+      </c>
+      <c r="K138" t="n">
+        <v>4.760114879320008</v>
+      </c>
+      <c r="L138" t="n">
+        <v>14.77705265714258</v>
+      </c>
+      <c r="M138" t="n">
+        <v>78.83031336632652</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5.064430218133074</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-9310.967628059669</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>7.446115734600539</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.000000000043942e-08</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.8189553136926873</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1476.015</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.813566693050359</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1954.801351333283</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8357216369473799</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9.61873e-08</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-84.36499999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.2962648364452972</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.9005835056790648</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>4.355019783095714</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3.607634364717111</v>
+      </c>
+      <c r="M139" t="n">
+        <v>78.25862137758851</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>4.811316464110353</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-8720.504584108672</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>5.216171439508798</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.8192201606935929</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1459.38</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8043976250267327</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1931.770085281579</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.8258752516087506</v>
+      </c>
+      <c r="F140" t="n">
+        <v>9.62606e-08</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-84.444</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.06492433219232048</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.014310593005116</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5.239716276678986</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.01935456888561009</v>
+      </c>
+      <c r="M140" t="n">
+        <v>77.51182730448956</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>4.515119068603103</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-8058.743922769041</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>7.174486143270542</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.000000000005142e-08</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8194724802478264</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1451.144</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.7998580131095349</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1917.336597696724</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.8197046103499608</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.63104e-08</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-84.52200000000001</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1.0570368241408</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1.227897346711024</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3.285076205876169</v>
+      </c>
+      <c r="L141" t="n">
+        <v>14.80312841820791</v>
+      </c>
+      <c r="M141" t="n">
+        <v>75.80413585887663</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>3.95316142324273</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-6893.843963403062</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>5.352696183400781</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8197406873615102</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1433.17</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7899508998749899</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1895.487282166043</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.8103635354990426</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9.632859999999999e-08</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.8189765562806439</v>
+      </c>
+      <c r="I142" t="n">
+        <v>218.4355551746952</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2.482146482319791</v>
+      </c>
+      <c r="K142" t="n">
+        <v>3.169630458842067</v>
+      </c>
+      <c r="L142" t="n">
+        <v>13.91899362428572</v>
+      </c>
+      <c r="M142" t="n">
+        <v>74.70374740596479</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>3.656323908945197</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-6260.118745598808</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>7.087704999945458</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.000000000023577e-08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8200099863063431</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1403.502</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7735981550523301</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1879.40781480687</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8034892007880067</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9.638560000000001e-08</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-84.67</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.2092596657023919</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.893030789528475</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3.750432008183268</v>
+      </c>
+      <c r="L143" t="n">
+        <v>9.902189719805582</v>
+      </c>
+      <c r="M143" t="n">
+        <v>75.59641130130557</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>3.89373036157181</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-6659.137677013047</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>6.462492215129032</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.000000000104934e-08</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8202854958693423</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1399.118</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7711817321959683</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1866.691116433037</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.7980525256116277</v>
+      </c>
+      <c r="F144" t="n">
+        <v>9.642870000000001e-08</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-84.73999999999999</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.4349214832108929</v>
+      </c>
+      <c r="I144" t="n">
+        <v>200.7162704063553</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2.310032999613516</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3.163314272649033</v>
+      </c>
+      <c r="L144" t="n">
+        <v>12.80518441346568</v>
+      </c>
+      <c r="M144" t="n">
+        <v>71.97983678564529</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>3.074002227919823</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-5059.27801755262</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>4.80060642110891</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.000000000056875e-08</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.8205908934782528</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1379.15</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.760175543419547</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1845.120781179249</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.7888307211170156</v>
+      </c>
+      <c r="F145" t="n">
+        <v>9.645660000000001e-08</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-84.81999999999999</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.3701394717652773</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2.335929102145418</v>
+      </c>
+      <c r="K145" t="n">
+        <v>5.004489859244035</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>71.96496809531085</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>3.071292667337166</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-5013.089439330403</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>7.159032068649481</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.000000000017028e-08</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.8208824224879117</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1359.163</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.7491588820075712</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1835.515012871585</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7847240386611521</v>
+      </c>
+      <c r="F146" t="n">
+        <v>9.64629e-08</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-84.883</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.3223559499627363</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1.898546098295892</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4.56112116579276</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>71.66015199783415</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3.016681303761611</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-4872.548960438281</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>4.557608400150116</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.8211788291260644</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1348.709</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7433967276872232</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1811.353803448595</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7743945770635136</v>
+      </c>
+      <c r="F147" t="n">
+        <v>9.64984e-08</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="H147" t="n">
+        <v>121.3816997576813</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.7126119870318681</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2.64866864389906</v>
+      </c>
+      <c r="K147" t="n">
+        <v>39.14406202042679</v>
+      </c>
+      <c r="L147" t="n">
+        <v>21.41592926820701</v>
+      </c>
+      <c r="M147" t="n">
+        <v>66.96628715035813</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>2.352003655164078</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-3613.793524151322</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>8.327452122856243</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.000000000390443e-08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.82146872071185</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1332.375</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7343935682584338</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1798.703986672823</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7689864952777493</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9.652589999999999e-08</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-85.023</v>
+      </c>
+      <c r="H148" t="n">
+        <v>171.0113492104345</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.7416526651963362</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1.823918039892177</v>
+      </c>
+      <c r="K148" t="n">
+        <v>4.660707813994264</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>66.90489445212472</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>2.345022262484005</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>-3575.396579701583</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>7.20621665343856</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.000000000004022e-08</v>
+      </c>
+      <c r="AD148" t="n">
         <v>0.821758690607435</v>
       </c>
     </row>
@@ -18362,7 +21274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21864,6 +24776,566 @@
         <v>1.000000000000042e-08</v>
       </c>
       <c r="AD61" t="n">
+        <v>0.8182581466551765</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2171.352</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3085.291125010337</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.80773e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.444</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1445789469345338</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.7604756728346141</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.853294080221938</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.669289995406845</v>
+      </c>
+      <c r="L62" t="n">
+        <v>89.76950346118916</v>
+      </c>
+      <c r="M62" t="n">
+        <v>88.09430783337544</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>30.05451289616062</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-78760.15730880057</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-190.9244325294928</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000232958e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8161385629375092</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1883.012</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.8672071594103583</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2436.193174009384</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7896153313574976</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.83661e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-81.511</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3818162323081923</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.147766437032013</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.425940734313148</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>10.26766489092141</v>
+      </c>
+      <c r="M63" t="n">
+        <v>84.09575976678013</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>9.669801019728071</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-21089.8647949108</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-35.32588200447844</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000001024e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8169989630959666</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1804.97</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.8312654972570085</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2290.591876072059</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.74242325383942</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.789380000000001e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-82.307</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2553528543394512</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.148965500645029</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.178143219805741</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.621626337690618</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>81.88686765536133</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.014839894666415</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-15220.71470400804</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-0.2526180468184975</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000028616e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.8171656507180421</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1770.276</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.8152874338200347</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2245.974991376862</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7279620951067745</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.76139e-08</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-82.712</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.4826688389467782</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.474534677935025</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.551418930969855</v>
+      </c>
+      <c r="K65" t="n">
+        <v>94.2665018684901</v>
+      </c>
+      <c r="L65" t="n">
+        <v>18.41846900261313</v>
+      </c>
+      <c r="M65" t="n">
+        <v>82.12892926366001</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>7.233436821182334</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-15445.57309959872</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.547942045868012</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.000000000041606e-08</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.8172691439735189</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1725.149</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.7945045298965807</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2208.057951621056</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7156724802148643</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.74876e-08</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-82.973</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.009891440307489442</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.6965849257542726</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.756289284891249</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.200001266309295</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>81.41976774629789</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>6.62765646336601</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-13852.93701736268</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.962476556874208</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.000000000016451e-08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8173830739668587</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1694.95</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.7805966052487114</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2173.878184337614</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.704594184553761</v>
+      </c>
+      <c r="F67" t="n">
+        <v>9.74243e-08</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-83.19</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.3278303911701608</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9353620008008451</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.971391505277188</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3.061888657648388</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>81.17035524019785</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>6.437574006989479</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-13236.67640537149</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>3.433354351091111</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.000000000107133e-08</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.8175095380799655</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1658.698</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7639010165095296</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2138.115766978489</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.6930029226889654</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9.741360000000001e-08</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-83.364</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.05366468757043546</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.7020164046096002</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.152978730997928</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2.82604458027804</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80.75572285552995</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>6.144098341469087</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-12411.65283345398</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>5.936963132610117</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.000000000000904e-08</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.8176623878828427</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1631.707</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.7514705123812261</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2111.21212628579</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6842829544258053</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.74237e-08</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-83.518</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3516471436276056</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.6421215460414904</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.976196603117052</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2.761157167783962</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>80.57165800571153</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>6.022021829632053</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-11990.81323150786</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4.89914605947456</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.000000000016248e-08</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.8178330000012838</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1599.709</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.7367340716751591</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2082.350874416249</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.6749284881209621</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.74664e-08</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-83.64400000000001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.061919367068565</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.175823067208262</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.517860839839246</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>24.400999184891</v>
+      </c>
+      <c r="M70" t="n">
+        <v>79.89208914264633</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.609481839932464</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-10973.14047150493</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>5.930691616077183</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.000000000025692e-08</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.8180311021553025</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1581.129</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.7281771909851558</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2057.531095024056</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6668839379029954</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9.751959999999999e-08</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-83.765</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1398900408625366</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.9920217197286048</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.595946545525786</v>
+      </c>
+      <c r="K71" t="n">
+        <v>218.4362878340127</v>
+      </c>
+      <c r="L71" t="n">
+        <v>12.90198656556534</v>
+      </c>
+      <c r="M71" t="n">
+        <v>80.04006496451282</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5.694564204306438</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-11021.41217326432</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>5.625273935444056</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD71" t="n">
         <v>0.8182581466551765</v>
       </c>
     </row>
@@ -21878,7 +25350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD127"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29076,6 +32548,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD127" t="n">
+        <v>0.8209818814846213</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1854.921</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2388.984962295792</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.72135e-08</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-81.926</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1656.568567225756</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1.028857051805552</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.016396611544593</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.71801986465499</v>
+      </c>
+      <c r="L128" t="n">
+        <v>7.742967931525837</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-85.82040409444005</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>-13.68412499268006</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>33683.17202914214</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-27.53562436280663</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.8165380297806613</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1716.726</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.9254981748548861</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2211.408221159387</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.9256685395935875</v>
+      </c>
+      <c r="F129" t="n">
+        <v>9.65722e-08</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-83.03700000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.2529629039766714</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.355951619639265</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.944795797822973</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.729611011067499</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>81.46238613246548</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>6.661239260371824</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-13909.11086847288</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-1.880157488272289</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.816893901879613</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1681.905</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9067259468192987</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2160.349836133622</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.904296121670664</v>
+      </c>
+      <c r="F130" t="n">
+        <v>9.64161e-08</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-83.36199999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2382581298525882</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1.258968562129347</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.306272676671824</v>
+      </c>
+      <c r="K130" t="n">
+        <v>113.2765236757852</v>
+      </c>
+      <c r="L130" t="n">
+        <v>16.10855099166881</v>
+      </c>
+      <c r="M130" t="n">
+        <v>81.73056589589275</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>6.8804450097968</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-14127.82846524425</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>2.932454824206843</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.816966791088103</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1646.014</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.8873768748103018</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2129.411283386107</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.8913456204177036</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9.63627e-08</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-83.54000000000001</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.1760504078327485</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.5045293470557471</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1.391650945373703</v>
+      </c>
+      <c r="K131" t="n">
+        <v>2.573435797253967</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>80.77018552246251</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>6.153894840862897</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-12395.1122341742</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>5.702421716281606</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.000000000000226e-08</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.817003527336025</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1627.187</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.8772271164108876</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2108.262040931066</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.8824928051891319</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9.63395e-08</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-83.667</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.223086058834283</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1.273925209285006</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1.820325334899557</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2.958181476390237</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>80.73905095853198</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>6.132843024214359</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-12233.19593743782</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>6.019765793581655</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.000000000004754e-08</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.8170836664869446</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1606.584</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.8661199048369176</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2089.619768976085</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8746893772692401</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.63448e-08</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0741945992124429</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.6978039638298839</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.960425074315506</v>
+      </c>
+      <c r="K133" t="n">
+        <v>156.9225691472907</v>
+      </c>
+      <c r="L133" t="n">
+        <v>11.97479660027733</v>
+      </c>
+      <c r="M133" t="n">
+        <v>80.42384485326912</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>5.927355759885804</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-11690.92654999617</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>5.881280818775167</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.000000000018646e-08</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.8172060814185189</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1589.029</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8566558899273878</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2071.751066326546</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.8672097560361421</v>
+      </c>
+      <c r="F134" t="n">
+        <v>9.63549e-08</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-83.85299999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.001248707332933483</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.7666237820916938</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.312164149141327</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>25.25669326091678</v>
+      </c>
+      <c r="M134" t="n">
+        <v>80.24359187525593</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>5.815759951450092</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-11359.06371320082</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>6.319563617524409</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.000000000001124e-08</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.8173700029627323</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1585.458</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.8547307405544495</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2053.938575453076</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8597536643676738</v>
+      </c>
+      <c r="F135" t="n">
+        <v>9.64281e-08</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-83.91800000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3805797275400432</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.103456164048328</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.500830451179291</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>15.15069688435534</v>
+      </c>
+      <c r="M135" t="n">
+        <v>80.22458941476644</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>5.804232923996405</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-11257.41373524666</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>7.085494468465868</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.8175663715730012</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1564.309</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8433291768220857</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2042.082571884564</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.8547908857166442</v>
+      </c>
+      <c r="F136" t="n">
+        <v>9.64436e-08</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-83.982</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3606018139721277</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.932489075902218</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.416635528966547</v>
+      </c>
+      <c r="K136" t="n">
+        <v>92.1903162381076</v>
+      </c>
+      <c r="L136" t="n">
+        <v>13.10461781313708</v>
+      </c>
+      <c r="M136" t="n">
+        <v>79.97780457130467</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>5.658463019198656</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-10869.38676452248</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>5.639931485149646</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.8177835016258257</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1555.784</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8387332937629151</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2026.092551225812</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8480976578767396</v>
+      </c>
+      <c r="F137" t="n">
+        <v>9.648890000000001e-08</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5511483594942026</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.948567449698868</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2.168022407329723</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>14.88958405013333</v>
+      </c>
+      <c r="M137" t="n">
+        <v>79.71579786482299</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>5.511282095653958</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-10490.28538429595</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>6.224691934585167</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.000000000037979e-08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.8180193315197199</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1538.178</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.8292417844210077</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2010.723251914548</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8416642564305896</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9.65104e-08</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-84.111</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3340320331106048</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.721110757677336</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.77561061095463</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>13.14867659308288</v>
+      </c>
+      <c r="M138" t="n">
+        <v>79.30153815519702</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5.293129337561722</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-9976.289598617124</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>6.900272159726342</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.000000000062752e-08</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.81826740690988</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1524.082</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8216425389544894</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1996.812005139222</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8358411780123992</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9.65556e-08</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-84.176</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3471056561107775</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1.13709222758171</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1.653177338914261</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>13.38858150051373</v>
+      </c>
+      <c r="M139" t="n">
+        <v>79.22364525887699</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>5.253962609440527</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-9821.918907996078</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>6.643089299408757</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.8185265014020772</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1517.797</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8182542544938572</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1985.199198156014</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.8309801984890925</v>
+      </c>
+      <c r="F140" t="n">
+        <v>9.65881e-08</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-84.235</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.2706076348460714</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.670943180479548</v>
+      </c>
+      <c r="J140" t="n">
+        <v>227.3232916582942</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3.506617038875208</v>
+      </c>
+      <c r="L140" t="n">
+        <v>15.61731569043798</v>
+      </c>
+      <c r="M140" t="n">
+        <v>78.61445943814785</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>4.965915012758859</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-9178.377094020414</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>5.950556861386303</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.000000000020636e-08</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.818778926608831</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1489.285</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.8028832494753145</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1965.088938694983</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.8225622888837907</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.65832e-08</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-84.30200000000001</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.6445833554132325</v>
+      </c>
+      <c r="J141" t="n">
+        <v>82.05334716232932</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3.813064629317002</v>
+      </c>
+      <c r="L141" t="n">
+        <v>17.6199836138575</v>
+      </c>
+      <c r="M141" t="n">
+        <v>78.30266259639752</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>4.829947665105149</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-8839.225052122372</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>8.497923526999102</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.000000000000275e-08</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8190324203767602</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1489.337</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8029112830142093</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1954.351781387989</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.818067845646829</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9.66049e-08</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-84.374</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4883549082127023</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.095797266738241</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2.891766816469899</v>
+      </c>
+      <c r="L142" t="n">
+        <v>14.94533875307528</v>
+      </c>
+      <c r="M142" t="n">
+        <v>77.5568465763868</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>4.531982853826364</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-8187.16246258248</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>6.926860876018736</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.00000000000057e-08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8193055149624258</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1477.017</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7962694907222465</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1938.076110545078</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8112550481199367</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9.663550000000001e-08</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-84.44199999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.7034386978764323</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1.348296817527572</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2.868179526312546</v>
+      </c>
+      <c r="L143" t="n">
+        <v>15.32296882602677</v>
+      </c>
+      <c r="M143" t="n">
+        <v>76.80255617255989</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>4.264377502545075</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-7598.949092311984</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>7.57491666089652</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8195705992598853</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1459.828</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7870027887980136</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1920.017897098878</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.8036960999761839</v>
+      </c>
+      <c r="F144" t="n">
+        <v>9.66478e-08</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-84.518</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.3641921920536133</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1.188582495060085</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3.504481906177751</v>
+      </c>
+      <c r="L144" t="n">
+        <v>14.74180737221922</v>
+      </c>
+      <c r="M144" t="n">
+        <v>76.08746304544461</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>4.037024273282904</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-7095.70000561196</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>8.875728333353891</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.000000000000073e-08</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.819850926027284</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1448.405</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.7808445750519835</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1908.781221096853</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.7989925642991625</v>
+      </c>
+      <c r="F145" t="n">
+        <v>9.66655e-08</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-84.58799999999999</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.780083888284994</v>
+      </c>
+      <c r="I145" t="n">
+        <v>265.9202271174925</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2.285032003146982</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3.418456234320121</v>
+      </c>
+      <c r="L145" t="n">
+        <v>14.97462815327426</v>
+      </c>
+      <c r="M145" t="n">
+        <v>74.42830302001586</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>3.588440331864283</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-6174.36839395098</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>6.403335234270799</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.8201283384230544</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1423.77</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.7675636860006437</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1893.084783767881</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7924222268643518</v>
+      </c>
+      <c r="F146" t="n">
+        <v>9.67068e-08</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-84.654</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.08991647443220739</v>
+      </c>
+      <c r="I146" t="n">
+        <v>129.7756561245102</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2.325242113593637</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4.857065206495601</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>75.7245552548771</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3.93019288369934</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-6777.427021364794</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>6.602450655352072</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.8204074573804105</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1417.283</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7640665020235363</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1873.043834194451</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7840333295335916</v>
+      </c>
+      <c r="F147" t="n">
+        <v>9.67213e-08</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-84.714</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.8293180911928117</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1.856753153755542</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3.671136805359361</v>
+      </c>
+      <c r="L147" t="n">
+        <v>12.79659607309218</v>
+      </c>
+      <c r="M147" t="n">
+        <v>71.47192935793714</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>2.983826024096705</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-4924.697935117063</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>8.311090644652722</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.000000000292301e-08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.8207055371406068</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1385.385</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7468700823377384</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1859.480337086301</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7783558148894155</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9.67732e-08</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-84.795</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.1133243076337183</v>
+      </c>
+      <c r="I148" t="n">
+        <v>138.6391193276019</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1.728790196691539</v>
+      </c>
+      <c r="K148" t="n">
+        <v>3.280980592147037</v>
+      </c>
+      <c r="L148" t="n">
+        <v>12.80737643806228</v>
+      </c>
+      <c r="M148" t="n">
+        <v>74.51123344201001</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>3.608630768459387</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>-6064.797403531207</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>7.19707130089671</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD148" t="n">
         <v>0.8209818814846213</v>
       </c>
     </row>
@@ -29090,7 +33738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32592,6 +37240,566 @@
         <v>1.000000000000105e-08</v>
       </c>
       <c r="AD61" t="n">
+        <v>0.818853211455457</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2100.214</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2965.393644485681</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.88663e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.185</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2057593420806764</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.105907683838851</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.36970407044839</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.641220531884353</v>
+      </c>
+      <c r="L62" t="n">
+        <v>49.39408555463013</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.96324123033871</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>28.11901144093827</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-71616.06502077462</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-171.1334095612729</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000012968e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8164851991062217</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1853.215</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.8823934132426505</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2442.017152254233</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8235052222477457</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.8513e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-81.44799999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1203477286669403</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.898654026974901</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.635442683566334</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.719989318811659</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>87.13931916918921</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>20.01207591544794</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-45061.81952303981</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-47.37994801868535</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000014577e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8172474918555485</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1789.613</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.8521098326170572</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2272.03449412809</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7661830996208776</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.78979e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-82.315</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.02481220319470143</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.6964719331509209</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.671513471678277</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.473927917717882</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>81.88833678925752</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.016127520282379</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-15106.11296741202</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-0.07081724266117817</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.00000000153e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.8174387567703176</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1742.008</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.8294430948465252</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2229.105464475118</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7517064281230476</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.75794e-08</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.2879055827993872</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.506813794196044</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.773380966419395</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.314709404821689</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>81.39979066064795</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>6.612028470594559</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-13932.58900800227</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.914762832142969</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.8175968994201085</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1716.142</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.8171272070369971</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2194.252609082881</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7399532312221749</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.743639999999999e-08</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-83.005</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1683943636202961</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.781194210531596</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.80280347844018</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.475649650161801</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>81.43435707413214</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>6.639115347060015</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-13786.63331417237</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.047053294870238</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.000000000000174e-08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8177714730722562</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1693.865</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.8065201927041721</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2158.654143258376</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.727948597068223</v>
+      </c>
+      <c r="F67" t="n">
+        <v>9.736049999999999e-08</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-83.205</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.417429452196065</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.425321431417159</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.030845255892864</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>19.55664655669159</v>
+      </c>
+      <c r="M67" t="n">
+        <v>81.6869081072623</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>6.843802973259718</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-14050.34403228993</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.857417691670889</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.000000000001539e-08</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.8179664656866953</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1649.548</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7854190096818704</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2130.134998287589</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7183312752587493</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9.73717e-08</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1286106502330682</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.7330588641550995</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.361303792710249</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2.748321941369903</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80.52929401056504</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>5.99459073920224</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-12026.51762871698</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4.109680187245885</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.8181836745645537</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.7708738252387614</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2098.78111570525</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7077580137153304</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.740380000000001e-08</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-83.53</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.04474668343653658</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.109429628303797</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.617469705417038</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.205082936199291</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>80.56663963579884</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>6.018759639972834</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-11913.14283832148</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>5.174037301547969</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.000000000007224e-08</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.8184047662893781</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1595.559</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.7597125816702489</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2069.876093420263</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.6980105650625225</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.74456e-08</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-83.664</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.06423757596991378</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7650552631925904</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1.509966839088409</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2.834348293579376</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>80.45632785736454</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.947910219392215</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-11610.49288341105</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>6.050638274220091</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.00000000000021e-08</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.8186232526962256</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1575.763</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.7502868755279224</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2043.988599371136</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6892806974116403</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9.74979e-08</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-83.785</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.5501458033630298</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.509719737848023</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.000623241495188</v>
+      </c>
+      <c r="K71" t="n">
+        <v>21.14189972878443</v>
+      </c>
+      <c r="L71" t="n">
+        <v>14.38673845139171</v>
+      </c>
+      <c r="M71" t="n">
+        <v>80.50804722548756</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5.980924602514635</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-11537.81654469432</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>6.257350190236139</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AD71" t="n">
         <v>0.818853211455457</v>
       </c>
     </row>
@@ -32606,7 +37814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD127"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39804,6 +45012,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD127" t="n">
+        <v>0.8218041925291998</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1859.949</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2578.362696465633</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.90408e-08</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-81.328</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.07862985149743296</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.6713827541761467</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1.845018331475061</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.435321416442945</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>87.09007767888573</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>19.67286475166236</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>-44562.78278374775</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-107.3027325998783</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.000000000025999e-08</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.8174613803224149</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1741.006</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.9360503970807801</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2221.548510273373</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.8616121049682525</v>
+      </c>
+      <c r="F129" t="n">
+        <v>9.80772e-08</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.5110277694281686</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.9770484696433644</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.319816735474548</v>
+      </c>
+      <c r="K129" t="n">
+        <v>4.397622809040036</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>81.84538930699718</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>6.978676287053522</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-14698.11016432498</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-0.5398390673656195</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.000000000461458e-08</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.8177850475871441</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1702.215</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.91519444888005</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2173.844179846736</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8431103129232351</v>
+      </c>
+      <c r="F130" t="n">
+        <v>9.79225e-08</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-83.06399999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.7152535867745332</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1.091341211769979</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.27294244963675</v>
+      </c>
+      <c r="K130" t="n">
+        <v>109.831049622968</v>
+      </c>
+      <c r="L130" t="n">
+        <v>15.22961902674731</v>
+      </c>
+      <c r="M130" t="n">
+        <v>81.69939753094116</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>6.854246276422602</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-14157.44454605444</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>3.704015162272071</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.8178456379488879</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1669.613</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.897666011272352</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2145.310615980667</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.8320437690637609</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9.79507e-08</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-83.23099999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.2019764229100033</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.9836200509265005</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.081804188927177</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3.879212420928498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>81.33003173151414</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>6.558016938701641</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-13346.76369863253</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>4.9463256623294</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.000000000055893e-08</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.8178922151452737</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1648.179</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.886142039378499</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2125.057825833924</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.8241888655722912</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9.80403e-08</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-83.349</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.2610037691569966</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.6546857917244217</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.179115876654897</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3.684186082680875</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>81.23911844931203</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>6.488907595617004</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-13058.46990651315</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>4.25519419952434</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.8179899605417242</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1622.917</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.8725599465361684</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2107.056987480151</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8172073658870653</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.81352e-08</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-83.44</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.1527783114673207</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.8530274045713003</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.598212038295621</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2.990977435564807</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>80.60546996201529</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>6.044091305916541</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-11989.41641045902</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>2.973737185888695</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.000000000118768e-08</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.8181237090838903</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1610.274</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8657624483251959</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2083.86710811746</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.8082133328154268</v>
+      </c>
+      <c r="F134" t="n">
+        <v>9.821129999999999e-08</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-83.53400000000001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.05929077803703878</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.238433217245756</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.560716357865072</v>
+      </c>
+      <c r="K134" t="n">
+        <v>142.9954905608733</v>
+      </c>
+      <c r="L134" t="n">
+        <v>14.09846820616437</v>
+      </c>
+      <c r="M134" t="n">
+        <v>81.02813574746196</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>6.333880392911789</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-12487.46503069001</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>4.174617211114537</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.0000000000002e-08</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.8182995252561174</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1591.012</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.8554062503864353</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2061.283376789911</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7994543900342167</v>
+      </c>
+      <c r="F135" t="n">
+        <v>9.82893e-08</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-83.621</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.5671932623847262</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.8438618306635417</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.998470242387886</v>
+      </c>
+      <c r="K135" t="n">
+        <v>63.14283551123326</v>
+      </c>
+      <c r="L135" t="n">
+        <v>14.3343036825985</v>
+      </c>
+      <c r="M135" t="n">
+        <v>80.65532393194952</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>6.076920319123904</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-11839.36444176706</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>5.733898027167243</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.818506955335304</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1573.55</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8460178209187456</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2041.689827867813</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.7918551686566516</v>
+      </c>
+      <c r="F136" t="n">
+        <v>9.83558e-08</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-83.718</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.2629833315448777</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.418673959908506</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.145778115761439</v>
+      </c>
+      <c r="K136" t="n">
+        <v>40.7591205789175</v>
+      </c>
+      <c r="L136" t="n">
+        <v>14.50598228471504</v>
+      </c>
+      <c r="M136" t="n">
+        <v>80.60168176755981</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>6.041610877417288</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-11661.33753679387</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>6.109641813789722</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.8187235001853064</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1546.478</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.831462583113838</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2027.15954356042</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.7862196991676964</v>
+      </c>
+      <c r="F137" t="n">
+        <v>9.84276e-08</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-83.794</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.1551171840530976</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.050480866123949</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2.290924625546688</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>22.44773017891563</v>
+      </c>
+      <c r="M137" t="n">
+        <v>79.95085488340752</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>5.642973774707093</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-10739.33531980895</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>4.599528198652933</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.8189363941046487</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1547.203</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.8318523787480194</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2008.313198503226</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7789102756009388</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9.8483e-08</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-83.861</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.8945027922325282</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.366291899499271</v>
+      </c>
+      <c r="J138" t="n">
+        <v>175.4470384430855</v>
+      </c>
+      <c r="K138" t="n">
+        <v>4.11893742600376</v>
+      </c>
+      <c r="L138" t="n">
+        <v>18.35831355793997</v>
+      </c>
+      <c r="M138" t="n">
+        <v>79.96308992866611</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5.649995623016379</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-10669.77870015526</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>5.246987271302487</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.000000000043376e-08</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.8191824354446653</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1515.979</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8150648216698414</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1987.004161158352</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.7706457139959779</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9.853999999999999e-08</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-83.95699999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.1127619683915746</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.7495989397176721</v>
+      </c>
+      <c r="J139" t="n">
+        <v>92.74001119599137</v>
+      </c>
+      <c r="K139" t="n">
+        <v>4.295206003041953</v>
+      </c>
+      <c r="L139" t="n">
+        <v>19.53239605355517</v>
+      </c>
+      <c r="M139" t="n">
+        <v>79.46950916523271</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>5.379538695557694</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-10029.73288370191</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>7.340377265121901</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.8194237523939037</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1511.163</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8124755033605759</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1975.898398618931</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.7663384214049686</v>
+      </c>
+      <c r="F140" t="n">
+        <v>9.85804e-08</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-84.018</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.8559532461375106</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.328389985989696</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2.333184107710662</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>14.66175364629218</v>
+      </c>
+      <c r="M140" t="n">
+        <v>79.31465910136225</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>5.29978245289024</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-9788.442375689649</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>4.346408811813035</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.000000000000099e-08</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8196299009321035</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1490.354</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.8012875621858448</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1948.404744053622</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7556751991193698</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.861950000000001e-08</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-84.107</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.2356607234229905</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1.213634806891813</v>
+      </c>
+      <c r="J141" t="n">
+        <v>137.9658200224859</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2.99416386679548</v>
+      </c>
+      <c r="L141" t="n">
+        <v>14.57072050935274</v>
+      </c>
+      <c r="M141" t="n">
+        <v>78.85400274089908</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>5.075471343248195</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-9265.580539951061</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>9.142040037818106</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.000000000001436e-08</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8199098661430432</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1468.902</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7897539126072811</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1942.473133893661</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.7533746654636152</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9.86953e-08</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-84.157</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.1185021279577231</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.9864508394808011</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>4.304114361557826</v>
+      </c>
+      <c r="L142" t="n">
+        <v>15.3647802535071</v>
+      </c>
+      <c r="M142" t="n">
+        <v>78.36099238823104</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>4.854837506900851</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-8755.207892042818</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>4.50147063119914</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.000000000000634e-08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8201691887276035</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1450.005</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7795939566084877</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1921.799240122437</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.7453564398665867</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9.872379999999999e-08</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-84.23699999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.05380113572511737</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1.090143531918051</v>
+      </c>
+      <c r="J143" t="n">
+        <v>63.35111615984849</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3.626598489664141</v>
+      </c>
+      <c r="L143" t="n">
+        <v>17.43238285260841</v>
+      </c>
+      <c r="M143" t="n">
+        <v>78.17445881809338</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>4.776092922867646</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-8527.547761122863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>6.712865146004788</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8204288800316157</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1440.09</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7742631652803383</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1907.307614901686</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.739735964034922</v>
+      </c>
+      <c r="F144" t="n">
+        <v>9.87643e-08</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-84.31</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.07207044813801851</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1.232324247895761</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>4.523189088942083</v>
+      </c>
+      <c r="L144" t="n">
+        <v>6.914344935431254</v>
+      </c>
+      <c r="M144" t="n">
+        <v>77.64146237975108</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>4.564006334416027</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-8047.945031695579</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>5.881987166349518</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.8206916463326047</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1430.57</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.769144745366674</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1892.251133305422</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.7338964125952028</v>
+      </c>
+      <c r="F145" t="n">
+        <v>9.8799e-08</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.6213181397165357</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1.247902344606112</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>2.80461654878724</v>
+      </c>
+      <c r="L145" t="n">
+        <v>14.49138730460957</v>
+      </c>
+      <c r="M145" t="n">
+        <v>76.52796988685211</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>4.174275743988929</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-7235.633427636122</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>5.538980953159012</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.000000000001557e-08</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.8209766645390726</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1415.333</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.7609525852590581</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1873.511165162557</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7266282465731948</v>
+      </c>
+      <c r="F146" t="n">
+        <v>9.88563e-08</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-84.453</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.188211527472301</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1.019736079446583</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.326592394364633</v>
+      </c>
+      <c r="L146" t="n">
+        <v>13.10354341677175</v>
+      </c>
+      <c r="M146" t="n">
+        <v>75.90669352731483</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3.983136241071378</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-6817.736554585192</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>6.643188404103512</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.00000000000026e-08</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.8212503947327692</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1398.834</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7520819119233915</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1859.866517525914</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7213362650938834</v>
+      </c>
+      <c r="F147" t="n">
+        <v>9.8869e-08</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.6035058288152853</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.8463011961467574</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2.844202944668714</v>
+      </c>
+      <c r="L147" t="n">
+        <v>13.05602717923162</v>
+      </c>
+      <c r="M147" t="n">
+        <v>75.45103271350774</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>3.85312522429649</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-6511.877174778572</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>5.910673956230767</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.8215162161485162</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1372.83</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7381008834113193</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1847.235037239816</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7164372335094549</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9.88957e-08</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-84.575</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.8605719348080185</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>3.362185293685391</v>
+      </c>
+      <c r="L148" t="n">
+        <v>13.26643862178885</v>
+      </c>
+      <c r="M148" t="n">
+        <v>75.66571386144132</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>3.913370700239529</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>-6573.57496791219</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>4.339350397981889</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD148" t="n">
         <v>0.8218041925291998</v>
       </c>
     </row>
@@ -39818,7 +46202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43320,6 +49704,566 @@
         <v>1.000000000006196e-08</v>
       </c>
       <c r="AD61" t="n">
+        <v>0.81985115140063</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1901.949</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2749.353534071263</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.02799e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-78.922</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.3346450058000554</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.890959066615111</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.277958507874815</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.042836670231522</v>
+      </c>
+      <c r="L62" t="n">
+        <v>30.03495252401388</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.51033630518397</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>22.99897536986291</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-53974.71950945709</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-165.1646215448336</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000017296e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8176698051296899</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1746.613</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.9183279888156832</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2271.667056857229</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8262549827461905</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.01085e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-81.69499999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1610724394091827</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8934902534604947</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.973319903309193</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.59014275151022</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.74904427002542</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>17.60537047733306</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-37551.0497807443</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-21.35167127158547</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000000242e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8181856435898024</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1699.104</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.8933488752852995</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2173.660616752567</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7906078973895345</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.00401e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-82.489</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.388816161843519</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9792127061044772</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.860796190842195</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.954153685741215</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>81.9062215115754</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.031839855797516</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-14514.85180401859</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.828953980688311</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000000528e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.8183769204677546</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1658.84</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.8721790121606836</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2137.17521112342</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7773373575418927</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.00171e-07</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-82.84</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.1415250389016196</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.246585801163391</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.645144929512142</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.36699026060447</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>81.49194910206108</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>6.68473070198293</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-13542.28276559242</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.451056985458763</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.8185163722777227</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1628.589</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.856273748665185</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2110.418671138663</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7676054188686092</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.00093e-07</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-83.071</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1598942784002132</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5099825813020249</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.42525797530225</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2.904213287956088</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>80.99987116188733</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>6.313659628394239</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-12568.92099399804</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.516923114106476</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8186844962466338</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1596.459</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.8393805512135184</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2077.370447218381</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.755585057168765</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.0013e-07</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-83.282</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1630186829299076</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.5731723277345485</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.428068579194771</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2.652329495690666</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>80.60684936062036</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>6.044994998973135</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-11845.22419483523</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.818297810895956</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.000000000000134e-08</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.8188554601852759</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1573.1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.8270989390356943</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2050.186584860075</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.745697692004034</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.00175e-07</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-83.41200000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1244895923720541</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.7789443752369859</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.618069492605652</v>
+      </c>
+      <c r="K68" t="n">
+        <v>109.7542742221394</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11.95330561959743</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80.41532819728054</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>5.921989464303661</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-11434.39076983167</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4.543562923048512</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.000000000000253e-08</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.8190826759879687</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1546.414</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.8130680685970023</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2020.812272300039</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7350136122027221</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.00236e-07</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-83.541</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.02914394035866134</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.8408035347977428</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.612262370933581</v>
+      </c>
+      <c r="K69" t="n">
+        <v>144.2822449300018</v>
+      </c>
+      <c r="L69" t="n">
+        <v>12.21083507529948</v>
+      </c>
+      <c r="M69" t="n">
+        <v>80.35126635696295</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>5.881925263315612</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-11204.7051286297</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>6.326656702948981</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.000000000000164e-08</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.819332156295854</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1531.022</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.8049753174243893</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1998.854409759556</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7270270574478058</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.00323e-07</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.5189174118278151</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.214168915191787</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.172152328658639</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>14.28678920538973</v>
+      </c>
+      <c r="M70" t="n">
+        <v>80.34649884336676</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.878964724563564</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-11062.34664654996</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>4.317954996042431</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.000000000010019e-08</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.8195950159865549</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1503.517</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.7905138360702627</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1974.457857720213</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.7181534979957349</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.00425e-07</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-83.768</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.4415845295430562</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.893304348388936</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.129368859957696</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>14.91811428563402</v>
+      </c>
+      <c r="M71" t="n">
+        <v>79.96284655099919</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5.649855780309382</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-10468.77814691912</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>4.237117696082237</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.000000000006196e-08</v>
+      </c>
+      <c r="AD71" t="n">
         <v>0.81985115140063</v>
       </c>
     </row>
@@ -43334,7 +50278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD127"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50532,6 +57476,1182 @@
         <v>1.000000000109218e-08</v>
       </c>
       <c r="AD127" t="n">
+        <v>0.8209298020088069</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1849.936</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2715.263723024029</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.04334e-07</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-79.729</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.07221102643770386</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.8153864675599375</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1.523630945438303</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.21598841060984</v>
+      </c>
+      <c r="L128" t="n">
+        <v>51.98606918974787</v>
+      </c>
+      <c r="M128" t="n">
+        <v>88.03838653368703</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>29.19708312213158</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>-67463.80481688313</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-170.2408674524675</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.000000000018286e-08</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.8165520185062216</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1737.542</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.9392443846706048</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2228.786138463523</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.8208359724193905</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.01775e-07</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-82.123</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.04802972034645723</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.162847846074162</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.071463983561139</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.750417880057738</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>81.87646600769138</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>7.005736580532762</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-14814.85070680051</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-3.248842204567154</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.000000000013943e-08</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.8168337792095237</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1690.178</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9136413367813806</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2180.894508495188</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8031980429754699</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.01436e-07</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-82.565</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.1571034666902901</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.6680626160459657</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1.910836983482066</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.196214401413367</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>81.50581769194375</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>6.695806946384173</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-13853.59290068857</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.708461525831126</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.000000000001757e-08</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.816915519181752</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1674.687</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.90526753357954</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2150.891078453141</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.7921481291908036</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.01433e-07</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-82.74299999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.358482999663529</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.9627377802583735</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1.958623020502255</v>
+      </c>
+      <c r="K131" t="n">
+        <v>4.857751477583812</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>81.75069506449455</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>6.897469167641519</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-14143.72172759192</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>3.536353899453388</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.000000000577437e-08</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.8169795429763897</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1657.438</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.8959434272320773</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2130.880636421414</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.7847785164853972</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.01522e-07</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-82.869</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.497352742750175</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1.349833159084221</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.519932584590876</v>
+      </c>
+      <c r="K132" t="n">
+        <v>33.2319258141921</v>
+      </c>
+      <c r="L132" t="n">
+        <v>20.30903338794726</v>
+      </c>
+      <c r="M132" t="n">
+        <v>81.92128411004097</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>7.045126467469285</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-14321.88272867534</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>2.924935331708184</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.000000000019187e-08</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.8170717724703349</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1620.582</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.8760205758469481</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2109.960749891053</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.7770739659649557</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.01607e-07</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.1072742295219764</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4619959198776698</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.993346798279628</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2.6840425335955</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>80.68534012519825</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>6.096854058715722</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-12160.6112450819</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>2.807780879382562</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.000000000003428e-08</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.8171979482723294</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1614.248</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8725966736146549</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2090.654714323986</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.7699637779550907</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.01687e-07</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-83.075</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4043530171562512</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.512388706013889</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.37238199963529</v>
+      </c>
+      <c r="K134" t="n">
+        <v>115.1112371819762</v>
+      </c>
+      <c r="L134" t="n">
+        <v>16.45125575877624</v>
+      </c>
+      <c r="M134" t="n">
+        <v>81.57974651930112</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>6.755461832548046</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-13435.87290284801</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>2.575547353859292</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.8173656663243782</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1589.135</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.859021609396217</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2072.693197316159</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7633487604687512</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.01774e-07</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3009057455802208</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.9824012355063746</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.834218651502062</v>
+      </c>
+      <c r="K135" t="n">
+        <v>98.11477485825704</v>
+      </c>
+      <c r="L135" t="n">
+        <v>13.55663055230919</v>
+      </c>
+      <c r="M135" t="n">
+        <v>80.97047297236134</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>6.292761078618605</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-12348.74472933945</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.671060994940717</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.000000000046243e-08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.8175583319736806</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1573.797</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8507305117582447</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2051.656558471574</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.755601211430989</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.01854e-07</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-83.241</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.2269290068811579</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.101760772814085</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.673655151434051</v>
+      </c>
+      <c r="K136" t="n">
+        <v>117.1986098632979</v>
+      </c>
+      <c r="L136" t="n">
+        <v>13.99043955274803</v>
+      </c>
+      <c r="M136" t="n">
+        <v>80.91333530017002</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>6.252526741927878</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-12155.25681238084</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>3.172168830990813</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.8177651938916631</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1557.214</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8417664178652667</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2034.194394765822</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.749170099949006</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.01902e-07</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-83.33499999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4727134313213929</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.203178740075887</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.972665473997059</v>
+      </c>
+      <c r="K137" t="n">
+        <v>197.3629486900238</v>
+      </c>
+      <c r="L137" t="n">
+        <v>14.42424309320021</v>
+      </c>
+      <c r="M137" t="n">
+        <v>80.78016904878108</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>6.160675103707614</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-11858.280242979</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>3.04614329024821</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.8179934978746392</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1534.302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.8293811245362003</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2016.451158592099</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7426354727511876</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.01963e-07</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-83.401</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0547763765681951</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.7475629351901885</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.738895974210846</v>
+      </c>
+      <c r="K138" t="n">
+        <v>134.7982161970187</v>
+      </c>
+      <c r="L138" t="n">
+        <v>12.36322587635323</v>
+      </c>
+      <c r="M138" t="n">
+        <v>80.2745815969581</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5.834654230646167</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-11095.67692918065</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.159168614843452</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.000000000060638e-08</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.8182255311758677</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1527.01</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8254393665510591</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1998.896250023604</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.7361702044166099</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.02014e-07</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-83.48699999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5453071387991288</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1.007795929683587</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2.543924050633056</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>14.62491971941346</v>
+      </c>
+      <c r="M139" t="n">
+        <v>80.47932636684661</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>5.962547138327809</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-11261.54318003224</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.142808010174122</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.000000000004977e-08</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.8184733066684976</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1504.367</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.813199483657813</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1980.300041171025</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.7293214373171591</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.02064e-07</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-83.55500000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3444030504286444</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.5264318081434376</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.574755172271788</v>
+      </c>
+      <c r="K140" t="n">
+        <v>160.0837812543127</v>
+      </c>
+      <c r="L140" t="n">
+        <v>12.51476857572979</v>
+      </c>
+      <c r="M140" t="n">
+        <v>80.08510871185089</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>5.720962251384011</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-10684.11138840195</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>4.604141973889227</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.000000000340535e-08</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8187178637891661</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1493.931</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.8075582074190675</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1963.498654280912</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7231336822392097</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.02105e-07</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-83.63</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.245714806729214</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1.071463879186556</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2.510289885984</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>14.561066897228</v>
+      </c>
+      <c r="M141" t="n">
+        <v>80.16381530960258</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>5.767663021381217</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-10690.68072800848</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>5.122786650373769</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.000000000002183e-08</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8189684566732628</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1480.147</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8001071388415599</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1946.148260189231</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.7167437342041227</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.02135e-07</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-83.70399999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3904550772244574</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.8634324040443383</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2.240531366720148</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>15.01970933529592</v>
+      </c>
+      <c r="M142" t="n">
+        <v>79.82965826704286</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>5.574320683196163</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-10226.30673371317</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>6.147883797360578</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.000000000041311e-08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8192341039442174</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1466.799</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7928917540931146</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1934.641942708281</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.7125060915090938</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.02168e-07</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-83.77500000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.2638232518632726</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.8594018518498668</v>
+      </c>
+      <c r="J143" t="n">
+        <v>149.6584194857321</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3.359417809749259</v>
+      </c>
+      <c r="L143" t="n">
+        <v>14.83379814423165</v>
+      </c>
+      <c r="M143" t="n">
+        <v>79.51745299937818</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>5.404704640116488</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-9811.820734313953</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>4.368828999999664</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8195014124726352</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1437.236</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7769112012523678</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1915.88602134111</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.7055985041509558</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.02204e-07</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-83.842</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.01007423593638938</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.8054758056909639</v>
+      </c>
+      <c r="J144" t="n">
+        <v>105.9799522777741</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3.564154106978066</v>
+      </c>
+      <c r="L144" t="n">
+        <v>17.08648223889134</v>
+      </c>
+      <c r="M144" t="n">
+        <v>78.85770683064864</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>5.077201933076315</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-9094.208120553181</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>5.334055379330152</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.000000000002956e-08</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.8197814386767727</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1441.264</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.7790885738749882</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1901.160074436681</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.700175109443635</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.02245e-07</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-83.932</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.7220517471916093</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1.335564449736083</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>4.212643479132743</v>
+      </c>
+      <c r="L145" t="n">
+        <v>16.47982504918808</v>
+      </c>
+      <c r="M145" t="n">
+        <v>78.41101124211923</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>4.876377777613471</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-8631.513384457108</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>4.883444725780237</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.8200545176185636</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1427.772</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.7717953485958433</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1882.099733560388</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.6931554079263675</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.02259e-07</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-83.994</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.9302917877483331</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1.381184476831069</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4.260408880643395</v>
+      </c>
+      <c r="L146" t="n">
+        <v>18.1641522587751</v>
+      </c>
+      <c r="M146" t="n">
+        <v>77.78010210306275</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>4.617419161472648</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-8066.439876583923</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>6.066403621508698</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.8203296737622451</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1398.795</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7561315634703037</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1867.991966839171</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.6879596817795514</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.02283e-07</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-84.06399999999999</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.01274439153736469</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1.084235647129528</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>4.536558949837817</v>
+      </c>
+      <c r="L147" t="n">
+        <v>8.44330511315562</v>
+      </c>
+      <c r="M147" t="n">
+        <v>77.66151198302688</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>4.571657614967597</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-7918.459157029197</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>5.755217785123591</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.000000000037755e-08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.8206258426420179</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1384.802</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7485675180114341</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1858.134241596125</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.6843291964018483</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.02313e-07</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-84.14</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.3239519518475613</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1.322944238129567</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>4.8118744503229</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3.48187088756099</v>
+      </c>
+      <c r="M148" t="n">
+        <v>77.64911761277996</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>4.566924819591673</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>-7840.941613102235</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.473669291390024</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.000000000109218e-08</v>
+      </c>
+      <c r="AD148" t="n">
         <v>0.8209298020088069</v>
       </c>
     </row>
@@ -50546,7 +58666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54051,6 +62171,566 @@
         <v>0.8366385479089919</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1559.477</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2813.986455296634</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.05842e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-80.506</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.3528159199901776</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.6669320117494155</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.529651980191906</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.103139989096558</v>
+      </c>
+      <c r="L62" t="n">
+        <v>44.89756659844245</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.96484616691941</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>28.14120497528986</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-57740.79517774256</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-380.3783518806579</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000007539e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8181831631597025</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1297.737</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.8321616798452302</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1826.828247836768</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6491958212514546</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.05331e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-83.16800000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.04660029998507831</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.327850653843779</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.463901758323729</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-69.91631284645814</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-2.735041045811539</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>6209.594969437313</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-14.41823400068881</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.818895471137981</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1239.304</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7946920666351603</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1750.669803530729</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6221315672062051</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.05269e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-83.71299999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.3107858070265758</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9096776634867305</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.980938647482868</v>
+      </c>
+      <c r="K64" t="n">
+        <v>61.49764626791477</v>
+      </c>
+      <c r="L64" t="n">
+        <v>15.4660026766381</v>
+      </c>
+      <c r="M64" t="n">
+        <v>80.92446931233515</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>6.260327511175567</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-10347.03658303436</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-3.649310196047281</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.00000000001464e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.819023732765717</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1217.375</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.7806303010560592</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1714.693787254134</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6093468516974013</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.05424e-07</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-83.935</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.474339229962512</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.351401500302413</v>
+      </c>
+      <c r="J65" t="n">
+        <v>100.7697835095543</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.936543064069988</v>
+      </c>
+      <c r="L65" t="n">
+        <v>22.04559694701835</v>
+      </c>
+      <c r="M65" t="n">
+        <v>80.9611350739129</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>6.286151177074117</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-10223.29399243064</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>-0.1141265549177888</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.000000000002396e-08</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.8191151929529787</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1181.601</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.7576905590784604</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1693.244625444675</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.6017245115937073</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.05608e-07</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-84.06999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1597118555682698</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8167215999862497</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.84388588911887</v>
+      </c>
+      <c r="K66" t="n">
+        <v>23.56478560098161</v>
+      </c>
+      <c r="L66" t="n">
+        <v>14.11058442340532</v>
+      </c>
+      <c r="M66" t="n">
+        <v>80.12736363966729</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>5.745942673259194</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-9147.921927695401</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-1.75005011937651</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8192422096301489</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1158.17</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.7426656500865355</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1668.877806469671</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5930653302642664</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.05822e-07</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.01618100064961282</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.070121003233528</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.70369905569678</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>13.85428694202342</v>
+      </c>
+      <c r="M67" t="n">
+        <v>79.92610058583583</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>5.628818597238174</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-8826.232647253944</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-1.488093375455492</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>4.231634030276023e-07</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.7868628787226625</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1145.558</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7345783233737978</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1646.719188679884</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5851908723939814</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.0607e-07</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.7233808433196347</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.725761784498405</v>
+      </c>
+      <c r="J68" t="n">
+        <v>25.67739654717785</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4.696672284942948</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.543562575648232</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80.06301893464592</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>5.707986855774786</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-8838.227600150214</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>-1.671341015480721</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>6.584274685941277e-07</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.7233923153944689</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1119.845</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.718090103284627</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1623.178401216876</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.5768252360140697</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.0626e-07</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-84.379</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.4088697727430021</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.8715005190239302</v>
+      </c>
+      <c r="J69" t="n">
+        <v>116.0786115068044</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.637143637841801</v>
+      </c>
+      <c r="L69" t="n">
+        <v>14.98323341364893</v>
+      </c>
+      <c r="M69" t="n">
+        <v>79.41383595310127</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>5.350598385698979</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-8135.038187212838</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-1.365157902565329</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>6.099039348884555e-07</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.734891437666408</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1104.321</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.7081354838833789</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1602.18810069103</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.569365960406564</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.06462e-07</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-84.465</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.7204716997980477</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.839993321069983</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4.223868249991634</v>
+      </c>
+      <c r="L70" t="n">
+        <v>9.708328117735769</v>
+      </c>
+      <c r="M70" t="n">
+        <v>79.05683543241226</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.171939534218198</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-7742.103527652958</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-1.33328542519871</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>3.240243778522406e-07</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.8278783438886272</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1081.877</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.6937434793844347</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1583.370574256017</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.5626788186118357</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.06619e-07</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-84.54300000000001</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7672461269706286</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.073688639716408</v>
+      </c>
+      <c r="J71" t="n">
+        <v>46.56680091890948</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3.671151584716592</v>
+      </c>
+      <c r="L71" t="n">
+        <v>13.67848923597194</v>
+      </c>
+      <c r="M71" t="n">
+        <v>78.98136727189252</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5.135636781980701</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-7586.701877014153</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-1.84882022897591</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>3.062665850609764e-07</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.8366385479089919</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
